--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -13,6 +13,7 @@
     <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +45,29 @@
       <b val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +84,13 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,11 +98,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB7E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB7E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB7E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB7E8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -92,6 +133,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2053,4 +2106,85 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5597"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول خطا (Fault)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Fault_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1430,6 +1430,76 @@
       <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FA-020</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>snapshot zeroing</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>snapshot نامعتبر به Fault_Evaluate بده</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2s</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>بدون Set/Clear کاذب؛ فقط valid چک شود؛ هر 9 فیلد صفر شده باشد</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>بدون fault کاذب</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fault | مالک تشخیص متمرکز قطع باتری (بیت 6 FAULT_CHARGER_BAT_LOST) + ماسک خطای قفل‌شده</t>
+          <t>Fault | مالک تشخیص متمرکز قطع باتری (FAULT_CHARGER_BAT_LOST، بیت ۶) + ماسک خطای قفل‌شده</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>قفل بیت BAT_LOST؛ شارژر به BAT_LOST می‌رود و PWM قطع</t>
+          <t>قفل FAULT_CHARGER_BAT_LOST؛ شارژر به BAT_LOST می‌رود و PWM قطع</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>بیت 6=1 و state=8 در پنل</t>
+          <t>FAULT_CHARGER_BAT_LOST=1 و state=8 در پنل</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
@@ -832,7 +832,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>قفل بیت BAT_LOST</t>
+          <t>قفل FAULT_CHARGER_BAT_LOST</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>بیت 6=1</t>
+          <t>FAULT_CHARGER_BAT_LOST=1</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -913,7 +913,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>بیت 6=0 و شارژ از نو</t>
+          <t>FAULT_CHARGER_BAT_LOST=0 و شارژ از نو</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>هیچ قفلی؛ بیت 6 پاک می‌ماند؛ تمپ‌های دبانس صفر</t>
+          <t>هیچ قفلی؛ FAULT_CHARGER_BAT_LOST پاک می‌ماند؛ تمپ‌های دبانس صفر</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>بیت 6=0 حین مود</t>
+          <t>FAULT_CHARGER_BAT_LOST=0 حین مود</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr"/>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>بیت 6 → برچسب «باتری قطع»؛ بقیه hex خام</t>
+          <t>FAULT_CHARGER_BAT_LOST → برچسب «باتری قطع»؛ بقیه hex خام</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1489,14 +1489,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>2026-10-12</t>
@@ -1584,7 +1581,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>قفل بیت 6</t>
+          <t>قفل FAULT_CHARGER_BAT_LOST</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1611,7 +1608,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>قفل بیت 6</t>
+          <t>قفل FAULT_CHARGER_BAT_LOST</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1692,7 +1689,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>BAT_LOST=بیت 6</t>
+          <t>FAULT_CHARGER_BAT_LOST (بیت ۶)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -1410,7 +1410,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>fault 0x40 در پنل</t>
+          <t>fault برابر 64 در پنل (روی صفحه به‌صورت 0x40 دیده می‌شود)</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -746,7 +746,10 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>سیم یک نیم‌باتری را حین شارژ قطع کن؛ ولتاژ گره خروجی را بپاییر</t>
+          <t>گام ۱: شارژ را در حالت BULK یا ABSORB راه بینداز.
+گام ۲: حین شارژ، سیم یکی از نیم‌باتری‌ها را قطع کن و ولتاژ گره خروجی را نگاه کن.
+گام ۳: وقتی خروجی پمپ بالای 14800 میلی‌ولت رفت، حداکثر 150 میلی‌ثانیه صبر کن.
+گام ۴: در پنل باید قفل FAULT_CHARGER_BAT_LOST ست شود، شارژر به وضعیت BAT_LOST برود (state=8) و PWM قطع شود.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -817,7 +820,10 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>هر نیم‌باتری را جدا کن تا زیر 6V بماند</t>
+          <t>گام ۱: ورودی را سالم در بازهٔ 21 تا 28 ولت نگه دار.
+گام ۲: هر نیم‌باتری را جدا کن تا ولتاژش زیر 6 ولت (6000 میلی‌ولت) بماند.
+گام ۳: 1000 میلی‌ثانیه صبر کن.
+گام ۴: باید قفل FAULT_CHARGER_BAT_LOST ست شده باشد.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -888,7 +894,10 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>هر دو نیم ≥7V وصل و بدون پمپ نگه دار</t>
+          <t>گام ۱: اول بیت FAULT_CHARGER_BAT_LOST را قفل کن (مثل FL-001).
+گام ۲: هر دو نیم‌باتری را وصل کن و هر دو را دست‌کم 7 ولت (7000 میلی‌ولت) نگه دار، بدون اینکه پمپ شارژ فعال باشد.
+گام ۳: 1000 میلی‌ثانیه صبر کن.
+گام ۴: بیت باید پاک شده باشد؛ شارژر از OFF می‌گذرد، گیت 15 ثانیه‌ای را رد می‌کند و با رمپ نرم وارد BULK می‌شود.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -959,7 +968,10 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>ولتاژ نیم را در بازهٔ 6..7V نگه دار</t>
+          <t>گام ۱: باتری واقعی را وصل کن.
+گام ۲: ولتاژ یک نیم‌باتری را در ناحیهٔ مرده، یعنی بین 6000 تا 7000 میلی‌ولت، ثابت نگه دار.
+گام ۳: 60 ثانیه وضعیت بیت را نگاه کن.
+گام ۴: نباید نه تریپ تازه بیاید نه بیت به‌صورت نوسانی پاک و ست شود؛ بیت باید بی‌تغییر بماند.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1030,7 +1042,9 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>state هر دو کانال در پنل</t>
+          <t>گام ۱: اول بیت FAULT_CHARGER_BAT_LOST را قفل کن.
+گام ۲: در پنل وضعیت هر دو کانال را نگاه کن (2 ثانیه).
+گام ۳: هر دو کانال باید وضعیت CHG_STATE_BAT_LOST (شماره 8) و PWM صفر نشان دهند.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1101,7 +1115,9 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>رفتار Set/Clear حین نبود snapshot</t>
+          <t>گام ۱: ADC را در حالت warm-up نگه دار یا کاری کن snapshot نامعتبر باشد.
+گام ۲: رفتار ست/پاک شدن بیت‌ها را در همین مدت نگاه کن.
+گام ۳: تا وقتی snapshot معتبر نیست هیچ Set و Clear نباید اتفاق بیفتد و وضعیت قبلی ماسک باید حفظ شود.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1172,7 +1188,10 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>پمپ عمدی خروجی بالای 14.8V با electronic load</t>
+          <t>گام ۱: مود تست دستی را فعال کن (پارامتر 19 = 1).
+گام ۲: با electronic load خروجی را عمداً بالای 14.8 ولت (14800 میلی‌ولت) پمپ کن.
+گام ۳: 5 ثانیه نگاه کن: هیچ قفلی نباید بیاید و FAULT_CHARGER_BAT_LOST باید پاک بماند.
+گام ۴: متغیرهای موقت دبانس (temp) باید صفر بمانند.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1243,7 +1262,10 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>مود دستی را خاموش کن و شرایط قاعدهٔ ۱ را دوباره بساز</t>
+          <t>گام ۱: تست FL-007 را انجام بده (مود دستی، بدون قفل).
+گام ۲: مود دستی را خاموش کن.
+گام ۳: شرایط قاعدهٔ ۱ FL-001 را دوباره بساز (قطع نیم‌باتری حین شارژ).
+گام ۴: تشخیص باید از صفر شروع شده باشد و دقیقاً مثل FL-001 قفل کند.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1314,7 +1336,10 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>func__Fault_Set/Clear از مسیر تست</t>
+          <t>گام ۱: دیباگر را وصل کن و مسیر تست func__Fault_Set/Clear را آماده کن.
+گام ۲: چند بیت دلخواه را یک بار Set و یک بار Clear کن.
+گام ۳: ماسک را با func__Fault_Get بخوان و func__Fault_Any را چک کن.
+گام ۴: ماسک باید دقیقاً همان بیت‌هایی باشد که ست کردی و Any با بودن/نبودن بیت درست جواب دهد.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1385,7 +1410,10 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>فیلد fault_mask را در پنل ببین</t>
+          <t>گام ۱: پنل ESP را وصل کن.
+گام ۲: یک خطای قطع باتری بساز تا فیلد fault پر شود.
+گام ۳: مقدار fault را در پنل بخوان: باید برابر 64 باشد (روی صفحه به‌صورت 0x40 دیده می‌شود) و کنارش برچسب «باتری قطع» بیاید.
+گام ۴: بقیهٔ بیت‌ها به‌صورت hex خام نمایش داده می‌شوند.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1456,7 +1484,9 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>snapshot نامعتبر به Fault_Evaluate بده</t>
+          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
+گام ۲: آن را 2 ثانیه به Fault_Evaluate بده.
+گام ۳: ماسک خطا را بخوان: هیچ Set یا Clear کاذبی نباید اتفاق افتاده باشد؛ تابع فقط valid را چک می‌کند و بر اساس فیلدهای صفر تصمیم نمی‌گیرد.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -15,15 +15,20 @@
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +71,67 @@
       <name val="Vazirmatn"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -89,8 +153,28 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -112,11 +196,69 @@
         <color rgb="009DB7E8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -144,6 +286,85 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,6 +728,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -517,21 +739,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Fault</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Fault | مالک تشخیص متمرکز قطع باتری (FAULT_CHARGER_BAT_LOST، بیت ۶) + ماسک خطای قفل‌شده</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -541,21 +763,21 @@
       <c r="A4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>دو قاعده: پمپ &gt;14.8V حین شارژ فعال (150ms) و غیبت هر نیم &lt;6V با ورودی سالم (1s)؛ بازیابی هر دو نیم ≥7V بدون پمپ (1s).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>شارژر و UI فقط پرچم را می‌خوانند؛ حین مود تست دستی شارژر، تشخیص کامل فریز است (تمپ‌های دبانس صفر).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>بدون snapshot معتبر هیچ Set/Clear انجام نمی‌شود.</t>
         </is>
@@ -565,7 +787,7 @@
       <c r="A8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>هشدار: تست قطع باتری حین شارژ با جریان محدود و زیر نظارت؛ ولتاژ گره پمپ‌شده می‌تواند بالای 15V برود.</t>
         </is>
@@ -590,161 +812,162 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Fault</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="14" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>FL-001</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>قاعدهٔ پمپ</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>شارژ فعال (BULK/ABSORB)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="17" t="inlineStr">
         <is>
           <t>گام ۱: شارژ را در حالت BULK یا ABSORB راه بینداز.
 گام ۲: حین شارژ، سیم یکی از نیم‌باتری‌ها را قطع کن و ولتاژ گره خروجی را نگاه کن.
@@ -752,73 +975,73 @@
 گام ۴: در پنل باید قفل FAULT_CHARGER_BAT_LOST ست شود، شارژر به وضعیت BAT_LOST برود (state=8) و PWM قطع شود.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>خروجی پمپ &gt;14800mV</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>150ms</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>قفل FAULT_CHARGER_BAT_LOST؛ شارژر به BAT_LOST می‌رود و PWM قطع</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>latch تا بازیابی</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>FAULT_CHARGER_BAT_LOST=1 و state=8 در پنل</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K5" s="17" t="inlineStr"/>
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr"/>
+      <c r="N5" s="17" t="inlineStr"/>
+      <c r="O5" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="P5" s="19" t="inlineStr"/>
+      <c r="Q5" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>FL-002</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>قاعدهٔ غیبت</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>ورودی سالم 21..28V</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>گام ۱: ورودی را سالم در بازهٔ 21 تا 28 ولت نگه دار.
 گام ۲: هر نیم‌باتری را جدا کن تا ولتاژش زیر 6 ولت (6000 میلی‌ولت) بماند.
@@ -826,73 +1049,73 @@
 گام ۴: باید قفل FAULT_CHARGER_BAT_LOST ست شده باشد.</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>هر نیم &lt;6000mV</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>1000ms</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>قفل FAULT_CHARGER_BAT_LOST</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>latch تا بازیابی</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>FAULT_CHARGER_BAT_LOST=1</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr"/>
+      <c r="N6" s="22" t="inlineStr"/>
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="P6" s="24" t="inlineStr"/>
+      <c r="Q6" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>FL-003</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>بازیابی</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>بیت قفل‌شده</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>گام ۱: اول بیت FAULT_CHARGER_BAT_LOST را قفل کن (مثل FL-001).
 گام ۲: هر دو نیم‌باتری را وصل کن و هر دو را دست‌کم 7 ولت (7000 میلی‌ولت) نگه دار، بدون اینکه پمپ شارژ فعال باشد.
@@ -900,73 +1123,73 @@
 گام ۴: بیت باید پاک شده باشد؛ شارژر از OFF می‌گذرد، گیت 15 ثانیه‌ای را رد می‌کند و با رمپ نرم وارد BULK می‌شود.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>هر دو نیم ≥7000mV</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>1000ms</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>پاک شدن بیت؛ شارژر OFF → گیت 15s → BULK نرم</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>پاک‌شدن یک‌باره</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t>FAULT_CHARGER_BAT_LOST=0 و شارژ از نو</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="K7" s="17" t="inlineStr"/>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="M7" s="17" t="inlineStr"/>
+      <c r="N7" s="17" t="inlineStr"/>
+      <c r="O7" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="P7" s="19" t="inlineStr"/>
+      <c r="Q7" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>FL-004</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>هیسترزیس 6/7V</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>باتری واقعی وصل</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>گام ۱: باتری واقعی را وصل کن.
 گام ۲: ولتاژ یک نیم‌باتری را در ناحیهٔ مرده، یعنی بین 6000 تا 7000 میلی‌ولت، ثابت نگه دار.
@@ -974,219 +1197,219 @@
 گام ۴: نباید نه تریپ تازه بیاید نه بیت به‌صورت نوسانی پاک و ست شود؛ بیت باید بی‌تغییر بماند.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>6000..7000mV</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>نه تریپ تازه، نه پاک‌شدن نوسانی</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>پایدار</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>بدون تغییر بیت</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="M8" s="22" t="inlineStr"/>
+      <c r="N8" s="22" t="inlineStr"/>
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="P8" s="24" t="inlineStr"/>
+      <c r="Q8" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="40.5" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>FL-005</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>آینه در شارژر</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>بیت قفل‌شده</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>گام ۱: اول بیت FAULT_CHARGER_BAT_LOST را قفل کن.
 گام ۲: در پنل وضعیت هر دو کانال را نگاه کن (2 ثانیه).
 گام ۳: هر دو کانال باید وضعیت CHG_STATE_BAT_LOST (شماره 8) و PWM صفر نشان دهند.</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>کانال‌ها به CHG_STATE_BAT_LOST (8) و PWM صفر</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>تا پاک شدن بیت</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>state=8</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr"/>
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr"/>
+      <c r="N9" s="17" t="inlineStr"/>
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr"/>
+      <c r="Q9" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="40.5" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>FL-006</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>snapshot نامعتبر</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>ADC در warm-up یا نامعتبر</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>گام ۱: ADC را در حالت warm-up نگه دار یا کاری کن snapshot نامعتبر باشد.
 گام ۲: رفتار ست/پاک شدن بیت‌ها را در همین مدت نگاه کن.
 گام ۳: تا وقتی snapshot معتبر نیست هیچ Set و Clear نباید اتفاق بیفتد و وضعیت قبلی ماسک باید حفظ شود.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>هیچ Set/Clear؛ وضعیت قبلی حفظ</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>بدون تغییر ماسک</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="M10" s="22" t="inlineStr"/>
+      <c r="N10" s="22" t="inlineStr"/>
+      <c r="O10" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="P10" s="24" t="inlineStr"/>
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>FL-007</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>فریز در مود دستی</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>مود تست دستی فعال (ID19=1)</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>گام ۱: مود تست دستی را فعال کن (پارامتر 19 = 1).
 گام ۲: با electronic load خروجی را عمداً بالای 14.8 ولت (14800 میلی‌ولت) پمپ کن.
@@ -1194,73 +1417,73 @@
 گام ۴: متغیرهای موقت دبانس (temp) باید صفر بمانند.</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>خروجی &gt;14800mV در مود دستی</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>هیچ قفلی؛ FAULT_CHARGER_BAT_LOST پاک می‌ماند؛ تمپ‌های دبانس صفر</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>فریز کامل</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>FAULT_CHARGER_BAT_LOST=0 حین مود</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="K11" s="17" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr"/>
+      <c r="N11" s="17" t="inlineStr"/>
+      <c r="O11" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="P11" s="19" t="inlineStr"/>
+      <c r="Q11" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>FL-008</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>خروج از مود دستی</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>بعد از FL-007</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>گام ۱: تست FL-007 را انجام بده (مود دستی، بدون قفل).
 گام ۲: مود دستی را خاموش کن.
@@ -1268,73 +1491,73 @@
 گام ۴: تشخیص باید از صفر شروع شده باشد و دقیقاً مثل FL-001 قفل کند.</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>تشخیص از نو شروع می‌شود (تمپ صفر) و قاعدهٔ ۱ کار می‌کند</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="27" t="inlineStr">
         <is>
           <t>قفل طبق FL-001</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr"/>
+      <c r="N12" s="22" t="inlineStr"/>
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="P12" s="24" t="inlineStr"/>
+      <c r="Q12" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>FL-009</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>تزریق دستی</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>دیباگر وصل</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>گام ۱: دیباگر را وصل کن و مسیر تست func__Fault_Set/Clear را آماده کن.
 گام ۲: چند بیت دلخواه را یک بار Set و یک بار Clear کن.
@@ -1342,73 +1565,73 @@
 گام ۴: ماسک باید دقیقاً همان بیت‌هایی باشد که ست کردی و Any با بودن/نبودن بیت درست جواب دهد.</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>بیت‌های دلخواه</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>ماسک دقیقاً Set/Clear می‌شود</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>Get/Any مطابق</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr"/>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="M13" s="17" t="inlineStr"/>
+      <c r="N13" s="17" t="inlineStr"/>
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="P13" s="19" t="inlineStr"/>
+      <c r="Q13" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>FL-010</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>تله‌متری</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>پنل ESP وصل</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل ESP را وصل کن.
 گام ۲: یک خطای قطع باتری بساز تا فیلد fault پر شود.
@@ -1416,141 +1639,394 @@
 گام ۴: بقیهٔ بیت‌ها به‌صورت hex خام نمایش داده می‌شوند.</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>FAULT_CHARGER_BAT_LOST → برچسب «باتری قطع»؛ بقیه hex خام</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="22" t="inlineStr">
         <is>
           <t>fault برابر 64 در پنل (روی صفحه به‌صورت 0x40 دیده می‌شود)</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="M14" s="22" t="inlineStr"/>
+      <c r="N14" s="22" t="inlineStr"/>
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="P14" s="24" t="inlineStr"/>
+      <c r="Q14" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="40.5" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>FA-020</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>snapshot zeroing</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
 گام ۲: آن را 2 ثانیه به Fault_Evaluate بده.
 گام ۳: ماسک خطا را بخوان: هیچ Set یا Clear کاذبی نباید اتفاق افتاده باشد؛ تابع فقط valid را چک می‌کند و بر اساس فیلدهای صفر تصمیم نمی‌گیرد.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="19" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr">
         <is>
           <t>بدون Set/Clear کاذب؛ فقط valid چک شود؛ هر 9 فیلد صفر شده باشد</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>بدون fault کاذب</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" s="17" t="n"/>
+      <c r="L15" s="28" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="M15" s="17" t="n"/>
+      <c r="N15" s="17" t="n"/>
+      <c r="O15" s="19" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="P15" s="19" t="n"/>
+      <c r="Q15" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="Q16" s="29">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="29">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="29">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="29">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="29">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="29">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="29">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="29">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="29">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="29">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="29">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="29">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="29">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="29">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="29">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="29">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="29">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="29">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="29">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="29">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="29">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="29">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="29">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="29">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="29">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="29">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="29">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="29">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="29">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="29">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="Q46" s="29">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="Q47" s="29">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="Q48" s="29">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="Q49" s="29">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="Q50" s="29">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="Q51" s="29">
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="Q52" s="29">
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="Q53" s="29">
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="Q54" s="29">
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="Q55" s="29">
+        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:Q15"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="C5:C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
+    <dataValidation sqref="L5:L95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1564,170 +2040,175 @@
     <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Fault</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="40" t="n"/>
+      <c r="C1" s="40" t="n"/>
+      <c r="D1" s="40" t="n"/>
+      <c r="E1" s="41" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>قاعدهٔ پمپ</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>&gt;14.8V حین BULK/ABSORB، 150ms</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>قفل FAULT_CHARGER_BAT_LOST</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>FAULT_BAT_DISCONNECT_MV / FAULT_BAT_DISCONNECT_DEBOUNCE_MS</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>فقط کانال فعال</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>قاعدهٔ غیبت</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>هر نیم &lt;6V با ورودی سالم، 1s</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>قفل FAULT_CHARGER_BAT_LOST</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="31" t="inlineStr">
         <is>
           <t>FAULT_BAT_ABSENT_MV / FAULT_BAT_ABSENT_DEBOUNCE_MS</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="31" t="inlineStr">
         <is>
           <t>هرکدام، نه هر دو</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>بازیابی</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>هر دو نیم ≥7V بدون پمپ، 1s</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>پاک شدن بیت</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>FAULT_BATTERY_BACK_MV / FAULT_BAT_RECOVER_MS</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t>هیسترزیس 1V</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>فریز مود دستی</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>IsManualTestModeActive</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>بدون Set/Clear، تمپ صفر</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>fault.c (v1.2)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t>پمپ عمدی عادی‌سازی شد</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>بیت‌های ماسک</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>0..6 در app_types.h</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>FAULT_CHARGER_BAT_LOST (بیت ۶)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>FAULT_*</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t>0x40 در تله‌متری</t>
         </is>
@@ -1737,6 +2218,10 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1744,6 +2229,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1766,81 +2252,93 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Fault</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
+      <c r="B2" s="40" t="n"/>
+      <c r="C2" s="40" t="n"/>
+      <c r="D2" s="40" t="n"/>
+      <c r="E2" s="40" t="n"/>
+      <c r="F2" s="40" t="n"/>
+      <c r="G2" s="40" t="n"/>
+      <c r="H2" s="40" t="n"/>
+      <c r="I2" s="40" t="n"/>
+      <c r="J2" s="40" t="n"/>
+      <c r="K2" s="40" t="n"/>
+      <c r="L2" s="40" t="n"/>
+      <c r="M2" s="41" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="30" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="30" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="30" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="30" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="30" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -1858,6 +2356,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1870,203 +2369,205 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Fault</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Fault — تشخیص متمرکز قطع باتری</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2026-09-23 (1.0 — شامل فریز v1.2)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>پنل ESP + مولتی‌متر + سیم‌کشی تست</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="33">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="33">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="33">
         <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="33">
         <f>IF(10=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/10)</f>
         <v/>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
@@ -2085,6 +2586,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2096,105 +2598,113 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -2208,7 +2718,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2220,55 +2730,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول خطا (Fault)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>Fault_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="38" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
@@ -2281,6 +2792,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$54</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -28,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,6 +131,13 @@
       <name val="Tahoma"/>
       <color rgb="000563C1"/>
       <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -258,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -365,6 +375,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -816,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1539,99 +1556,25 @@
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>FL-009</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>تزریق دستی</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>پایین</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>دیباگر وصل</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>گام ۱: دیباگر را وصل کن و مسیر تست func__Fault_Set/Clear را آماده کن.
-گام ۲: چند بیت دلخواه را یک بار Set و یک بار Clear کن.
-گام ۳: ماسک را با func__Fault_Get بخوان و func__Fault_Any را چک کن.
-گام ۴: ماسک باید دقیقاً همان بیت‌هایی باشد که ست کردی و Any با بودن/نبودن بیت درست جواب دهد.</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>بیت‌های دلخواه</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>ماسک دقیقاً Set/Clear می‌شود</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>Get/Any مطابق</t>
-        </is>
-      </c>
-      <c r="K13" s="17" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="inlineStr"/>
-      <c r="N13" s="17" t="inlineStr"/>
-      <c r="O13" s="19" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P13" s="19" t="inlineStr"/>
-      <c r="Q13" s="21" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
           <t>FL-010</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>تله‌متری</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>پنل ESP وصل</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>گام ۱: پنل ESP را وصل کن.
 گام ۲: یک خطای قطع باتری بساز تا فیلد fault پر شود.
@@ -1639,366 +1582,366 @@
 گام ۴: بقیهٔ بیت‌ها به‌صورت hex خام نمایش داده می‌شوند.</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G13" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>FAULT_CHARGER_BAT_LOST → برچسب «باتری قطع»؛ بقیه hex خام</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="22" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>fault برابر 64 در پنل (روی صفحه به‌صورت 0x40 دیده می‌شود)</t>
         </is>
       </c>
-      <c r="K14" s="22" t="inlineStr"/>
-      <c r="L14" s="20" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M14" s="22" t="inlineStr"/>
-      <c r="N14" s="22" t="inlineStr"/>
-      <c r="O14" s="24" t="inlineStr">
+      <c r="M13" s="22" t="inlineStr"/>
+      <c r="N13" s="22" t="inlineStr"/>
+      <c r="O13" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P14" s="24" t="inlineStr"/>
-      <c r="Q14" s="25" t="inlineStr">
+      <c r="P13" s="24" t="inlineStr"/>
+      <c r="Q13" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="40.5" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="14" ht="54" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>FA-020</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>snapshot zeroing</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
 گام ۲: آن را 2 ثانیه به Fault_Evaluate بده.
 گام ۳: ماسک خطا را بخوان: هیچ Set یا Clear کاذبی نباید اتفاق افتاده باشد؛ تابع فقط valid را چک می‌کند و بر اساس فیلدهای صفر تصمیم نمی‌گیرد.</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>بدون Set/Clear کاذب؛ فقط valid چک شود؛ هر 9 فیلد صفر شده باشد</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J14" s="17" t="inlineStr">
         <is>
           <t>بدون fault کاذب</t>
         </is>
       </c>
-      <c r="K15" s="17" t="n"/>
-      <c r="L15" s="28" t="inlineStr">
+      <c r="K14" s="17" t="n"/>
+      <c r="L14" s="28" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M15" s="17" t="n"/>
-      <c r="N15" s="17" t="n"/>
-      <c r="O15" s="19" t="inlineStr">
+      <c r="M14" s="17" t="n"/>
+      <c r="N14" s="17" t="n"/>
+      <c r="O14" s="19" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P15" s="19" t="n"/>
-      <c r="Q15" s="21" t="inlineStr">
+      <c r="P14" s="19" t="n"/>
+      <c r="Q14" s="21" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
+      </c>
+    </row>
+    <row r="15" ht="40.5" customHeight="1">
+      <c r="Q15" s="29">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="Q16" s="29">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="Q17" s="29">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="Q18" s="29">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="Q19" s="29">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="Q20" s="29">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="Q21" s="29">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="Q22" s="29">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="Q23" s="29">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="Q24" s="29">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="29">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="29">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="29">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="29">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="29">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="29">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="29">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="29">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="29">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="29">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="29">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="29">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="29">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="29">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="29">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="29">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="29">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="29">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="29">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="29">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="29">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="29">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="29">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="29">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="29">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="29">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="29">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="29">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="Q53" s="29">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="Q54" s="29">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="Q55" s="29">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q15"/>
+  <autoFilter ref="A4:Q54"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -2013,10 +1956,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId4"/>
+    <hyperlink ref="E7" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D12" location="'برنامه تست'!A11"/>
+    <hyperlink ref="E12" location="'برنامه تست'!A11"/>
+    <hyperlink ref="J12" location="'برنامه تست'!A5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2024,6 +1967,343 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="44" t="inlineStr">
+        <is>
+          <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>FL-009</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>تزریق دستی</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>دیباگر وصل</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: دیباگر را وصل کن و مسیر تست func__Fault_Set/Clear را آماده کن.
+گام ۲: چند بیت دلخواه را یک بار Set و یک بار Clear کن.
+گام ۳: ماسک را با func__Fault_Get بخوان و func__Fault_Any را چک کن.
+گام ۴: ماسک باید دقیقاً همان بیت‌هایی باشد که ست کردی و Any با بودن/نبودن بیت درست جواب دهد.</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>بیت‌های دلخواه</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>ماسک دقیقاً Set/Clear می‌شود</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t>Get/Any مطابق</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="17" t="n"/>
+      <c r="N5" s="17" t="n"/>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="Q6" s="29">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="Q7" s="29">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="Q8" s="29">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="29">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="29">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="29">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="29">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="29">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="29">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="29">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="29">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="29">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="29">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="29">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="29">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="29">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="29">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="29">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="29">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="29">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -2226,7 +2506,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -2353,7 +2633,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -2583,7 +2863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -2715,7 +2995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -999,7 +999,7 @@
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>150ms</t>
+          <t>کمتر از یک ثانیه</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>1000ms</t>
+          <t>۱ ثانیه</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>1000ms</t>
+          <t>۱ ثانیه</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -15,6 +15,7 @@
     <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$54</definedName>
@@ -833,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -981,40 +982,39 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>شارژ فعال (BULK/ABSORB)</t>
+          <t>دستگاه با برق شهر روشن است و باتری واقعی در حال شارژ است (چراغ زرد چشمک می‌زند)</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: شارژ را در حالت BULK یا ABSORB راه بینداز.
-گام ۲: حین شارژ، سیم یکی از نیم‌باتری‌ها را قطع کن و ولتاژ گره خروجی را نگاه کن.
-گام ۳: وقتی خروجی پمپ بالای 14800 میلی‌ولت رفت، حداکثر 150 میلی‌ثانیه صبر کن.
-گام ۴: در پنل باید قفل FAULT_CHARGER_BAT_LOST ست شود، شارژر به وضعیت BAT_LOST برود (state=8) و PWM قطع شود.</t>
+          <t>گام ۱: حین شارژ، سیم یکی از باتری‌ها را از ترمینال جدا کن.
+گام ۲: چند ثانیه صبر کن و چراغ‌ها را ببین: قرمز باید تندتند چشمک بزند، سبز ثابت بماند و هر چند ثانیه سه بوق بیاید.
+گام ۳: در پنل نگاه کن که خطای شمارهٔ ۶ ثبت شده و جریان شارژ صفر شده است.</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>خروجی پمپ &gt;14800mV</t>
+          <t>کشیدن سیم باتری حین شارژ</t>
         </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>کمتر از یک ثانیه</t>
+          <t>کمتر از یک دقیقه</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>قفل FAULT_CHARGER_BAT_LOST؛ شارژر به BAT_LOST می‌رود و PWM قطع</t>
+          <t>خطای ۶ (قطع باتری) می‌آید: قرمز چشمک‌تند، سبز ثابت، سه بوق دوره‌ای و شارژ کاملاً متوقف</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>latch تا بازیابی</t>
+          <t>می‌ماند تا باتری برگردد</t>
         </is>
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>FAULT_CHARGER_BAT_LOST=1 و state=8 در پنل</t>
+          <t>آمدن خطا ظرف چند ثانیه با همان چهره = قبول؛ نیامدن یا شارژِ ادامه‌دار = رد</t>
         </is>
       </c>
       <c r="K5" s="17" t="inlineStr"/>
@@ -1055,40 +1055,39 @@
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>ورودی سالم 21..28V</t>
+          <t>باتری را اصلاً وصل نکرده‌ای؛ فقط برق شهر آماده است</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: ورودی را سالم در بازهٔ 21 تا 28 ولت نگه دار.
-گام ۲: هر نیم‌باتری را جدا کن تا ولتاژش زیر 6 ولت (6000 میلی‌ولت) بماند.
-گام ۳: 1000 میلی‌ثانیه صبر کن.
-گام ۴: باید قفل FAULT_CHARGER_BAT_LOST ست شده باشد.</t>
+          <t>گام ۱: بدون باتری، برق شهر را به دستگاه وصل کن.
+گام ۲: چند ثانیه صبر کن.
+گام ۳: چراغ‌ها و پنل را چک کن.</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>هر نیم &lt;6000mV</t>
+          <t>روشن‌کردن دستگاه بدون باتری با برق شهر</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>۱ ثانیه</t>
+          <t>کمتر از یک دقیقه</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>قفل FAULT_CHARGER_BAT_LOST</t>
+          <t>خطای ۶ می‌آید (قرمز چشمک‌تند و سه بوق) و شارژ هیچ‌وقت شروع نمی‌شود</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t>latch تا بازیابی</t>
+          <t>می‌ماند تا باتری وصل شود</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>FAULT_CHARGER_BAT_LOST=1</t>
+          <t>آمدن خطای ۶ و شروع‌نشدن شارژ = قبول؛ شروع شارژ بی‌باتری = رد</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr"/>
@@ -1127,42 +1126,41 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>بیت قفل‌شده</t>
-        </is>
-      </c>
-      <c r="E7" s="26" t="inlineStr">
-        <is>
-          <t>گام ۱: اول بیت FAULT_CHARGER_BAT_LOST را قفل کن (مثل FL-001).
-گام ۲: هر دو نیم‌باتری را وصل کن و هر دو را دست‌کم 7 ولت (7000 میلی‌ولت) نگه دار، بدون اینکه پمپ شارژ فعال باشد.
-گام ۳: 1000 میلی‌ثانیه صبر کن.
-گام ۴: بیت باید پاک شده باشد؛ شارژر از OFF می‌گذرد، گیت 15 ثانیه‌ای را رد می‌کند و با رمپ نرم وارد BULK می‌شود.</t>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>از FL-001 ادامه بده؛ خطای ۶ فعال است و سیم باتری جداست</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: سیم باتری را سر جایش وصل کن.
+گام ۲: چند ثانیه صبر کن: چشمک قرمز و بوق باید قطع شود.
+گام ۳: کمی بیشتر صبر کن؛ شارژ باید بعد از یک مکث کوتاه آرام از سر گرفته شود.</t>
         </is>
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>هر دو نیم ≥7000mV</t>
+          <t>وصل دوبارهٔ باتری</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>۱ ثانیه</t>
+          <t>یک دقیقه</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>پاک شدن بیت؛ شارژر OFF → گیت 15s → BULK نرم</t>
+          <t>خطای ۶ خودش پاک می‌شود و شارژ بدون پرش و ناگهانی برگشتن، عادی شروع می‌شود</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>پاک‌شدن یک‌باره</t>
+          <t>پاک‌شدن خودکار با برگشت باتری</t>
         </is>
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>FAULT_CHARGER_BAT_LOST=0 و شارژ از نو</t>
+          <t>پاک‌شدن و شروع آرام شارژ = قبول؛ ماندن خطا یا شروع خشن = رد</t>
         </is>
       </c>
       <c r="K7" s="17" t="inlineStr"/>
@@ -1203,40 +1201,39 @@
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>باتری واقعی وصل</t>
+          <t>به‌جای یکی از باتری‌ها منبع آزمایشگاهی گذاشته‌ای؛ دستگاه با برق شهر روشن است</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>گام ۱: باتری واقعی را وصل کن.
-گام ۲: ولتاژ یک نیم‌باتری را در ناحیهٔ مرده، یعنی بین 6000 تا 7000 میلی‌ولت، ثابت نگه دار.
-گام ۳: 60 ثانیه وضعیت بیت را نگاه کن.
-گام ۴: نباید نه تریپ تازه بیاید نه بیت به‌صورت نوسانی پاک و ست شود؛ بیت باید بی‌تغییر بماند.</t>
+          <t>گام ۱: ولتاژ منبع را حدود ۶٫۵ ولت نگه دار (نه وصلِ سالم، نه قطعِ کامل).
+گام ۲: دو دقیقه نگاه کن؛ خطا نباید پرپر بزند.
+گام ۳: ولتاژ را بالای ۷ ببر (سالم) و بعد زیر ۶ ببر (قطع) و هر بار رفتار را چک کن.</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>6000..7000mV</t>
+          <t>ولتاژ یک نیم باتری: ۶٫۵ بعد بالای ۷ بعد زیر ۶ ولت</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>60s</t>
+          <t>سه دقیقه</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>نه تریپ تازه، نه پاک‌شدن نوسانی</t>
+          <t>روی ۶٫۵ نه خطای تازه می‌آید نه پاک و ست می‌شود؛ بالای ۷ سالم است و زیر ۶ خطای ۶ می‌آید</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
-          <t>پایدار</t>
+          <t>بدون پرپر دور مرز</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
         <is>
-          <t>بدون تغییر بیت</t>
+          <t>رفتار تمیز در هر سه نقطه = قبول؛ پرپر زدن رو ۶٫۵ = رد</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr"/>
@@ -1275,41 +1272,41 @@
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>بیت قفل‌شده</t>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>خطای ۶ را مثل FL-001 ساخته‌ای و فعال است</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>گام ۱: اول بیت FAULT_CHARGER_BAT_LOST را قفل کن.
-گام ۲: در پنل وضعیت هر دو کانال را نگاه کن (2 ثانیه).
-گام ۳: هر دو کانال باید وضعیت CHG_STATE_BAT_LOST (شماره 8) و PWM صفر نشان دهند.</t>
+          <t>گام ۱: یک آمپرمتر دستی سریِ مسیر شارژ بگذار یا جریان شارژ پنل را نگاه کن.
+گام ۲: تا وقتی خطا هست جریان را زیر نظر بگیر.
+گام ۳: باتری را وصل کن و ببین شارژ کی برمی‌گردد.</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>نگه‌داشتن خطای ۶ و بعد وصل باتری</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>2s</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>کانال‌ها به CHG_STATE_BAT_LOST (8) و PWM صفر</t>
+          <t>تا وقتی خطای ۶ هست جریان شارژ صفر می‌ماند؛ شارژر بیکار است و فقط با برگشت باتری دوباره راه می‌افتد</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>تا پاک شدن بیت</t>
+          <t>توقف کامل تا بازیابی</t>
         </is>
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>state=8</t>
+          <t>جریان صفر در تمام مدت خطا = قبول؛ هر جریان شارژی حین خطا = رد</t>
         </is>
       </c>
       <c r="K9" s="17" t="inlineStr"/>
@@ -1335,71 +1332,71 @@
     <row r="10" ht="40.5" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>FL-006</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>snapshot نامعتبر</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+          <t>FL-007</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>فریز در مود دستی</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>ADC در warm-up یا نامعتبر</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>گام ۱: ADC را در حالت warm-up نگه دار یا کاری کن snapshot نامعتبر باشد.
-گام ۲: رفتار ست/پاک شدن بیت‌ها را در همین مدت نگاه کن.
-گام ۳: تا وقتی snapshot معتبر نیست هیچ Set و Clear نباید اتفاق بیفتد و وضعیت قبلی ماسک باید حفظ شود.</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>هیچ Set/Clear؛ وضعیت قبلی حفظ</t>
-        </is>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="inlineStr">
-        <is>
-          <t>بدون تغییر ماسک</t>
-        </is>
-      </c>
-      <c r="K10" s="22" t="inlineStr"/>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>دستگاه روشن و از پنل، مود تست دستی شارژر را می‌توانی روشن کنی</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل مود تست دستی شارژر را فعال کن.
+گام ۲: در همین مود سیم باتری را بکش و چند ثانیه صبر کن.
+گام ۳: باتری را وصل کن.</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>قطع و وصل باتری داخل مود دستی</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>در مود دستی خطای ۶ ساخته نمی‌شود و چراغ قرمز قطع باتری نمی‌آید</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>بدون قفل در مود دستی</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>نیامدن خطا در مود دستی = قبول؛ آمدن خطای ۶ = رد</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr"/>
       <c r="L10" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="22" t="inlineStr"/>
-      <c r="N10" s="22" t="inlineStr"/>
-      <c r="O10" s="24" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr"/>
+      <c r="N10" s="17" t="inlineStr"/>
+      <c r="O10" s="19" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="24" t="inlineStr"/>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="P10" s="19" t="inlineStr"/>
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1408,72 +1405,71 @@
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>FL-007</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>فریز در مود دستی</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>مود تست دستی فعال (ID19=1)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>گام ۱: مود تست دستی را فعال کن (پارامتر 19 = 1).
-گام ۲: با electronic load خروجی را عمداً بالای 14.8 ولت (14800 میلی‌ولت) پمپ کن.
-گام ۳: 5 ثانیه نگاه کن: هیچ قفلی نباید بیاید و FAULT_CHARGER_BAT_LOST باید پاک بماند.
-گام ۴: متغیرهای موقت دبانس (temp) باید صفر بمانند.</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>خروجی &gt;14800mV در مود دستی</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>5s</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>هیچ قفلی؛ FAULT_CHARGER_BAT_LOST پاک می‌ماند؛ تمپ‌های دبانس صفر</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>فریز کامل</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>FAULT_CHARGER_BAT_LOST=0 حین مود</t>
-        </is>
-      </c>
-      <c r="K11" s="17" t="inlineStr"/>
+          <t>FL-008</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>خروج از مود دستی</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>از FL-007 ادامه بده؛ مود دستی فعال است</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل از مود تست دستی خارج شو.
+گام ۲: حالا سیم باتری را حین شارژ بکش.
+گام ۳: چراغ‌ها را ببین.</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>خروج از مود دستی و قطع باتری</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>بعد از خروج از مود دستی، قطع باتری دوباره مثل حالت عادی خطای ۶ می‌سازد</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>برگشت رفتار عادی</t>
+        </is>
+      </c>
+      <c r="J11" s="27" t="inlineStr">
+        <is>
+          <t>ساخته‌شدن دوبارهٔ خطای ۶ = قبول؛ نساختن = رد</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr"/>
       <c r="L11" s="20" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="17" t="inlineStr"/>
-      <c r="N11" s="17" t="inlineStr"/>
-      <c r="O11" s="19" t="inlineStr">
+      <c r="M11" s="22" t="inlineStr"/>
+      <c r="N11" s="22" t="inlineStr"/>
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="19" t="inlineStr"/>
-      <c r="Q11" s="21" t="inlineStr">
+      <c r="P11" s="24" t="inlineStr"/>
+      <c r="Q11" s="25" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -1482,12 +1478,12 @@
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>FL-008</t>
+          <t>FL-010</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>خروج از مود دستی</t>
+          <t>تله‌متری</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -1495,42 +1491,41 @@
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
-        <is>
-          <t>بعد از FL-007</t>
-        </is>
-      </c>
-      <c r="E12" s="27" t="inlineStr">
-        <is>
-          <t>گام ۱: تست FL-007 را انجام بده (مود دستی، بدون قفل).
-گام ۲: مود دستی را خاموش کن.
-گام ۳: شرایط قاعدهٔ ۱ FL-001 را دوباره بساز (قطع نیم‌باتری حین شارژ).
-گام ۴: تشخیص باید از صفر شروع شده باشد و دقیقاً مثل FL-001 قفل کند.</t>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>پنل باز است و تله‌متری زنده را می‌بینی</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
+گام ۲: در پنل نگاه کن خطای ۶ و توقف شارژ دیده می‌شود.
+گام ۳: باتری را وصل کن و پاک‌شدن خطا را در پنل ببین.</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ساختن و پاک‌کردن خطای ۶ جلوی پنل</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>2s</t>
+          <t>دو دقیقه</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
         <is>
-          <t>تشخیص از نو شروع می‌شود (تمپ صفر) و قاعدهٔ ۱ کار می‌کند</t>
+          <t>پنل همان چیزی را نشان می‌دهد که روی دستگاه می‌بینی: خطای ۶ می‌آید و با برگشت باتری پاک می‌شود</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="27" t="inlineStr">
-        <is>
-          <t>قفل طبق FL-001</t>
+          <t>هم‌گام با چراغ‌های دستگاه</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>یکی‌بودن پنل و چراغ‌ها = قبول؛ اختلاف پنل با واقعیت = رد</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr"/>
@@ -1554,388 +1549,241 @@
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>FL-010</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>تله‌متری</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>پنل ESP وصل</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>گام ۱: پنل ESP را وصل کن.
-گام ۲: یک خطای قطع باتری بساز تا فیلد fault پر شود.
-گام ۳: مقدار fault را در پنل بخوان: باید برابر 64 باشد (روی صفحه به‌صورت 0x40 دیده می‌شود) و کنارش برچسب «باتری قطع» بیاید.
-گام ۴: بقیهٔ بیت‌ها به‌صورت hex خام نمایش داده می‌شوند.</t>
-        </is>
-      </c>
-      <c r="F13" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr">
-        <is>
-          <t>FAULT_CHARGER_BAT_LOST → برچسب «باتری قطع»؛ بقیه hex خام</t>
-        </is>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="22" t="inlineStr">
-        <is>
-          <t>fault برابر 64 در پنل (روی صفحه به‌صورت 0x40 دیده می‌شود)</t>
-        </is>
-      </c>
-      <c r="K13" s="22" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M13" s="22" t="inlineStr"/>
-      <c r="N13" s="22" t="inlineStr"/>
-      <c r="O13" s="24" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P13" s="24" t="inlineStr"/>
-      <c r="Q13" s="25" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="Q13" s="29">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>FA-020</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>snapshot zeroing</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
-گام ۲: آن را 2 ثانیه به Fault_Evaluate بده.
-گام ۳: ماسک خطا را بخوان: هیچ Set یا Clear کاذبی نباید اتفاق افتاده باشد؛ تابع فقط valid را چک می‌کند و بر اساس فیلدهای صفر تصمیم نمی‌گیرد.</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>2s</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>بدون Set/Clear کاذب؛ فقط valid چک شود؛ هر 9 فیلد صفر شده باشد</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>بدون fault کاذب</t>
-        </is>
-      </c>
-      <c r="K14" s="17" t="n"/>
-      <c r="L14" s="28" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="n"/>
-      <c r="N14" s="17" t="n"/>
-      <c r="O14" s="19" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P14" s="19" t="n"/>
-      <c r="Q14" s="21" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
+      <c r="Q14" s="29">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
       </c>
     </row>
     <row r="15" ht="40.5" customHeight="1">
       <c r="Q15" s="29">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="Q16" s="29">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="Q17" s="29">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="Q18" s="29">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="Q19" s="29">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="Q20" s="29">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="Q21" s="29">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="Q22" s="29">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="Q23" s="29">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="Q24" s="29">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="29">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="29">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="29">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="29">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="29">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="29">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="29">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="29">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="29">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="29">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="29">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="29">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="29">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="29">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="29">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="29">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="29">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="29">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="29">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="29">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="29">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="29">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="29">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="Q48" s="29">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="Q49" s="29">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="Q50" s="29">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
+        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="Q51" s="29">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
+        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="Q52" s="29">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="Q53" s="29">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="Q54" s="29">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
@@ -1956,10 +1804,9 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E7" location="'برنامه تست'!A5"/>
-    <hyperlink ref="D12" location="'برنامه تست'!A11"/>
-    <hyperlink ref="E12" location="'برنامه تست'!A11"/>
-    <hyperlink ref="J12" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D7" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D9" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D11" location="'برنامه تست'!A10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2172,7 +2019,73 @@
       </c>
     </row>
     <row r="6">
-      <c r="Q6" s="29">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>FA-020</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>snapshot zeroing</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
+گام ۲: آن را 2 ثانیه به Fault_Evaluate بده.
+گام ۳: ماسک خطا را بخوان: هیچ Set یا Clear کاذبی نباید اتفاق افتاده باشد؛ تابع فقط valid را چک می‌کند و بر اساس فیلدهای صفر تصمیم نمی‌گیرد.</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>2s</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>بدون Set/Clear کاذب؛ فقط valid چک شود؛ هر 9 فیلد صفر شده باشد</t>
+        </is>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>بدون fault کاذب</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="n"/>
+      <c r="L6" s="28" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M6" s="17" t="n"/>
+      <c r="N6" s="17" t="n"/>
+      <c r="O6" s="19" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P6" s="19" t="n"/>
+      <c r="Q6" s="21">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -3076,4 +2989,234 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>برنامهٔ تست آزمایشگاهی — ماژول Fault</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>FL-006</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>snapshot نامعتبر</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>ADC در warm-up یا نامعتبر</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>گام ۱: ADC را در حالت warm-up نگه دار یا کاری کن snapshot نامعتبر باشد.
+گام ۲: رفتار ست/پاک شدن بیت‌ها را در همین مدت نگاه کن.
+گام ۳: تا وقتی snapshot معتبر نیست هیچ Set و Clear نباید اتفاق بیفتد و وضعیت قبلی ماسک باید حفظ شود.</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>هیچ Set/Clear؛ وضعیت قبلی حفظ</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="22" t="inlineStr">
+        <is>
+          <t>بدون تغییر ماسک</t>
+        </is>
+      </c>
+      <c r="K5" s="22" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="22" t="n"/>
+      <c r="N5" s="22" t="n"/>
+      <c r="O5" s="24" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="24" t="n"/>
+      <c r="Q5" s="25">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1"/>
+    <row r="7" ht="54" customHeight="1"/>
+    <row r="8" ht="54" customHeight="1"/>
+    <row r="9" ht="40.5" customHeight="1"/>
+    <row r="10" ht="40.5" customHeight="1"/>
+    <row r="11" ht="54" customHeight="1"/>
+    <row r="12" ht="54" customHeight="1"/>
+    <row r="13" ht="54" customHeight="1"/>
+    <row r="14" ht="54" customHeight="1"/>
+    <row r="15" ht="40.5" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,6 +140,51 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="9">
@@ -269,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -384,6 +429,78 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -757,55 +874,55 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="46" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Fault</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>Fault | مالک تشخیص متمرکز قطع باتری (FAULT_CHARGER_BAT_LOST، بیت ۶) + ماسک خطای قفل‌شده</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="47" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>دو قاعده: پمپ &gt;14.8V حین شارژ فعال (150ms) و غیبت هر نیم &lt;6V با ورودی سالم (1s)؛ بازیابی هر دو نیم ≥7V بدون پمپ (1s).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>شارژر و UI فقط پرچم را می‌خوانند؛ حین مود تست دستی شارژر، تشخیص کامل فریز است (تمپ‌های دبانس صفر).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>بدون snapshot معتبر هیچ Set/Clear انجام نمی‌شود.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="47" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>هشدار: تست قطع باتری حین شارژ با جریان محدود و زیر نظارت؛ ولتاژ گره پمپ‌شده می‌تواند بالای 15V برود.</t>
         </is>
@@ -857,933 +974,1621 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Fault</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+      <c r="D1" s="50" t="n"/>
+      <c r="E1" s="50" t="n"/>
+      <c r="F1" s="50" t="n"/>
+      <c r="G1" s="50" t="n"/>
+      <c r="H1" s="50" t="n"/>
+      <c r="I1" s="50" t="n"/>
+      <c r="J1" s="50" t="n"/>
+      <c r="K1" s="50" t="n"/>
+      <c r="L1" s="50" t="n"/>
+      <c r="M1" s="50" t="n"/>
+      <c r="N1" s="50" t="n"/>
+      <c r="O1" s="50" t="n"/>
+      <c r="P1" s="50" t="n"/>
+      <c r="Q1" s="50" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="50" t="n"/>
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="50" t="n"/>
+      <c r="F2" s="50" t="n"/>
+      <c r="G2" s="50" t="n"/>
+      <c r="H2" s="50" t="n"/>
+      <c r="I2" s="50" t="n"/>
+      <c r="J2" s="50" t="n"/>
+      <c r="K2" s="50" t="n"/>
+      <c r="L2" s="50" t="n"/>
+      <c r="M2" s="50" t="n"/>
+      <c r="N2" s="50" t="n"/>
+      <c r="O2" s="50" t="n"/>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="50" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="47" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="50" t="n"/>
+      <c r="C3" s="50" t="n"/>
+      <c r="D3" s="50" t="n"/>
+      <c r="E3" s="50" t="n"/>
+      <c r="F3" s="50" t="n"/>
+      <c r="G3" s="50" t="n"/>
+      <c r="H3" s="50" t="n"/>
+      <c r="I3" s="50" t="n"/>
+      <c r="J3" s="50" t="n"/>
+      <c r="K3" s="50" t="n"/>
+      <c r="L3" s="50" t="n"/>
+      <c r="M3" s="50" t="n"/>
+      <c r="N3" s="50" t="n"/>
+      <c r="O3" s="50" t="n"/>
+      <c r="P3" s="50" t="n"/>
+      <c r="Q3" s="50" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="48" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="48" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="48" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="48" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="48" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="48" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="48" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="48" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="48" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="48" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="48" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="48" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>FL-001</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>قاعدهٔ پمپ</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="52" t="inlineStr">
         <is>
           <t>دستگاه با برق شهر روشن است و باتری واقعی در حال شارژ است (چراغ زرد چشمک می‌زند)</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="52" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ، سیم یکی از باتری‌ها را از ترمینال جدا کن.
 گام ۲: چند ثانیه صبر کن و چراغ‌ها را ببین: قرمز باید تندتند چشمک بزند، سبز ثابت بماند و هر چند ثانیه سه بوق بیاید.
 گام ۳: در پنل نگاه کن که خطای شمارهٔ ۶ ثبت شده و جریان شارژ صفر شده است.</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="54" t="inlineStr">
         <is>
           <t>کشیدن سیم باتری حین شارژ</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="54" t="inlineStr">
         <is>
           <t>کمتر از یک دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="52" t="inlineStr">
         <is>
           <t>خطای ۶ (قطع باتری) می‌آید: قرمز چشمک‌تند، سبز ثابت، سه بوق دوره‌ای و شارژ کاملاً متوقف</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="52" t="inlineStr">
         <is>
           <t>می‌ماند تا باتری برگردد</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="52" t="inlineStr">
         <is>
           <t>آمدن خطا ظرف چند ثانیه با همان چهره = قبول؛ نیامدن یا شارژِ ادامه‌دار = رد</t>
         </is>
       </c>
-      <c r="K5" s="17" t="inlineStr"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="K5" s="52" t="inlineStr"/>
+      <c r="L5" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="17" t="inlineStr"/>
-      <c r="N5" s="17" t="inlineStr"/>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="M5" s="52" t="inlineStr"/>
+      <c r="N5" s="52" t="inlineStr"/>
+      <c r="O5" s="54" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="19" t="inlineStr"/>
-      <c r="Q5" s="21" t="inlineStr">
+      <c r="P5" s="54" t="inlineStr"/>
+      <c r="Q5" s="56" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>FL-002</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="57" t="inlineStr">
         <is>
           <t>قاعدهٔ غیبت</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="57" t="inlineStr">
         <is>
           <t>باتری را اصلاً وصل نکرده‌ای؛ فقط برق شهر آماده است</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="57" t="inlineStr">
         <is>
           <t>گام ۱: بدون باتری، برق شهر را به دستگاه وصل کن.
 گام ۲: چند ثانیه صبر کن.
 گام ۳: چراغ‌ها و پنل را چک کن.</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr">
+      <c r="F6" s="59" t="inlineStr">
         <is>
           <t>روشن‌کردن دستگاه بدون باتری با برق شهر</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="59" t="inlineStr">
         <is>
           <t>کمتر از یک دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="57" t="inlineStr">
         <is>
           <t>خطای ۶ می‌آید (قرمز چشمک‌تند و سه بوق) و شارژ هیچ‌وقت شروع نمی‌شود</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="57" t="inlineStr">
         <is>
           <t>می‌ماند تا باتری وصل شود</t>
         </is>
       </c>
-      <c r="J6" s="22" t="inlineStr">
+      <c r="J6" s="57" t="inlineStr">
         <is>
           <t>آمدن خطای ۶ و شروع‌نشدن شارژ = قبول؛ شروع شارژ بی‌باتری = رد</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="K6" s="57" t="inlineStr"/>
+      <c r="L6" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr"/>
-      <c r="N6" s="22" t="inlineStr"/>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="M6" s="57" t="inlineStr"/>
+      <c r="N6" s="57" t="inlineStr"/>
+      <c r="O6" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="24" t="inlineStr"/>
-      <c r="Q6" s="25" t="inlineStr">
+      <c r="P6" s="59" t="inlineStr"/>
+      <c r="Q6" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="51" t="inlineStr">
         <is>
           <t>FL-003</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="52" t="inlineStr">
         <is>
           <t>بازیابی</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="53" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="26" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>از FL-001 ادامه بده؛ خطای ۶ فعال است و سیم باتری جداست</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="52" t="inlineStr">
         <is>
           <t>گام ۱: سیم باتری را سر جایش وصل کن.
 گام ۲: چند ثانیه صبر کن: چشمک قرمز و بوق باید قطع شود.
 گام ۳: کمی بیشتر صبر کن؛ شارژ باید بعد از یک مکث کوتاه آرام از سر گرفته شود.</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="54" t="inlineStr">
         <is>
           <t>وصل دوبارهٔ باتری</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="54" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="52" t="inlineStr">
         <is>
           <t>خطای ۶ خودش پاک می‌شود و شارژ بدون پرش و ناگهانی برگشتن، عادی شروع می‌شود</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="52" t="inlineStr">
         <is>
           <t>پاک‌شدن خودکار با برگشت باتری</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="52" t="inlineStr">
         <is>
           <t>پاک‌شدن و شروع آرام شارژ = قبول؛ ماندن خطا یا شروع خشن = رد</t>
         </is>
       </c>
-      <c r="K7" s="17" t="inlineStr"/>
-      <c r="L7" s="20" t="inlineStr">
+      <c r="K7" s="52" t="inlineStr"/>
+      <c r="L7" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="17" t="inlineStr"/>
-      <c r="N7" s="17" t="inlineStr"/>
-      <c r="O7" s="19" t="inlineStr">
+      <c r="M7" s="52" t="inlineStr"/>
+      <c r="N7" s="52" t="inlineStr"/>
+      <c r="O7" s="54" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="19" t="inlineStr"/>
-      <c r="Q7" s="21" t="inlineStr">
+      <c r="P7" s="54" t="inlineStr"/>
+      <c r="Q7" s="56" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>FL-004</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="57" t="inlineStr">
         <is>
           <t>هیسترزیس 6/7V</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="57" t="inlineStr">
         <is>
           <t>به‌جای یکی از باتری‌ها منبع آزمایشگاهی گذاشته‌ای؛ دستگاه با برق شهر روشن است</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="57" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را حدود ۶٫۵ ولت نگه دار (نه وصلِ سالم، نه قطعِ کامل).
 گام ۲: دو دقیقه نگاه کن؛ خطا نباید پرپر بزند.
 گام ۳: ولتاژ را بالای ۷ ببر (سالم) و بعد زیر ۶ ببر (قطع) و هر بار رفتار را چک کن.</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="59" t="inlineStr">
         <is>
           <t>ولتاژ یک نیم باتری: ۶٫۵ بعد بالای ۷ بعد زیر ۶ ولت</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="59" t="inlineStr">
         <is>
           <t>سه دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="57" t="inlineStr">
         <is>
           <t>روی ۶٫۵ نه خطای تازه می‌آید نه پاک و ست می‌شود؛ بالای ۷ سالم است و زیر ۶ خطای ۶ می‌آید</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="57" t="inlineStr">
         <is>
           <t>بدون پرپر دور مرز</t>
         </is>
       </c>
-      <c r="J8" s="22" t="inlineStr">
+      <c r="J8" s="57" t="inlineStr">
         <is>
           <t>رفتار تمیز در هر سه نقطه = قبول؛ پرپر زدن رو ۶٫۵ = رد</t>
         </is>
       </c>
-      <c r="K8" s="22" t="inlineStr"/>
-      <c r="L8" s="20" t="inlineStr">
+      <c r="K8" s="57" t="inlineStr"/>
+      <c r="L8" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="22" t="inlineStr"/>
-      <c r="N8" s="22" t="inlineStr"/>
-      <c r="O8" s="24" t="inlineStr">
+      <c r="M8" s="57" t="inlineStr"/>
+      <c r="N8" s="57" t="inlineStr"/>
+      <c r="O8" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="24" t="inlineStr"/>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="P8" s="59" t="inlineStr"/>
+      <c r="Q8" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="51" t="inlineStr">
         <is>
           <t>FL-005</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="52" t="inlineStr">
         <is>
           <t>آینه در شارژر</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D9" s="26" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>خطای ۶ را مثل FL-001 ساخته‌ای و فعال است</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="52" t="inlineStr">
         <is>
           <t>گام ۱: یک آمپرمتر دستی سریِ مسیر شارژ بگذار یا جریان شارژ پنل را نگاه کن.
 گام ۲: تا وقتی خطا هست جریان را زیر نظر بگیر.
 گام ۳: باتری را وصل کن و ببین شارژ کی برمی‌گردد.</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="54" t="inlineStr">
         <is>
           <t>نگه‌داشتن خطای ۶ و بعد وصل باتری</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="54" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="52" t="inlineStr">
         <is>
           <t>تا وقتی خطای ۶ هست جریان شارژ صفر می‌ماند؛ شارژر بیکار است و فقط با برگشت باتری دوباره راه می‌افتد</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="52" t="inlineStr">
         <is>
           <t>توقف کامل تا بازیابی</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="52" t="inlineStr">
         <is>
           <t>جریان صفر در تمام مدت خطا = قبول؛ هر جریان شارژی حین خطا = رد</t>
         </is>
       </c>
-      <c r="K9" s="17" t="inlineStr"/>
-      <c r="L9" s="20" t="inlineStr">
+      <c r="K9" s="52" t="inlineStr"/>
+      <c r="L9" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="17" t="inlineStr"/>
-      <c r="N9" s="17" t="inlineStr"/>
-      <c r="O9" s="19" t="inlineStr">
+      <c r="M9" s="52" t="inlineStr"/>
+      <c r="N9" s="52" t="inlineStr"/>
+      <c r="O9" s="54" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="19" t="inlineStr"/>
-      <c r="Q9" s="21" t="inlineStr">
+      <c r="P9" s="54" t="inlineStr"/>
+      <c r="Q9" s="56" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>FL-007</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="52" t="inlineStr">
         <is>
           <t>فریز در مود دستی</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="52" t="inlineStr">
         <is>
           <t>دستگاه روشن و از پنل، مود تست دستی شارژر را می‌توانی روشن کنی</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="52" t="inlineStr">
         <is>
           <t>گام ۱: از پنل مود تست دستی شارژر را فعال کن.
 گام ۲: در همین مود سیم باتری را بکش و چند ثانیه صبر کن.
 گام ۳: باتری را وصل کن.</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="54" t="inlineStr">
         <is>
           <t>قطع و وصل باتری داخل مود دستی</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="54" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="52" t="inlineStr">
         <is>
           <t>در مود دستی خطای ۶ ساخته نمی‌شود و چراغ قرمز قطع باتری نمی‌آید</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I10" s="52" t="inlineStr">
         <is>
           <t>بدون قفل در مود دستی</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="52" t="inlineStr">
         <is>
           <t>نیامدن خطا در مود دستی = قبول؛ آمدن خطای ۶ = رد</t>
         </is>
       </c>
-      <c r="K10" s="17" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="K10" s="52" t="inlineStr"/>
+      <c r="L10" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M10" s="17" t="inlineStr"/>
-      <c r="N10" s="17" t="inlineStr"/>
-      <c r="O10" s="19" t="inlineStr">
+      <c r="M10" s="52" t="inlineStr"/>
+      <c r="N10" s="52" t="inlineStr"/>
+      <c r="O10" s="54" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P10" s="19" t="inlineStr"/>
-      <c r="Q10" s="21" t="inlineStr">
+      <c r="P10" s="54" t="inlineStr"/>
+      <c r="Q10" s="56" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>FL-008</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="57" t="inlineStr">
         <is>
           <t>خروج از مود دستی</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="62" t="inlineStr">
         <is>
           <t>از FL-007 ادامه بده؛ مود دستی فعال است</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="62" t="inlineStr">
         <is>
           <t>گام ۱: از پنل از مود تست دستی خارج شو.
 گام ۲: حالا سیم باتری را حین شارژ بکش.
 گام ۳: چراغ‌ها را ببین.</t>
         </is>
       </c>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="F11" s="59" t="inlineStr">
         <is>
           <t>خروج از مود دستی و قطع باتری</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="59" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="57" t="inlineStr">
         <is>
           <t>بعد از خروج از مود دستی، قطع باتری دوباره مثل حالت عادی خطای ۶ می‌سازد</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="57" t="inlineStr">
         <is>
           <t>برگشت رفتار عادی</t>
         </is>
       </c>
-      <c r="J11" s="27" t="inlineStr">
+      <c r="J11" s="62" t="inlineStr">
         <is>
           <t>ساخته‌شدن دوبارهٔ خطای ۶ = قبول؛ نساختن = رد</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr"/>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="K11" s="57" t="inlineStr"/>
+      <c r="L11" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M11" s="22" t="inlineStr"/>
-      <c r="N11" s="22" t="inlineStr"/>
-      <c r="O11" s="24" t="inlineStr">
+      <c r="M11" s="57" t="inlineStr"/>
+      <c r="N11" s="57" t="inlineStr"/>
+      <c r="O11" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P11" s="24" t="inlineStr"/>
-      <c r="Q11" s="25" t="inlineStr">
+      <c r="P11" s="59" t="inlineStr"/>
+      <c r="Q11" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>FL-010</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="57" t="inlineStr">
         <is>
           <t>تله‌متری</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="57" t="inlineStr">
         <is>
           <t>پنل باز است و تله‌متری زنده را می‌بینی</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="57" t="inlineStr">
         <is>
           <t>گام ۱: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
 گام ۲: در پنل نگاه کن خطای ۶ و توقف شارژ دیده می‌شود.
 گام ۳: باتری را وصل کن و پاک‌شدن خطا را در پنل ببین.</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="F12" s="59" t="inlineStr">
         <is>
           <t>ساختن و پاک‌کردن خطای ۶ جلوی پنل</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="59" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="57" t="inlineStr">
         <is>
           <t>پنل همان چیزی را نشان می‌دهد که روی دستگاه می‌بینی: خطای ۶ می‌آید و با برگشت باتری پاک می‌شود</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="57" t="inlineStr">
         <is>
           <t>هم‌گام با چراغ‌های دستگاه</t>
         </is>
       </c>
-      <c r="J12" s="22" t="inlineStr">
+      <c r="J12" s="57" t="inlineStr">
         <is>
           <t>یکی‌بودن پنل و چراغ‌ها = قبول؛ اختلاف پنل با واقعیت = رد</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="K12" s="57" t="inlineStr"/>
+      <c r="L12" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr"/>
-      <c r="N12" s="22" t="inlineStr"/>
-      <c r="O12" s="24" t="inlineStr">
+      <c r="M12" s="57" t="inlineStr"/>
+      <c r="N12" s="57" t="inlineStr"/>
+      <c r="O12" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P12" s="24" t="inlineStr"/>
-      <c r="Q12" s="25" t="inlineStr">
+      <c r="P12" s="59" t="inlineStr"/>
+      <c r="Q12" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="13" ht="54" customHeight="1">
-      <c r="Q13" s="29">
+      <c r="A13" s="50" t="n"/>
+      <c r="B13" s="50" t="n"/>
+      <c r="C13" s="50" t="n"/>
+      <c r="D13" s="50" t="n"/>
+      <c r="E13" s="50" t="n"/>
+      <c r="F13" s="50" t="n"/>
+      <c r="G13" s="50" t="n"/>
+      <c r="H13" s="50" t="n"/>
+      <c r="I13" s="50" t="n"/>
+      <c r="J13" s="50" t="n"/>
+      <c r="K13" s="50" t="n"/>
+      <c r="L13" s="50" t="n"/>
+      <c r="M13" s="50" t="n"/>
+      <c r="N13" s="50" t="n"/>
+      <c r="O13" s="50" t="n"/>
+      <c r="P13" s="50" t="n"/>
+      <c r="Q13" s="63">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="Q14" s="29">
+      <c r="A14" s="50" t="n"/>
+      <c r="B14" s="50" t="n"/>
+      <c r="C14" s="50" t="n"/>
+      <c r="D14" s="50" t="n"/>
+      <c r="E14" s="50" t="n"/>
+      <c r="F14" s="50" t="n"/>
+      <c r="G14" s="50" t="n"/>
+      <c r="H14" s="50" t="n"/>
+      <c r="I14" s="50" t="n"/>
+      <c r="J14" s="50" t="n"/>
+      <c r="K14" s="50" t="n"/>
+      <c r="L14" s="50" t="n"/>
+      <c r="M14" s="50" t="n"/>
+      <c r="N14" s="50" t="n"/>
+      <c r="O14" s="50" t="n"/>
+      <c r="P14" s="50" t="n"/>
+      <c r="Q14" s="63">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="40.5" customHeight="1">
-      <c r="Q15" s="29">
+      <c r="A15" s="50" t="n"/>
+      <c r="B15" s="50" t="n"/>
+      <c r="C15" s="50" t="n"/>
+      <c r="D15" s="50" t="n"/>
+      <c r="E15" s="50" t="n"/>
+      <c r="F15" s="50" t="n"/>
+      <c r="G15" s="50" t="n"/>
+      <c r="H15" s="50" t="n"/>
+      <c r="I15" s="50" t="n"/>
+      <c r="J15" s="50" t="n"/>
+      <c r="K15" s="50" t="n"/>
+      <c r="L15" s="50" t="n"/>
+      <c r="M15" s="50" t="n"/>
+      <c r="N15" s="50" t="n"/>
+      <c r="O15" s="50" t="n"/>
+      <c r="P15" s="50" t="n"/>
+      <c r="Q15" s="63">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="29">
+      <c r="A16" s="50" t="n"/>
+      <c r="B16" s="50" t="n"/>
+      <c r="C16" s="50" t="n"/>
+      <c r="D16" s="50" t="n"/>
+      <c r="E16" s="50" t="n"/>
+      <c r="F16" s="50" t="n"/>
+      <c r="G16" s="50" t="n"/>
+      <c r="H16" s="50" t="n"/>
+      <c r="I16" s="50" t="n"/>
+      <c r="J16" s="50" t="n"/>
+      <c r="K16" s="50" t="n"/>
+      <c r="L16" s="50" t="n"/>
+      <c r="M16" s="50" t="n"/>
+      <c r="N16" s="50" t="n"/>
+      <c r="O16" s="50" t="n"/>
+      <c r="P16" s="50" t="n"/>
+      <c r="Q16" s="63">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="29">
+      <c r="A17" s="50" t="n"/>
+      <c r="B17" s="50" t="n"/>
+      <c r="C17" s="50" t="n"/>
+      <c r="D17" s="50" t="n"/>
+      <c r="E17" s="50" t="n"/>
+      <c r="F17" s="50" t="n"/>
+      <c r="G17" s="50" t="n"/>
+      <c r="H17" s="50" t="n"/>
+      <c r="I17" s="50" t="n"/>
+      <c r="J17" s="50" t="n"/>
+      <c r="K17" s="50" t="n"/>
+      <c r="L17" s="50" t="n"/>
+      <c r="M17" s="50" t="n"/>
+      <c r="N17" s="50" t="n"/>
+      <c r="O17" s="50" t="n"/>
+      <c r="P17" s="50" t="n"/>
+      <c r="Q17" s="63">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="29">
+      <c r="A18" s="50" t="n"/>
+      <c r="B18" s="50" t="n"/>
+      <c r="C18" s="50" t="n"/>
+      <c r="D18" s="50" t="n"/>
+      <c r="E18" s="50" t="n"/>
+      <c r="F18" s="50" t="n"/>
+      <c r="G18" s="50" t="n"/>
+      <c r="H18" s="50" t="n"/>
+      <c r="I18" s="50" t="n"/>
+      <c r="J18" s="50" t="n"/>
+      <c r="K18" s="50" t="n"/>
+      <c r="L18" s="50" t="n"/>
+      <c r="M18" s="50" t="n"/>
+      <c r="N18" s="50" t="n"/>
+      <c r="O18" s="50" t="n"/>
+      <c r="P18" s="50" t="n"/>
+      <c r="Q18" s="63">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="29">
+      <c r="A19" s="50" t="n"/>
+      <c r="B19" s="50" t="n"/>
+      <c r="C19" s="50" t="n"/>
+      <c r="D19" s="50" t="n"/>
+      <c r="E19" s="50" t="n"/>
+      <c r="F19" s="50" t="n"/>
+      <c r="G19" s="50" t="n"/>
+      <c r="H19" s="50" t="n"/>
+      <c r="I19" s="50" t="n"/>
+      <c r="J19" s="50" t="n"/>
+      <c r="K19" s="50" t="n"/>
+      <c r="L19" s="50" t="n"/>
+      <c r="M19" s="50" t="n"/>
+      <c r="N19" s="50" t="n"/>
+      <c r="O19" s="50" t="n"/>
+      <c r="P19" s="50" t="n"/>
+      <c r="Q19" s="63">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="29">
+      <c r="A20" s="50" t="n"/>
+      <c r="B20" s="50" t="n"/>
+      <c r="C20" s="50" t="n"/>
+      <c r="D20" s="50" t="n"/>
+      <c r="E20" s="50" t="n"/>
+      <c r="F20" s="50" t="n"/>
+      <c r="G20" s="50" t="n"/>
+      <c r="H20" s="50" t="n"/>
+      <c r="I20" s="50" t="n"/>
+      <c r="J20" s="50" t="n"/>
+      <c r="K20" s="50" t="n"/>
+      <c r="L20" s="50" t="n"/>
+      <c r="M20" s="50" t="n"/>
+      <c r="N20" s="50" t="n"/>
+      <c r="O20" s="50" t="n"/>
+      <c r="P20" s="50" t="n"/>
+      <c r="Q20" s="63">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="29">
+      <c r="A21" s="50" t="n"/>
+      <c r="B21" s="50" t="n"/>
+      <c r="C21" s="50" t="n"/>
+      <c r="D21" s="50" t="n"/>
+      <c r="E21" s="50" t="n"/>
+      <c r="F21" s="50" t="n"/>
+      <c r="G21" s="50" t="n"/>
+      <c r="H21" s="50" t="n"/>
+      <c r="I21" s="50" t="n"/>
+      <c r="J21" s="50" t="n"/>
+      <c r="K21" s="50" t="n"/>
+      <c r="L21" s="50" t="n"/>
+      <c r="M21" s="50" t="n"/>
+      <c r="N21" s="50" t="n"/>
+      <c r="O21" s="50" t="n"/>
+      <c r="P21" s="50" t="n"/>
+      <c r="Q21" s="63">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="29">
+      <c r="A22" s="50" t="n"/>
+      <c r="B22" s="50" t="n"/>
+      <c r="C22" s="50" t="n"/>
+      <c r="D22" s="50" t="n"/>
+      <c r="E22" s="50" t="n"/>
+      <c r="F22" s="50" t="n"/>
+      <c r="G22" s="50" t="n"/>
+      <c r="H22" s="50" t="n"/>
+      <c r="I22" s="50" t="n"/>
+      <c r="J22" s="50" t="n"/>
+      <c r="K22" s="50" t="n"/>
+      <c r="L22" s="50" t="n"/>
+      <c r="M22" s="50" t="n"/>
+      <c r="N22" s="50" t="n"/>
+      <c r="O22" s="50" t="n"/>
+      <c r="P22" s="50" t="n"/>
+      <c r="Q22" s="63">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="29">
+      <c r="A23" s="50" t="n"/>
+      <c r="B23" s="50" t="n"/>
+      <c r="C23" s="50" t="n"/>
+      <c r="D23" s="50" t="n"/>
+      <c r="E23" s="50" t="n"/>
+      <c r="F23" s="50" t="n"/>
+      <c r="G23" s="50" t="n"/>
+      <c r="H23" s="50" t="n"/>
+      <c r="I23" s="50" t="n"/>
+      <c r="J23" s="50" t="n"/>
+      <c r="K23" s="50" t="n"/>
+      <c r="L23" s="50" t="n"/>
+      <c r="M23" s="50" t="n"/>
+      <c r="N23" s="50" t="n"/>
+      <c r="O23" s="50" t="n"/>
+      <c r="P23" s="50" t="n"/>
+      <c r="Q23" s="63">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="29">
+      <c r="A24" s="50" t="n"/>
+      <c r="B24" s="50" t="n"/>
+      <c r="C24" s="50" t="n"/>
+      <c r="D24" s="50" t="n"/>
+      <c r="E24" s="50" t="n"/>
+      <c r="F24" s="50" t="n"/>
+      <c r="G24" s="50" t="n"/>
+      <c r="H24" s="50" t="n"/>
+      <c r="I24" s="50" t="n"/>
+      <c r="J24" s="50" t="n"/>
+      <c r="K24" s="50" t="n"/>
+      <c r="L24" s="50" t="n"/>
+      <c r="M24" s="50" t="n"/>
+      <c r="N24" s="50" t="n"/>
+      <c r="O24" s="50" t="n"/>
+      <c r="P24" s="50" t="n"/>
+      <c r="Q24" s="63">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="29">
+      <c r="A25" s="50" t="n"/>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+      <c r="E25" s="50" t="n"/>
+      <c r="F25" s="50" t="n"/>
+      <c r="G25" s="50" t="n"/>
+      <c r="H25" s="50" t="n"/>
+      <c r="I25" s="50" t="n"/>
+      <c r="J25" s="50" t="n"/>
+      <c r="K25" s="50" t="n"/>
+      <c r="L25" s="50" t="n"/>
+      <c r="M25" s="50" t="n"/>
+      <c r="N25" s="50" t="n"/>
+      <c r="O25" s="50" t="n"/>
+      <c r="P25" s="50" t="n"/>
+      <c r="Q25" s="63">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="29">
+      <c r="A26" s="50" t="n"/>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+      <c r="E26" s="50" t="n"/>
+      <c r="F26" s="50" t="n"/>
+      <c r="G26" s="50" t="n"/>
+      <c r="H26" s="50" t="n"/>
+      <c r="I26" s="50" t="n"/>
+      <c r="J26" s="50" t="n"/>
+      <c r="K26" s="50" t="n"/>
+      <c r="L26" s="50" t="n"/>
+      <c r="M26" s="50" t="n"/>
+      <c r="N26" s="50" t="n"/>
+      <c r="O26" s="50" t="n"/>
+      <c r="P26" s="50" t="n"/>
+      <c r="Q26" s="63">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="29">
+      <c r="A27" s="50" t="n"/>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+      <c r="E27" s="50" t="n"/>
+      <c r="F27" s="50" t="n"/>
+      <c r="G27" s="50" t="n"/>
+      <c r="H27" s="50" t="n"/>
+      <c r="I27" s="50" t="n"/>
+      <c r="J27" s="50" t="n"/>
+      <c r="K27" s="50" t="n"/>
+      <c r="L27" s="50" t="n"/>
+      <c r="M27" s="50" t="n"/>
+      <c r="N27" s="50" t="n"/>
+      <c r="O27" s="50" t="n"/>
+      <c r="P27" s="50" t="n"/>
+      <c r="Q27" s="63">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="29">
+      <c r="A28" s="50" t="n"/>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+      <c r="E28" s="50" t="n"/>
+      <c r="F28" s="50" t="n"/>
+      <c r="G28" s="50" t="n"/>
+      <c r="H28" s="50" t="n"/>
+      <c r="I28" s="50" t="n"/>
+      <c r="J28" s="50" t="n"/>
+      <c r="K28" s="50" t="n"/>
+      <c r="L28" s="50" t="n"/>
+      <c r="M28" s="50" t="n"/>
+      <c r="N28" s="50" t="n"/>
+      <c r="O28" s="50" t="n"/>
+      <c r="P28" s="50" t="n"/>
+      <c r="Q28" s="63">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="29">
+      <c r="A29" s="50" t="n"/>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+      <c r="E29" s="50" t="n"/>
+      <c r="F29" s="50" t="n"/>
+      <c r="G29" s="50" t="n"/>
+      <c r="H29" s="50" t="n"/>
+      <c r="I29" s="50" t="n"/>
+      <c r="J29" s="50" t="n"/>
+      <c r="K29" s="50" t="n"/>
+      <c r="L29" s="50" t="n"/>
+      <c r="M29" s="50" t="n"/>
+      <c r="N29" s="50" t="n"/>
+      <c r="O29" s="50" t="n"/>
+      <c r="P29" s="50" t="n"/>
+      <c r="Q29" s="63">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="29">
+      <c r="A30" s="50" t="n"/>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+      <c r="E30" s="50" t="n"/>
+      <c r="F30" s="50" t="n"/>
+      <c r="G30" s="50" t="n"/>
+      <c r="H30" s="50" t="n"/>
+      <c r="I30" s="50" t="n"/>
+      <c r="J30" s="50" t="n"/>
+      <c r="K30" s="50" t="n"/>
+      <c r="L30" s="50" t="n"/>
+      <c r="M30" s="50" t="n"/>
+      <c r="N30" s="50" t="n"/>
+      <c r="O30" s="50" t="n"/>
+      <c r="P30" s="50" t="n"/>
+      <c r="Q30" s="63">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="29">
+      <c r="A31" s="50" t="n"/>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+      <c r="E31" s="50" t="n"/>
+      <c r="F31" s="50" t="n"/>
+      <c r="G31" s="50" t="n"/>
+      <c r="H31" s="50" t="n"/>
+      <c r="I31" s="50" t="n"/>
+      <c r="J31" s="50" t="n"/>
+      <c r="K31" s="50" t="n"/>
+      <c r="L31" s="50" t="n"/>
+      <c r="M31" s="50" t="n"/>
+      <c r="N31" s="50" t="n"/>
+      <c r="O31" s="50" t="n"/>
+      <c r="P31" s="50" t="n"/>
+      <c r="Q31" s="63">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="29">
+      <c r="A32" s="50" t="n"/>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+      <c r="E32" s="50" t="n"/>
+      <c r="F32" s="50" t="n"/>
+      <c r="G32" s="50" t="n"/>
+      <c r="H32" s="50" t="n"/>
+      <c r="I32" s="50" t="n"/>
+      <c r="J32" s="50" t="n"/>
+      <c r="K32" s="50" t="n"/>
+      <c r="L32" s="50" t="n"/>
+      <c r="M32" s="50" t="n"/>
+      <c r="N32" s="50" t="n"/>
+      <c r="O32" s="50" t="n"/>
+      <c r="P32" s="50" t="n"/>
+      <c r="Q32" s="63">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="29">
+      <c r="A33" s="50" t="n"/>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+      <c r="E33" s="50" t="n"/>
+      <c r="F33" s="50" t="n"/>
+      <c r="G33" s="50" t="n"/>
+      <c r="H33" s="50" t="n"/>
+      <c r="I33" s="50" t="n"/>
+      <c r="J33" s="50" t="n"/>
+      <c r="K33" s="50" t="n"/>
+      <c r="L33" s="50" t="n"/>
+      <c r="M33" s="50" t="n"/>
+      <c r="N33" s="50" t="n"/>
+      <c r="O33" s="50" t="n"/>
+      <c r="P33" s="50" t="n"/>
+      <c r="Q33" s="63">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="29">
+      <c r="A34" s="50" t="n"/>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+      <c r="E34" s="50" t="n"/>
+      <c r="F34" s="50" t="n"/>
+      <c r="G34" s="50" t="n"/>
+      <c r="H34" s="50" t="n"/>
+      <c r="I34" s="50" t="n"/>
+      <c r="J34" s="50" t="n"/>
+      <c r="K34" s="50" t="n"/>
+      <c r="L34" s="50" t="n"/>
+      <c r="M34" s="50" t="n"/>
+      <c r="N34" s="50" t="n"/>
+      <c r="O34" s="50" t="n"/>
+      <c r="P34" s="50" t="n"/>
+      <c r="Q34" s="63">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="29">
+      <c r="A35" s="50" t="n"/>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+      <c r="E35" s="50" t="n"/>
+      <c r="F35" s="50" t="n"/>
+      <c r="G35" s="50" t="n"/>
+      <c r="H35" s="50" t="n"/>
+      <c r="I35" s="50" t="n"/>
+      <c r="J35" s="50" t="n"/>
+      <c r="K35" s="50" t="n"/>
+      <c r="L35" s="50" t="n"/>
+      <c r="M35" s="50" t="n"/>
+      <c r="N35" s="50" t="n"/>
+      <c r="O35" s="50" t="n"/>
+      <c r="P35" s="50" t="n"/>
+      <c r="Q35" s="63">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="29">
+      <c r="A36" s="50" t="n"/>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+      <c r="E36" s="50" t="n"/>
+      <c r="F36" s="50" t="n"/>
+      <c r="G36" s="50" t="n"/>
+      <c r="H36" s="50" t="n"/>
+      <c r="I36" s="50" t="n"/>
+      <c r="J36" s="50" t="n"/>
+      <c r="K36" s="50" t="n"/>
+      <c r="L36" s="50" t="n"/>
+      <c r="M36" s="50" t="n"/>
+      <c r="N36" s="50" t="n"/>
+      <c r="O36" s="50" t="n"/>
+      <c r="P36" s="50" t="n"/>
+      <c r="Q36" s="63">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="29">
+      <c r="A37" s="50" t="n"/>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+      <c r="E37" s="50" t="n"/>
+      <c r="F37" s="50" t="n"/>
+      <c r="G37" s="50" t="n"/>
+      <c r="H37" s="50" t="n"/>
+      <c r="I37" s="50" t="n"/>
+      <c r="J37" s="50" t="n"/>
+      <c r="K37" s="50" t="n"/>
+      <c r="L37" s="50" t="n"/>
+      <c r="M37" s="50" t="n"/>
+      <c r="N37" s="50" t="n"/>
+      <c r="O37" s="50" t="n"/>
+      <c r="P37" s="50" t="n"/>
+      <c r="Q37" s="63">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="29">
+      <c r="A38" s="50" t="n"/>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+      <c r="E38" s="50" t="n"/>
+      <c r="F38" s="50" t="n"/>
+      <c r="G38" s="50" t="n"/>
+      <c r="H38" s="50" t="n"/>
+      <c r="I38" s="50" t="n"/>
+      <c r="J38" s="50" t="n"/>
+      <c r="K38" s="50" t="n"/>
+      <c r="L38" s="50" t="n"/>
+      <c r="M38" s="50" t="n"/>
+      <c r="N38" s="50" t="n"/>
+      <c r="O38" s="50" t="n"/>
+      <c r="P38" s="50" t="n"/>
+      <c r="Q38" s="63">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="29">
+      <c r="A39" s="50" t="n"/>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+      <c r="E39" s="50" t="n"/>
+      <c r="F39" s="50" t="n"/>
+      <c r="G39" s="50" t="n"/>
+      <c r="H39" s="50" t="n"/>
+      <c r="I39" s="50" t="n"/>
+      <c r="J39" s="50" t="n"/>
+      <c r="K39" s="50" t="n"/>
+      <c r="L39" s="50" t="n"/>
+      <c r="M39" s="50" t="n"/>
+      <c r="N39" s="50" t="n"/>
+      <c r="O39" s="50" t="n"/>
+      <c r="P39" s="50" t="n"/>
+      <c r="Q39" s="63">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="29">
+      <c r="A40" s="50" t="n"/>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+      <c r="E40" s="50" t="n"/>
+      <c r="F40" s="50" t="n"/>
+      <c r="G40" s="50" t="n"/>
+      <c r="H40" s="50" t="n"/>
+      <c r="I40" s="50" t="n"/>
+      <c r="J40" s="50" t="n"/>
+      <c r="K40" s="50" t="n"/>
+      <c r="L40" s="50" t="n"/>
+      <c r="M40" s="50" t="n"/>
+      <c r="N40" s="50" t="n"/>
+      <c r="O40" s="50" t="n"/>
+      <c r="P40" s="50" t="n"/>
+      <c r="Q40" s="63">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="29">
+      <c r="A41" s="50" t="n"/>
+      <c r="B41" s="50" t="n"/>
+      <c r="C41" s="50" t="n"/>
+      <c r="D41" s="50" t="n"/>
+      <c r="E41" s="50" t="n"/>
+      <c r="F41" s="50" t="n"/>
+      <c r="G41" s="50" t="n"/>
+      <c r="H41" s="50" t="n"/>
+      <c r="I41" s="50" t="n"/>
+      <c r="J41" s="50" t="n"/>
+      <c r="K41" s="50" t="n"/>
+      <c r="L41" s="50" t="n"/>
+      <c r="M41" s="50" t="n"/>
+      <c r="N41" s="50" t="n"/>
+      <c r="O41" s="50" t="n"/>
+      <c r="P41" s="50" t="n"/>
+      <c r="Q41" s="63">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="29">
+      <c r="A42" s="50" t="n"/>
+      <c r="B42" s="50" t="n"/>
+      <c r="C42" s="50" t="n"/>
+      <c r="D42" s="50" t="n"/>
+      <c r="E42" s="50" t="n"/>
+      <c r="F42" s="50" t="n"/>
+      <c r="G42" s="50" t="n"/>
+      <c r="H42" s="50" t="n"/>
+      <c r="I42" s="50" t="n"/>
+      <c r="J42" s="50" t="n"/>
+      <c r="K42" s="50" t="n"/>
+      <c r="L42" s="50" t="n"/>
+      <c r="M42" s="50" t="n"/>
+      <c r="N42" s="50" t="n"/>
+      <c r="O42" s="50" t="n"/>
+      <c r="P42" s="50" t="n"/>
+      <c r="Q42" s="63">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="29">
+      <c r="A43" s="50" t="n"/>
+      <c r="B43" s="50" t="n"/>
+      <c r="C43" s="50" t="n"/>
+      <c r="D43" s="50" t="n"/>
+      <c r="E43" s="50" t="n"/>
+      <c r="F43" s="50" t="n"/>
+      <c r="G43" s="50" t="n"/>
+      <c r="H43" s="50" t="n"/>
+      <c r="I43" s="50" t="n"/>
+      <c r="J43" s="50" t="n"/>
+      <c r="K43" s="50" t="n"/>
+      <c r="L43" s="50" t="n"/>
+      <c r="M43" s="50" t="n"/>
+      <c r="N43" s="50" t="n"/>
+      <c r="O43" s="50" t="n"/>
+      <c r="P43" s="50" t="n"/>
+      <c r="Q43" s="63">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="29">
+      <c r="A44" s="50" t="n"/>
+      <c r="B44" s="50" t="n"/>
+      <c r="C44" s="50" t="n"/>
+      <c r="D44" s="50" t="n"/>
+      <c r="E44" s="50" t="n"/>
+      <c r="F44" s="50" t="n"/>
+      <c r="G44" s="50" t="n"/>
+      <c r="H44" s="50" t="n"/>
+      <c r="I44" s="50" t="n"/>
+      <c r="J44" s="50" t="n"/>
+      <c r="K44" s="50" t="n"/>
+      <c r="L44" s="50" t="n"/>
+      <c r="M44" s="50" t="n"/>
+      <c r="N44" s="50" t="n"/>
+      <c r="O44" s="50" t="n"/>
+      <c r="P44" s="50" t="n"/>
+      <c r="Q44" s="63">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="Q45" s="29">
+      <c r="A45" s="50" t="n"/>
+      <c r="B45" s="50" t="n"/>
+      <c r="C45" s="50" t="n"/>
+      <c r="D45" s="50" t="n"/>
+      <c r="E45" s="50" t="n"/>
+      <c r="F45" s="50" t="n"/>
+      <c r="G45" s="50" t="n"/>
+      <c r="H45" s="50" t="n"/>
+      <c r="I45" s="50" t="n"/>
+      <c r="J45" s="50" t="n"/>
+      <c r="K45" s="50" t="n"/>
+      <c r="L45" s="50" t="n"/>
+      <c r="M45" s="50" t="n"/>
+      <c r="N45" s="50" t="n"/>
+      <c r="O45" s="50" t="n"/>
+      <c r="P45" s="50" t="n"/>
+      <c r="Q45" s="63">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="Q46" s="29">
+      <c r="A46" s="50" t="n"/>
+      <c r="B46" s="50" t="n"/>
+      <c r="C46" s="50" t="n"/>
+      <c r="D46" s="50" t="n"/>
+      <c r="E46" s="50" t="n"/>
+      <c r="F46" s="50" t="n"/>
+      <c r="G46" s="50" t="n"/>
+      <c r="H46" s="50" t="n"/>
+      <c r="I46" s="50" t="n"/>
+      <c r="J46" s="50" t="n"/>
+      <c r="K46" s="50" t="n"/>
+      <c r="L46" s="50" t="n"/>
+      <c r="M46" s="50" t="n"/>
+      <c r="N46" s="50" t="n"/>
+      <c r="O46" s="50" t="n"/>
+      <c r="P46" s="50" t="n"/>
+      <c r="Q46" s="63">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="Q47" s="29">
+      <c r="A47" s="50" t="n"/>
+      <c r="B47" s="50" t="n"/>
+      <c r="C47" s="50" t="n"/>
+      <c r="D47" s="50" t="n"/>
+      <c r="E47" s="50" t="n"/>
+      <c r="F47" s="50" t="n"/>
+      <c r="G47" s="50" t="n"/>
+      <c r="H47" s="50" t="n"/>
+      <c r="I47" s="50" t="n"/>
+      <c r="J47" s="50" t="n"/>
+      <c r="K47" s="50" t="n"/>
+      <c r="L47" s="50" t="n"/>
+      <c r="M47" s="50" t="n"/>
+      <c r="N47" s="50" t="n"/>
+      <c r="O47" s="50" t="n"/>
+      <c r="P47" s="50" t="n"/>
+      <c r="Q47" s="63">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="Q48" s="29">
+      <c r="A48" s="50" t="n"/>
+      <c r="B48" s="50" t="n"/>
+      <c r="C48" s="50" t="n"/>
+      <c r="D48" s="50" t="n"/>
+      <c r="E48" s="50" t="n"/>
+      <c r="F48" s="50" t="n"/>
+      <c r="G48" s="50" t="n"/>
+      <c r="H48" s="50" t="n"/>
+      <c r="I48" s="50" t="n"/>
+      <c r="J48" s="50" t="n"/>
+      <c r="K48" s="50" t="n"/>
+      <c r="L48" s="50" t="n"/>
+      <c r="M48" s="50" t="n"/>
+      <c r="N48" s="50" t="n"/>
+      <c r="O48" s="50" t="n"/>
+      <c r="P48" s="50" t="n"/>
+      <c r="Q48" s="63">
         <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="Q49" s="29">
+      <c r="A49" s="50" t="n"/>
+      <c r="B49" s="50" t="n"/>
+      <c r="C49" s="50" t="n"/>
+      <c r="D49" s="50" t="n"/>
+      <c r="E49" s="50" t="n"/>
+      <c r="F49" s="50" t="n"/>
+      <c r="G49" s="50" t="n"/>
+      <c r="H49" s="50" t="n"/>
+      <c r="I49" s="50" t="n"/>
+      <c r="J49" s="50" t="n"/>
+      <c r="K49" s="50" t="n"/>
+      <c r="L49" s="50" t="n"/>
+      <c r="M49" s="50" t="n"/>
+      <c r="N49" s="50" t="n"/>
+      <c r="O49" s="50" t="n"/>
+      <c r="P49" s="50" t="n"/>
+      <c r="Q49" s="63">
         <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="Q50" s="29">
+      <c r="A50" s="50" t="n"/>
+      <c r="B50" s="50" t="n"/>
+      <c r="C50" s="50" t="n"/>
+      <c r="D50" s="50" t="n"/>
+      <c r="E50" s="50" t="n"/>
+      <c r="F50" s="50" t="n"/>
+      <c r="G50" s="50" t="n"/>
+      <c r="H50" s="50" t="n"/>
+      <c r="I50" s="50" t="n"/>
+      <c r="J50" s="50" t="n"/>
+      <c r="K50" s="50" t="n"/>
+      <c r="L50" s="50" t="n"/>
+      <c r="M50" s="50" t="n"/>
+      <c r="N50" s="50" t="n"/>
+      <c r="O50" s="50" t="n"/>
+      <c r="P50" s="50" t="n"/>
+      <c r="Q50" s="63">
         <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="Q51" s="29">
+      <c r="A51" s="50" t="n"/>
+      <c r="B51" s="50" t="n"/>
+      <c r="C51" s="50" t="n"/>
+      <c r="D51" s="50" t="n"/>
+      <c r="E51" s="50" t="n"/>
+      <c r="F51" s="50" t="n"/>
+      <c r="G51" s="50" t="n"/>
+      <c r="H51" s="50" t="n"/>
+      <c r="I51" s="50" t="n"/>
+      <c r="J51" s="50" t="n"/>
+      <c r="K51" s="50" t="n"/>
+      <c r="L51" s="50" t="n"/>
+      <c r="M51" s="50" t="n"/>
+      <c r="N51" s="50" t="n"/>
+      <c r="O51" s="50" t="n"/>
+      <c r="P51" s="50" t="n"/>
+      <c r="Q51" s="63">
         <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="Q52" s="29">
+      <c r="A52" s="50" t="n"/>
+      <c r="B52" s="50" t="n"/>
+      <c r="C52" s="50" t="n"/>
+      <c r="D52" s="50" t="n"/>
+      <c r="E52" s="50" t="n"/>
+      <c r="F52" s="50" t="n"/>
+      <c r="G52" s="50" t="n"/>
+      <c r="H52" s="50" t="n"/>
+      <c r="I52" s="50" t="n"/>
+      <c r="J52" s="50" t="n"/>
+      <c r="K52" s="50" t="n"/>
+      <c r="L52" s="50" t="n"/>
+      <c r="M52" s="50" t="n"/>
+      <c r="N52" s="50" t="n"/>
+      <c r="O52" s="50" t="n"/>
+      <c r="P52" s="50" t="n"/>
+      <c r="Q52" s="63">
         <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
         <v/>
       </c>
@@ -1843,129 +2648,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="64" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+      <c r="D1" s="50" t="n"/>
+      <c r="E1" s="50" t="n"/>
+      <c r="F1" s="50" t="n"/>
+      <c r="G1" s="50" t="n"/>
+      <c r="H1" s="50" t="n"/>
+      <c r="I1" s="50" t="n"/>
+      <c r="J1" s="50" t="n"/>
+      <c r="K1" s="50" t="n"/>
+      <c r="L1" s="50" t="n"/>
+      <c r="M1" s="50" t="n"/>
+      <c r="N1" s="50" t="n"/>
+      <c r="O1" s="50" t="n"/>
+      <c r="P1" s="50" t="n"/>
+      <c r="Q1" s="50" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="B2" s="44" t="inlineStr">
+      <c r="A2" s="50" t="n"/>
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="C2" s="50" t="n"/>
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="50" t="n"/>
+      <c r="F2" s="50" t="n"/>
+      <c r="G2" s="50" t="n"/>
+      <c r="H2" s="50" t="n"/>
+      <c r="I2" s="50" t="n"/>
+      <c r="J2" s="50" t="n"/>
+      <c r="K2" s="50" t="n"/>
+      <c r="L2" s="50" t="n"/>
+      <c r="M2" s="50" t="n"/>
+      <c r="N2" s="50" t="n"/>
+      <c r="O2" s="50" t="n"/>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="50" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="50" t="n"/>
+      <c r="B3" s="50" t="n"/>
+      <c r="C3" s="50" t="n"/>
+      <c r="D3" s="50" t="n"/>
+      <c r="E3" s="50" t="n"/>
+      <c r="F3" s="50" t="n"/>
+      <c r="G3" s="50" t="n"/>
+      <c r="H3" s="50" t="n"/>
+      <c r="I3" s="50" t="n"/>
+      <c r="J3" s="50" t="n"/>
+      <c r="K3" s="50" t="n"/>
+      <c r="L3" s="50" t="n"/>
+      <c r="M3" s="50" t="n"/>
+      <c r="N3" s="50" t="n"/>
+      <c r="O3" s="50" t="n"/>
+      <c r="P3" s="50" t="n"/>
+      <c r="Q3" s="50" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="48" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="48" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="48" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="48" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="48" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="48" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="48" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="48" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="48" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="48" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="48" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="48" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>FL-009</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>تزریق دستی</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="54" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="52" t="inlineStr">
         <is>
           <t>دیباگر وصل</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="52" t="inlineStr">
         <is>
           <t>گام ۱: دیباگر را وصل کن و مسیر تست func__Fault_Set/Clear را آماده کن.
 گام ۲: چند بیت دلخواه را یک بار Set و یک بار Clear کن.
@@ -1973,233 +2828,537 @@
 گام ۴: ماسک باید دقیقاً همان بیت‌هایی باشد که ست کردی و Any با بودن/نبودن بیت درست جواب دهد.</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="54" t="inlineStr">
         <is>
           <t>بیت‌های دلخواه</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="52" t="inlineStr">
         <is>
           <t>ماسک دقیقاً Set/Clear می‌شود</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="52" t="inlineStr">
         <is>
           <t>Get/Any مطابق</t>
         </is>
       </c>
-      <c r="K5" s="17" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="K5" s="52" t="n"/>
+      <c r="L5" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="M5" s="52" t="n"/>
+      <c r="N5" s="52" t="n"/>
+      <c r="O5" s="54" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="19" t="n"/>
-      <c r="Q5" s="21" t="inlineStr">
+      <c r="P5" s="54" t="n"/>
+      <c r="Q5" s="56" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>FA-020</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="52" t="inlineStr">
         <is>
           <t>snapshot zeroing</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="52" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="52" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
 گام ۲: آن را 2 ثانیه به Fault_Evaluate بده.
 گام ۳: ماسک خطا را بخوان: هیچ Set یا Clear کاذبی نباید اتفاق افتاده باشد؛ تابع فقط valid را چک می‌کند و بر اساس فیلدهای صفر تصمیم نمی‌گیرد.</t>
         </is>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="54" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="54" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="52" t="inlineStr">
         <is>
           <t>بدون Set/Clear کاذب؛ فقط valid چک شود؛ هر 9 فیلد صفر شده باشد</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="52" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="52" t="inlineStr">
         <is>
           <t>بدون fault کاذب</t>
         </is>
       </c>
-      <c r="K6" s="17" t="n"/>
-      <c r="L6" s="28" t="inlineStr">
+      <c r="K6" s="52" t="n"/>
+      <c r="L6" s="66" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="17" t="n"/>
-      <c r="O6" s="19" t="inlineStr">
+      <c r="M6" s="52" t="n"/>
+      <c r="N6" s="52" t="n"/>
+      <c r="O6" s="54" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P6" s="19" t="n"/>
-      <c r="Q6" s="21">
+      <c r="P6" s="54" t="n"/>
+      <c r="Q6" s="56">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="Q7" s="29">
+      <c r="A7" s="50" t="n"/>
+      <c r="B7" s="50" t="n"/>
+      <c r="C7" s="50" t="n"/>
+      <c r="D7" s="50" t="n"/>
+      <c r="E7" s="50" t="n"/>
+      <c r="F7" s="50" t="n"/>
+      <c r="G7" s="50" t="n"/>
+      <c r="H7" s="50" t="n"/>
+      <c r="I7" s="50" t="n"/>
+      <c r="J7" s="50" t="n"/>
+      <c r="K7" s="50" t="n"/>
+      <c r="L7" s="50" t="n"/>
+      <c r="M7" s="50" t="n"/>
+      <c r="N7" s="50" t="n"/>
+      <c r="O7" s="50" t="n"/>
+      <c r="P7" s="50" t="n"/>
+      <c r="Q7" s="63">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="Q8" s="29">
+      <c r="A8" s="50" t="n"/>
+      <c r="B8" s="50" t="n"/>
+      <c r="C8" s="50" t="n"/>
+      <c r="D8" s="50" t="n"/>
+      <c r="E8" s="50" t="n"/>
+      <c r="F8" s="50" t="n"/>
+      <c r="G8" s="50" t="n"/>
+      <c r="H8" s="50" t="n"/>
+      <c r="I8" s="50" t="n"/>
+      <c r="J8" s="50" t="n"/>
+      <c r="K8" s="50" t="n"/>
+      <c r="L8" s="50" t="n"/>
+      <c r="M8" s="50" t="n"/>
+      <c r="N8" s="50" t="n"/>
+      <c r="O8" s="50" t="n"/>
+      <c r="P8" s="50" t="n"/>
+      <c r="Q8" s="63">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="29">
+      <c r="A9" s="50" t="n"/>
+      <c r="B9" s="50" t="n"/>
+      <c r="C9" s="50" t="n"/>
+      <c r="D9" s="50" t="n"/>
+      <c r="E9" s="50" t="n"/>
+      <c r="F9" s="50" t="n"/>
+      <c r="G9" s="50" t="n"/>
+      <c r="H9" s="50" t="n"/>
+      <c r="I9" s="50" t="n"/>
+      <c r="J9" s="50" t="n"/>
+      <c r="K9" s="50" t="n"/>
+      <c r="L9" s="50" t="n"/>
+      <c r="M9" s="50" t="n"/>
+      <c r="N9" s="50" t="n"/>
+      <c r="O9" s="50" t="n"/>
+      <c r="P9" s="50" t="n"/>
+      <c r="Q9" s="63">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="29">
+      <c r="A10" s="50" t="n"/>
+      <c r="B10" s="50" t="n"/>
+      <c r="C10" s="50" t="n"/>
+      <c r="D10" s="50" t="n"/>
+      <c r="E10" s="50" t="n"/>
+      <c r="F10" s="50" t="n"/>
+      <c r="G10" s="50" t="n"/>
+      <c r="H10" s="50" t="n"/>
+      <c r="I10" s="50" t="n"/>
+      <c r="J10" s="50" t="n"/>
+      <c r="K10" s="50" t="n"/>
+      <c r="L10" s="50" t="n"/>
+      <c r="M10" s="50" t="n"/>
+      <c r="N10" s="50" t="n"/>
+      <c r="O10" s="50" t="n"/>
+      <c r="P10" s="50" t="n"/>
+      <c r="Q10" s="63">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="29">
+      <c r="A11" s="50" t="n"/>
+      <c r="B11" s="50" t="n"/>
+      <c r="C11" s="50" t="n"/>
+      <c r="D11" s="50" t="n"/>
+      <c r="E11" s="50" t="n"/>
+      <c r="F11" s="50" t="n"/>
+      <c r="G11" s="50" t="n"/>
+      <c r="H11" s="50" t="n"/>
+      <c r="I11" s="50" t="n"/>
+      <c r="J11" s="50" t="n"/>
+      <c r="K11" s="50" t="n"/>
+      <c r="L11" s="50" t="n"/>
+      <c r="M11" s="50" t="n"/>
+      <c r="N11" s="50" t="n"/>
+      <c r="O11" s="50" t="n"/>
+      <c r="P11" s="50" t="n"/>
+      <c r="Q11" s="63">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="29">
+      <c r="A12" s="50" t="n"/>
+      <c r="B12" s="50" t="n"/>
+      <c r="C12" s="50" t="n"/>
+      <c r="D12" s="50" t="n"/>
+      <c r="E12" s="50" t="n"/>
+      <c r="F12" s="50" t="n"/>
+      <c r="G12" s="50" t="n"/>
+      <c r="H12" s="50" t="n"/>
+      <c r="I12" s="50" t="n"/>
+      <c r="J12" s="50" t="n"/>
+      <c r="K12" s="50" t="n"/>
+      <c r="L12" s="50" t="n"/>
+      <c r="M12" s="50" t="n"/>
+      <c r="N12" s="50" t="n"/>
+      <c r="O12" s="50" t="n"/>
+      <c r="P12" s="50" t="n"/>
+      <c r="Q12" s="63">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="29">
+      <c r="A13" s="50" t="n"/>
+      <c r="B13" s="50" t="n"/>
+      <c r="C13" s="50" t="n"/>
+      <c r="D13" s="50" t="n"/>
+      <c r="E13" s="50" t="n"/>
+      <c r="F13" s="50" t="n"/>
+      <c r="G13" s="50" t="n"/>
+      <c r="H13" s="50" t="n"/>
+      <c r="I13" s="50" t="n"/>
+      <c r="J13" s="50" t="n"/>
+      <c r="K13" s="50" t="n"/>
+      <c r="L13" s="50" t="n"/>
+      <c r="M13" s="50" t="n"/>
+      <c r="N13" s="50" t="n"/>
+      <c r="O13" s="50" t="n"/>
+      <c r="P13" s="50" t="n"/>
+      <c r="Q13" s="63">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="29">
+      <c r="A14" s="50" t="n"/>
+      <c r="B14" s="50" t="n"/>
+      <c r="C14" s="50" t="n"/>
+      <c r="D14" s="50" t="n"/>
+      <c r="E14" s="50" t="n"/>
+      <c r="F14" s="50" t="n"/>
+      <c r="G14" s="50" t="n"/>
+      <c r="H14" s="50" t="n"/>
+      <c r="I14" s="50" t="n"/>
+      <c r="J14" s="50" t="n"/>
+      <c r="K14" s="50" t="n"/>
+      <c r="L14" s="50" t="n"/>
+      <c r="M14" s="50" t="n"/>
+      <c r="N14" s="50" t="n"/>
+      <c r="O14" s="50" t="n"/>
+      <c r="P14" s="50" t="n"/>
+      <c r="Q14" s="63">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="29">
+      <c r="A15" s="50" t="n"/>
+      <c r="B15" s="50" t="n"/>
+      <c r="C15" s="50" t="n"/>
+      <c r="D15" s="50" t="n"/>
+      <c r="E15" s="50" t="n"/>
+      <c r="F15" s="50" t="n"/>
+      <c r="G15" s="50" t="n"/>
+      <c r="H15" s="50" t="n"/>
+      <c r="I15" s="50" t="n"/>
+      <c r="J15" s="50" t="n"/>
+      <c r="K15" s="50" t="n"/>
+      <c r="L15" s="50" t="n"/>
+      <c r="M15" s="50" t="n"/>
+      <c r="N15" s="50" t="n"/>
+      <c r="O15" s="50" t="n"/>
+      <c r="P15" s="50" t="n"/>
+      <c r="Q15" s="63">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="29">
+      <c r="A16" s="50" t="n"/>
+      <c r="B16" s="50" t="n"/>
+      <c r="C16" s="50" t="n"/>
+      <c r="D16" s="50" t="n"/>
+      <c r="E16" s="50" t="n"/>
+      <c r="F16" s="50" t="n"/>
+      <c r="G16" s="50" t="n"/>
+      <c r="H16" s="50" t="n"/>
+      <c r="I16" s="50" t="n"/>
+      <c r="J16" s="50" t="n"/>
+      <c r="K16" s="50" t="n"/>
+      <c r="L16" s="50" t="n"/>
+      <c r="M16" s="50" t="n"/>
+      <c r="N16" s="50" t="n"/>
+      <c r="O16" s="50" t="n"/>
+      <c r="P16" s="50" t="n"/>
+      <c r="Q16" s="63">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="29">
+      <c r="A17" s="50" t="n"/>
+      <c r="B17" s="50" t="n"/>
+      <c r="C17" s="50" t="n"/>
+      <c r="D17" s="50" t="n"/>
+      <c r="E17" s="50" t="n"/>
+      <c r="F17" s="50" t="n"/>
+      <c r="G17" s="50" t="n"/>
+      <c r="H17" s="50" t="n"/>
+      <c r="I17" s="50" t="n"/>
+      <c r="J17" s="50" t="n"/>
+      <c r="K17" s="50" t="n"/>
+      <c r="L17" s="50" t="n"/>
+      <c r="M17" s="50" t="n"/>
+      <c r="N17" s="50" t="n"/>
+      <c r="O17" s="50" t="n"/>
+      <c r="P17" s="50" t="n"/>
+      <c r="Q17" s="63">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="29">
+      <c r="A18" s="50" t="n"/>
+      <c r="B18" s="50" t="n"/>
+      <c r="C18" s="50" t="n"/>
+      <c r="D18" s="50" t="n"/>
+      <c r="E18" s="50" t="n"/>
+      <c r="F18" s="50" t="n"/>
+      <c r="G18" s="50" t="n"/>
+      <c r="H18" s="50" t="n"/>
+      <c r="I18" s="50" t="n"/>
+      <c r="J18" s="50" t="n"/>
+      <c r="K18" s="50" t="n"/>
+      <c r="L18" s="50" t="n"/>
+      <c r="M18" s="50" t="n"/>
+      <c r="N18" s="50" t="n"/>
+      <c r="O18" s="50" t="n"/>
+      <c r="P18" s="50" t="n"/>
+      <c r="Q18" s="63">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="29">
+      <c r="A19" s="50" t="n"/>
+      <c r="B19" s="50" t="n"/>
+      <c r="C19" s="50" t="n"/>
+      <c r="D19" s="50" t="n"/>
+      <c r="E19" s="50" t="n"/>
+      <c r="F19" s="50" t="n"/>
+      <c r="G19" s="50" t="n"/>
+      <c r="H19" s="50" t="n"/>
+      <c r="I19" s="50" t="n"/>
+      <c r="J19" s="50" t="n"/>
+      <c r="K19" s="50" t="n"/>
+      <c r="L19" s="50" t="n"/>
+      <c r="M19" s="50" t="n"/>
+      <c r="N19" s="50" t="n"/>
+      <c r="O19" s="50" t="n"/>
+      <c r="P19" s="50" t="n"/>
+      <c r="Q19" s="63">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="29">
+      <c r="A20" s="50" t="n"/>
+      <c r="B20" s="50" t="n"/>
+      <c r="C20" s="50" t="n"/>
+      <c r="D20" s="50" t="n"/>
+      <c r="E20" s="50" t="n"/>
+      <c r="F20" s="50" t="n"/>
+      <c r="G20" s="50" t="n"/>
+      <c r="H20" s="50" t="n"/>
+      <c r="I20" s="50" t="n"/>
+      <c r="J20" s="50" t="n"/>
+      <c r="K20" s="50" t="n"/>
+      <c r="L20" s="50" t="n"/>
+      <c r="M20" s="50" t="n"/>
+      <c r="N20" s="50" t="n"/>
+      <c r="O20" s="50" t="n"/>
+      <c r="P20" s="50" t="n"/>
+      <c r="Q20" s="63">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="29">
+      <c r="A21" s="50" t="n"/>
+      <c r="B21" s="50" t="n"/>
+      <c r="C21" s="50" t="n"/>
+      <c r="D21" s="50" t="n"/>
+      <c r="E21" s="50" t="n"/>
+      <c r="F21" s="50" t="n"/>
+      <c r="G21" s="50" t="n"/>
+      <c r="H21" s="50" t="n"/>
+      <c r="I21" s="50" t="n"/>
+      <c r="J21" s="50" t="n"/>
+      <c r="K21" s="50" t="n"/>
+      <c r="L21" s="50" t="n"/>
+      <c r="M21" s="50" t="n"/>
+      <c r="N21" s="50" t="n"/>
+      <c r="O21" s="50" t="n"/>
+      <c r="P21" s="50" t="n"/>
+      <c r="Q21" s="63">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="29">
+      <c r="A22" s="50" t="n"/>
+      <c r="B22" s="50" t="n"/>
+      <c r="C22" s="50" t="n"/>
+      <c r="D22" s="50" t="n"/>
+      <c r="E22" s="50" t="n"/>
+      <c r="F22" s="50" t="n"/>
+      <c r="G22" s="50" t="n"/>
+      <c r="H22" s="50" t="n"/>
+      <c r="I22" s="50" t="n"/>
+      <c r="J22" s="50" t="n"/>
+      <c r="K22" s="50" t="n"/>
+      <c r="L22" s="50" t="n"/>
+      <c r="M22" s="50" t="n"/>
+      <c r="N22" s="50" t="n"/>
+      <c r="O22" s="50" t="n"/>
+      <c r="P22" s="50" t="n"/>
+      <c r="Q22" s="63">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="29">
+      <c r="A23" s="50" t="n"/>
+      <c r="B23" s="50" t="n"/>
+      <c r="C23" s="50" t="n"/>
+      <c r="D23" s="50" t="n"/>
+      <c r="E23" s="50" t="n"/>
+      <c r="F23" s="50" t="n"/>
+      <c r="G23" s="50" t="n"/>
+      <c r="H23" s="50" t="n"/>
+      <c r="I23" s="50" t="n"/>
+      <c r="J23" s="50" t="n"/>
+      <c r="K23" s="50" t="n"/>
+      <c r="L23" s="50" t="n"/>
+      <c r="M23" s="50" t="n"/>
+      <c r="N23" s="50" t="n"/>
+      <c r="O23" s="50" t="n"/>
+      <c r="P23" s="50" t="n"/>
+      <c r="Q23" s="63">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="29">
+      <c r="A24" s="50" t="n"/>
+      <c r="B24" s="50" t="n"/>
+      <c r="C24" s="50" t="n"/>
+      <c r="D24" s="50" t="n"/>
+      <c r="E24" s="50" t="n"/>
+      <c r="F24" s="50" t="n"/>
+      <c r="G24" s="50" t="n"/>
+      <c r="H24" s="50" t="n"/>
+      <c r="I24" s="50" t="n"/>
+      <c r="J24" s="50" t="n"/>
+      <c r="K24" s="50" t="n"/>
+      <c r="L24" s="50" t="n"/>
+      <c r="M24" s="50" t="n"/>
+      <c r="N24" s="50" t="n"/>
+      <c r="O24" s="50" t="n"/>
+      <c r="P24" s="50" t="n"/>
+      <c r="Q24" s="63">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="29">
+      <c r="A25" s="50" t="n"/>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+      <c r="E25" s="50" t="n"/>
+      <c r="F25" s="50" t="n"/>
+      <c r="G25" s="50" t="n"/>
+      <c r="H25" s="50" t="n"/>
+      <c r="I25" s="50" t="n"/>
+      <c r="J25" s="50" t="n"/>
+      <c r="K25" s="50" t="n"/>
+      <c r="L25" s="50" t="n"/>
+      <c r="M25" s="50" t="n"/>
+      <c r="N25" s="50" t="n"/>
+      <c r="O25" s="50" t="n"/>
+      <c r="P25" s="50" t="n"/>
+      <c r="Q25" s="63">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
@@ -2234,174 +3393,180 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Fault</t>
         </is>
       </c>
-      <c r="B1" s="40" t="n"/>
-      <c r="C1" s="40" t="n"/>
-      <c r="D1" s="40" t="n"/>
-      <c r="E1" s="41" t="n"/>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="67" t="n"/>
+      <c r="C1" s="67" t="n"/>
+      <c r="D1" s="67" t="n"/>
+      <c r="E1" s="68" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="50" t="n"/>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="50" t="n"/>
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="50" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="69" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="69" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="69" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="69" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="69" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="70" t="inlineStr">
         <is>
           <t>قاعدهٔ پمپ</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="70" t="inlineStr">
         <is>
           <t>&gt;14.8V حین BULK/ABSORB، 150ms</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
+      <c r="C4" s="70" t="inlineStr">
         <is>
           <t>قفل FAULT_CHARGER_BAT_LOST</t>
         </is>
       </c>
-      <c r="D4" s="31" t="inlineStr">
+      <c r="D4" s="70" t="inlineStr">
         <is>
           <t>FAULT_BAT_DISCONNECT_MV / FAULT_BAT_DISCONNECT_DEBOUNCE_MS</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="70" t="inlineStr">
         <is>
           <t>فقط کانال فعال</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="70" t="inlineStr">
         <is>
           <t>قاعدهٔ غیبت</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="70" t="inlineStr">
         <is>
           <t>هر نیم &lt;6V با ورودی سالم، 1s</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C5" s="70" t="inlineStr">
         <is>
           <t>قفل FAULT_CHARGER_BAT_LOST</t>
         </is>
       </c>
-      <c r="D5" s="31" t="inlineStr">
+      <c r="D5" s="70" t="inlineStr">
         <is>
           <t>FAULT_BAT_ABSENT_MV / FAULT_BAT_ABSENT_DEBOUNCE_MS</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E5" s="70" t="inlineStr">
         <is>
           <t>هرکدام، نه هر دو</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="70" t="inlineStr">
         <is>
           <t>بازیابی</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="70" t="inlineStr">
         <is>
           <t>هر دو نیم ≥7V بدون پمپ، 1s</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="70" t="inlineStr">
         <is>
           <t>پاک شدن بیت</t>
         </is>
       </c>
-      <c r="D6" s="31" t="inlineStr">
+      <c r="D6" s="70" t="inlineStr">
         <is>
           <t>FAULT_BATTERY_BACK_MV / FAULT_BAT_RECOVER_MS</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr">
+      <c r="E6" s="70" t="inlineStr">
         <is>
           <t>هیسترزیس 1V</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="70" t="inlineStr">
         <is>
           <t>فریز مود دستی</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="70" t="inlineStr">
         <is>
           <t>IsManualTestModeActive</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="70" t="inlineStr">
         <is>
           <t>بدون Set/Clear، تمپ صفر</t>
         </is>
       </c>
-      <c r="D7" s="42" t="inlineStr">
+      <c r="D7" s="71" t="inlineStr">
         <is>
           <t>fault.c (v1.2)</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="70" t="inlineStr">
         <is>
           <t>پمپ عمدی عادی‌سازی شد</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="70" t="inlineStr">
         <is>
           <t>بیت‌های ماسک</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="71" t="inlineStr">
         <is>
           <t>0..6 در app_types.h</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C8" s="70" t="inlineStr">
         <is>
           <t>FAULT_CHARGER_BAT_LOST (بیت ۶)</t>
         </is>
       </c>
-      <c r="D8" s="31" t="inlineStr">
+      <c r="D8" s="70" t="inlineStr">
         <is>
           <t>FAULT_*</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr">
+      <c r="E8" s="70" t="inlineStr">
         <is>
           <t>0x40 در تله‌متری</t>
         </is>
@@ -2445,93 +3610,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="46" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Fault</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+      <c r="D1" s="50" t="n"/>
+      <c r="E1" s="50" t="n"/>
+      <c r="F1" s="50" t="n"/>
+      <c r="G1" s="50" t="n"/>
+      <c r="H1" s="50" t="n"/>
+      <c r="I1" s="50" t="n"/>
+      <c r="J1" s="50" t="n"/>
+      <c r="K1" s="50" t="n"/>
+      <c r="L1" s="50" t="n"/>
+      <c r="M1" s="50" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="40" t="n"/>
-      <c r="C2" s="40" t="n"/>
-      <c r="D2" s="40" t="n"/>
-      <c r="E2" s="40" t="n"/>
-      <c r="F2" s="40" t="n"/>
-      <c r="G2" s="40" t="n"/>
-      <c r="H2" s="40" t="n"/>
-      <c r="I2" s="40" t="n"/>
-      <c r="J2" s="40" t="n"/>
-      <c r="K2" s="40" t="n"/>
-      <c r="L2" s="40" t="n"/>
-      <c r="M2" s="41" t="n"/>
+      <c r="B2" s="67" t="n"/>
+      <c r="C2" s="67" t="n"/>
+      <c r="D2" s="67" t="n"/>
+      <c r="E2" s="67" t="n"/>
+      <c r="F2" s="67" t="n"/>
+      <c r="G2" s="67" t="n"/>
+      <c r="H2" s="67" t="n"/>
+      <c r="I2" s="67" t="n"/>
+      <c r="J2" s="67" t="n"/>
+      <c r="K2" s="67" t="n"/>
+      <c r="L2" s="67" t="n"/>
+      <c r="M2" s="68" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="69" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="69" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="69" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="69" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="69" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="69" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="30" t="inlineStr">
+      <c r="G3" s="69" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="30" t="inlineStr">
+      <c r="H3" s="69" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="30" t="inlineStr">
+      <c r="I3" s="69" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="30" t="inlineStr">
+      <c r="J3" s="69" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="30" t="inlineStr">
+      <c r="K3" s="69" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="30" t="inlineStr">
+      <c r="L3" s="69" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="30" t="inlineStr">
+      <c r="M3" s="69" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -2562,209 +3739,233 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="46" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Fault</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="50" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="47" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
+      <c r="B3" s="50" t="n"/>
+      <c r="C3" s="50" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
+      <c r="C4" s="50" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>Fault — تشخیص متمرکز قطع باتری</t>
         </is>
       </c>
+      <c r="C5" s="50" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>2026-09-23 (1.0 — شامل فریز v1.2)</t>
         </is>
       </c>
+      <c r="C6" s="50" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
+      <c r="C7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
+      <c r="C8" s="50" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>پنل ESP + مولتی‌متر + سیم‌کشی تست</t>
         </is>
       </c>
-    </row>
-    <row r="10"/>
+      <c r="C9" s="50" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="50" t="n"/>
+      <c r="B10" s="50" t="n"/>
+      <c r="C10" s="50" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
+      <c r="B11" s="50" t="n"/>
+      <c r="C11" s="50" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="69" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr">
+      <c r="C12" s="69" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="73" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="33" t="n">
+      <c r="B13" s="73" t="n">
         <v>10</v>
       </c>
-      <c r="C13" s="33" t="inlineStr">
+      <c r="C13" s="73" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="73" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="73">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="33" t="inlineStr">
+      <c r="C14" s="73" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="73" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="73">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="33" t="inlineStr">
+      <c r="C15" s="73" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="73" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="33">
+      <c r="B16" s="73">
         <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C16" s="73" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="73" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="73">
         <f>IF(10=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/10)</f>
         <v/>
       </c>
-      <c r="C17" s="33" t="inlineStr">
+      <c r="C17" s="73" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="50" t="n"/>
+      <c r="B18" s="50" t="n"/>
+      <c r="C18" s="50" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
       </c>
+      <c r="B19" s="50" t="n"/>
+      <c r="C19" s="50" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2791,117 +3992,136 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="75" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
+      <c r="B2" s="50" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="75" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
+      <c r="B3" s="50" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="75" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
+      <c r="B4" s="50" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="75" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
+      <c r="B5" s="50" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="75" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
+      <c r="B6" s="50" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="50" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
+      <c r="B7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="74" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
+      <c r="B8" s="50" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="35" t="inlineStr">
+      <c r="A9" s="50" t="n"/>
+      <c r="B9" s="75" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="35" t="inlineStr">
+      <c r="A10" s="50" t="n"/>
+      <c r="B10" s="75" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="A11" s="50" t="n"/>
+      <c r="B11" s="75" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="12">
+      <c r="A12" s="50" t="n"/>
+      <c r="B12" s="50" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="74" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
+      <c r="B13" s="50" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="75" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
+      <c r="B14" s="50" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="75" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
+      <c r="B15" s="50" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="75" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
+      <c r="B16" s="50" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="75" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
+      <c r="B17" s="50" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2923,60 +4143,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول خطا (Fault)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="50" t="n"/>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="50" t="n"/>
+    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="38" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Fault_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C3" s="50" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C4" s="50" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
+      <c r="C5" s="50" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
+      <c r="C6" s="50" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3021,181 +4251,229 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>برنامهٔ تست آزمایشگاهی — ماژول Fault</t>
         </is>
       </c>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+      <c r="D1" s="50" t="n"/>
+      <c r="E1" s="50" t="n"/>
+      <c r="F1" s="50" t="n"/>
+      <c r="G1" s="50" t="n"/>
+      <c r="H1" s="50" t="n"/>
+      <c r="I1" s="50" t="n"/>
+      <c r="J1" s="50" t="n"/>
+      <c r="K1" s="50" t="n"/>
+      <c r="L1" s="50" t="n"/>
+      <c r="M1" s="50" t="n"/>
+      <c r="N1" s="50" t="n"/>
+      <c r="O1" s="50" t="n"/>
+      <c r="P1" s="50" t="n"/>
+      <c r="Q1" s="50" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="50" t="n"/>
+      <c r="C2" s="50" t="n"/>
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="50" t="n"/>
+      <c r="F2" s="50" t="n"/>
+      <c r="G2" s="50" t="n"/>
+      <c r="H2" s="50" t="n"/>
+      <c r="I2" s="50" t="n"/>
+      <c r="J2" s="50" t="n"/>
+      <c r="K2" s="50" t="n"/>
+      <c r="L2" s="50" t="n"/>
+      <c r="M2" s="50" t="n"/>
+      <c r="N2" s="50" t="n"/>
+      <c r="O2" s="50" t="n"/>
+      <c r="P2" s="50" t="n"/>
+      <c r="Q2" s="50" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="47" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="50" t="n"/>
+      <c r="C3" s="50" t="n"/>
+      <c r="D3" s="50" t="n"/>
+      <c r="E3" s="50" t="n"/>
+      <c r="F3" s="50" t="n"/>
+      <c r="G3" s="50" t="n"/>
+      <c r="H3" s="50" t="n"/>
+      <c r="I3" s="50" t="n"/>
+      <c r="J3" s="50" t="n"/>
+      <c r="K3" s="50" t="n"/>
+      <c r="L3" s="50" t="n"/>
+      <c r="M3" s="50" t="n"/>
+      <c r="N3" s="50" t="n"/>
+      <c r="O3" s="50" t="n"/>
+      <c r="P3" s="50" t="n"/>
+      <c r="Q3" s="50" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="48" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="48" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="48" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="48" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="48" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="48" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="48" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="48" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="48" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="48" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="48" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="48" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>FL-006</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t>snapshot نامعتبر</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="58" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>ADC در warm-up یا نامعتبر</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="57" t="inlineStr">
         <is>
           <t>گام ۱: ADC را در حالت warm-up نگه دار یا کاری کن snapshot نامعتبر باشد.
 گام ۲: رفتار ست/پاک شدن بیت‌ها را در همین مدت نگاه کن.
 گام ۳: تا وقتی snapshot معتبر نیست هیچ Set و Clear نباید اتفاق بیفتد و وضعیت قبلی ماسک باید حفظ شود.</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="24" t="inlineStr">
+      <c r="G5" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="57" t="inlineStr">
         <is>
           <t>هیچ Set/Clear؛ وضعیت قبلی حفظ</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J5" s="57" t="inlineStr">
         <is>
           <t>بدون تغییر ماسک</t>
         </is>
       </c>
-      <c r="K5" s="22" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="K5" s="57" t="n"/>
+      <c r="L5" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="22" t="n"/>
-      <c r="N5" s="22" t="n"/>
-      <c r="O5" s="24" t="inlineStr">
+      <c r="M5" s="57" t="n"/>
+      <c r="N5" s="57" t="n"/>
+      <c r="O5" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="24" t="n"/>
-      <c r="Q5" s="25">
+      <c r="P5" s="59" t="n"/>
+      <c r="Q5" s="60">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -186,6 +186,10 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -230,7 +234,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -310,11 +314,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -501,6 +506,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -867,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -925,6 +933,14 @@
       <c r="A9" s="47" t="inlineStr">
         <is>
           <t>هشدار: تست قطع باتری حین شارژ با جریان محدود و زیر نظارت؛ ولتاژ گره پمپ‌شده می‌تواند بالای 15V برود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="76" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
         </is>
       </c>
     </row>
@@ -979,22 +995,6 @@
           <t>برنامهٔ تست عملی — ماژول Fault</t>
         </is>
       </c>
-      <c r="B1" s="50" t="n"/>
-      <c r="C1" s="50" t="n"/>
-      <c r="D1" s="50" t="n"/>
-      <c r="E1" s="50" t="n"/>
-      <c r="F1" s="50" t="n"/>
-      <c r="G1" s="50" t="n"/>
-      <c r="H1" s="50" t="n"/>
-      <c r="I1" s="50" t="n"/>
-      <c r="J1" s="50" t="n"/>
-      <c r="K1" s="50" t="n"/>
-      <c r="L1" s="50" t="n"/>
-      <c r="M1" s="50" t="n"/>
-      <c r="N1" s="50" t="n"/>
-      <c r="O1" s="50" t="n"/>
-      <c r="P1" s="50" t="n"/>
-      <c r="Q1" s="50" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="47" t="inlineStr">
@@ -1002,22 +1002,6 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
-      <c r="B2" s="50" t="n"/>
-      <c r="C2" s="50" t="n"/>
-      <c r="D2" s="50" t="n"/>
-      <c r="E2" s="50" t="n"/>
-      <c r="F2" s="50" t="n"/>
-      <c r="G2" s="50" t="n"/>
-      <c r="H2" s="50" t="n"/>
-      <c r="I2" s="50" t="n"/>
-      <c r="J2" s="50" t="n"/>
-      <c r="K2" s="50" t="n"/>
-      <c r="L2" s="50" t="n"/>
-      <c r="M2" s="50" t="n"/>
-      <c r="N2" s="50" t="n"/>
-      <c r="O2" s="50" t="n"/>
-      <c r="P2" s="50" t="n"/>
-      <c r="Q2" s="50" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="47" t="inlineStr">
@@ -1025,22 +1009,6 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
-      <c r="B3" s="50" t="n"/>
-      <c r="C3" s="50" t="n"/>
-      <c r="D3" s="50" t="n"/>
-      <c r="E3" s="50" t="n"/>
-      <c r="F3" s="50" t="n"/>
-      <c r="G3" s="50" t="n"/>
-      <c r="H3" s="50" t="n"/>
-      <c r="I3" s="50" t="n"/>
-      <c r="J3" s="50" t="n"/>
-      <c r="K3" s="50" t="n"/>
-      <c r="L3" s="50" t="n"/>
-      <c r="M3" s="50" t="n"/>
-      <c r="N3" s="50" t="n"/>
-      <c r="O3" s="50" t="n"/>
-      <c r="P3" s="50" t="n"/>
-      <c r="Q3" s="50" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="48" t="inlineStr">
@@ -1090,7 +1058,7 @@
       </c>
       <c r="J4" s="48" t="inlineStr">
         <is>
-          <t>معیار قبولی</t>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
       <c r="K4" s="48" t="inlineStr">
@@ -1179,27 +1147,26 @@
       </c>
       <c r="J5" s="52" t="inlineStr">
         <is>
-          <t>آمدن خطا ظرف چند ثانیه با همان چهره = قبول؛ نیامدن یا شارژِ ادامه‌دار = رد</t>
-        </is>
-      </c>
-      <c r="K5" s="52" t="inlineStr"/>
+          <t>باید ببینید: ظرف چند ثانیه خطای قطع باتری می‌آید؛ قرمز تند چشمک می‌زند، سبز ثابت است، سه بوق دوره‌ای می‌آید و شارژ کاملاً می‌ایستد. اگر خطا نیامد یا شارژ ادامه داشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K5" s="52" t="n"/>
       <c r="L5" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="52" t="inlineStr"/>
-      <c r="N5" s="52" t="inlineStr"/>
+      <c r="M5" s="52" t="n"/>
+      <c r="N5" s="52" t="n"/>
       <c r="O5" s="54" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="54" t="inlineStr"/>
-      <c r="Q5" s="56" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="P5" s="54" t="n"/>
+      <c r="Q5" s="56">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
@@ -1252,27 +1219,26 @@
       </c>
       <c r="J6" s="57" t="inlineStr">
         <is>
-          <t>آمدن خطای ۶ و شروع‌نشدن شارژ = قبول؛ شروع شارژ بی‌باتری = رد</t>
-        </is>
-      </c>
-      <c r="K6" s="57" t="inlineStr"/>
+          <t>باید ببینید: بدون باتری خطای قطع باتری می‌آید و شارژ هیچ‌وقت شروع نمی‌شود. اگر شارژ بی‌باتری شروع شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K6" s="57" t="n"/>
       <c r="L6" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="57" t="inlineStr"/>
-      <c r="N6" s="57" t="inlineStr"/>
+      <c r="M6" s="57" t="n"/>
+      <c r="N6" s="57" t="n"/>
       <c r="O6" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="59" t="inlineStr"/>
-      <c r="Q6" s="60" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="P6" s="59" t="n"/>
+      <c r="Q6" s="60">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
@@ -1325,1273 +1291,1147 @@
       </c>
       <c r="J7" s="52" t="inlineStr">
         <is>
-          <t>پاک‌شدن و شروع آرام شارژ = قبول؛ ماندن خطا یا شروع خشن = رد</t>
-        </is>
-      </c>
-      <c r="K7" s="52" t="inlineStr"/>
+          <t>باید ببینید: با برگشت باتری خطا خودش پاک می‌شود و شارژ آرام و عادی شروع می‌شود. اگر خطا ماند یا شارژ خشن شروع شد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K7" s="52" t="n"/>
       <c r="L7" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="52" t="inlineStr"/>
-      <c r="N7" s="52" t="inlineStr"/>
+      <c r="M7" s="52" t="n"/>
+      <c r="N7" s="52" t="n"/>
       <c r="O7" s="54" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="54" t="inlineStr"/>
-      <c r="Q7" s="56" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="54" customHeight="1">
+      <c r="P7" s="54" t="n"/>
+      <c r="Q7" s="56">
+        <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="40.5" customHeight="1">
       <c r="A8" s="51" t="inlineStr">
         <is>
+          <t>FL-005</t>
+        </is>
+      </c>
+      <c r="B8" s="52" t="inlineStr">
+        <is>
+          <t>آینه در شارژر</t>
+        </is>
+      </c>
+      <c r="C8" s="53" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>خطای ۶ را مثل FL-001 ساخته‌ای و فعال است</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>گام ۱: یک آمپرمتر دستی سریِ مسیر شارژ بگذار یا جریان شارژ پنل را نگاه کن.
+گام ۲: تا وقتی خطا هست جریان را زیر نظر بگیر.
+گام ۳: باتری را وصل کن و ببین شارژ کی برمی‌گردد.</t>
+        </is>
+      </c>
+      <c r="F8" s="54" t="inlineStr">
+        <is>
+          <t>نگه‌داشتن خطای ۶ و بعد وصل باتری</t>
+        </is>
+      </c>
+      <c r="G8" s="54" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H8" s="52" t="inlineStr">
+        <is>
+          <t>تا وقتی خطای ۶ هست جریان شارژ صفر می‌ماند؛ شارژر بیکار است و فقط با برگشت باتری دوباره راه می‌افتد</t>
+        </is>
+      </c>
+      <c r="I8" s="52" t="inlineStr">
+        <is>
+          <t>توقف کامل تا بازیابی</t>
+        </is>
+      </c>
+      <c r="J8" s="52" t="inlineStr">
+        <is>
+          <t>باید ببینید: تا وقتی خطا هست جریان شارژ در پنل صفر می‌ماند و فقط با برگشت باتری شارژ راه می‌افتد. اگر حین خطا جریان شارژ دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K8" s="52" t="n"/>
+      <c r="L8" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M8" s="52" t="n"/>
+      <c r="N8" s="52" t="n"/>
+      <c r="O8" s="54" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P8" s="54" t="n"/>
+      <c r="Q8" s="56">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="40.5" customHeight="1">
+      <c r="A9" s="51" t="inlineStr">
+        <is>
+          <t>FL-007</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>فریز در مود دستی</t>
+        </is>
+      </c>
+      <c r="C9" s="53" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>دستگاه روشن و از پنل، مود تست دستی شارژر را می‌توانی روشن کنی</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل مود تست دستی شارژر را فعال کن.
+گام ۲: در همین مود سیم باتری را بکش و چند ثانیه صبر کن.
+گام ۳: باتری را وصل کن.</t>
+        </is>
+      </c>
+      <c r="F9" s="54" t="inlineStr">
+        <is>
+          <t>قطع و وصل باتری داخل مود دستی</t>
+        </is>
+      </c>
+      <c r="G9" s="54" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H9" s="52" t="inlineStr">
+        <is>
+          <t>در مود دستی خطای ۶ ساخته نمی‌شود و چراغ قرمز قطع باتری نمی‌آید</t>
+        </is>
+      </c>
+      <c r="I9" s="52" t="inlineStr">
+        <is>
+          <t>بدون قفل در مود دستی</t>
+        </is>
+      </c>
+      <c r="J9" s="52" t="inlineStr">
+        <is>
+          <t>باید ببینید: در مود دستی خطای قطع باتری ساخته نمی‌شود و چراغ قرمز آن نمی‌آید. اگر خطا آمد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K9" s="52" t="n"/>
+      <c r="L9" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M9" s="52" t="n"/>
+      <c r="N9" s="52" t="n"/>
+      <c r="O9" s="54" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P9" s="54" t="n"/>
+      <c r="Q9" s="56">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="51" t="inlineStr">
+        <is>
+          <t>FL-008</t>
+        </is>
+      </c>
+      <c r="B10" s="57" t="inlineStr">
+        <is>
+          <t>خروج از مود دستی</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D10" s="62" t="inlineStr">
+        <is>
+          <t>از FL-007 ادامه بده؛ مود دستی فعال است</t>
+        </is>
+      </c>
+      <c r="E10" s="62" t="inlineStr">
+        <is>
+          <t>گام ۱: از پنل از مود تست دستی خارج شو.
+گام ۲: حالا سیم باتری را حین شارژ بکش.
+گام ۳: چراغ‌ها را ببین.</t>
+        </is>
+      </c>
+      <c r="F10" s="59" t="inlineStr">
+        <is>
+          <t>خروج از مود دستی و قطع باتری</t>
+        </is>
+      </c>
+      <c r="G10" s="59" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H10" s="57" t="inlineStr">
+        <is>
+          <t>بعد از خروج از مود دستی، قطع باتری دوباره مثل حالت عادی خطای ۶ می‌سازد</t>
+        </is>
+      </c>
+      <c r="I10" s="57" t="inlineStr">
+        <is>
+          <t>برگشت رفتار عادی</t>
+        </is>
+      </c>
+      <c r="J10" s="62" t="inlineStr">
+        <is>
+          <t>باید ببینید: بعد از خروج از مود دستی، قطع باتری دوباره خطای همیشگی را می‌سازد. اگر نساخت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K10" s="57" t="n"/>
+      <c r="L10" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M10" s="57" t="n"/>
+      <c r="N10" s="57" t="n"/>
+      <c r="O10" s="59" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P10" s="59" t="n"/>
+      <c r="Q10" s="60">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="51" t="inlineStr">
+        <is>
+          <t>FL-010</t>
+        </is>
+      </c>
+      <c r="B11" s="57" t="inlineStr">
+        <is>
+          <t>تله‌متری</t>
+        </is>
+      </c>
+      <c r="C11" s="59" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D11" s="57" t="inlineStr">
+        <is>
+          <t>پنل باز است و تله‌متری زنده را می‌بینی</t>
+        </is>
+      </c>
+      <c r="E11" s="57" t="inlineStr">
+        <is>
+          <t>گام ۱: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
+گام ۲: در پنل نگاه کن خطای ۶ و توقف شارژ دیده می‌شود.
+گام ۳: باتری را وصل کن و پاک‌شدن خطا را در پنل ببین.</t>
+        </is>
+      </c>
+      <c r="F11" s="59" t="inlineStr">
+        <is>
+          <t>ساختن و پاک‌کردن خطای ۶ جلوی پنل</t>
+        </is>
+      </c>
+      <c r="G11" s="59" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H11" s="57" t="inlineStr">
+        <is>
+          <t>پنل همان چیزی را نشان می‌دهد که روی دستگاه می‌بینی: خطای ۶ می‌آید و با برگشت باتری پاک می‌شود</t>
+        </is>
+      </c>
+      <c r="I11" s="57" t="inlineStr">
+        <is>
+          <t>هم‌گام با چراغ‌های دستگاه</t>
+        </is>
+      </c>
+      <c r="J11" s="57" t="inlineStr">
+        <is>
+          <t>باید ببینید: پنل همان چیزی را نشان می‌دهد که روی دستگاه می‌بینید؛ خطا می‌آید و با برگشت باتری پاک می‌شود. اگر پنل با چراغ‌ها اختلاف داشت، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K11" s="57" t="n"/>
+      <c r="L11" s="55" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M11" s="57" t="n"/>
+      <c r="N11" s="57" t="n"/>
+      <c r="O11" s="59" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P11" s="59" t="n"/>
+      <c r="Q11" s="60">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="54" customHeight="1">
+      <c r="A12" s="51" t="inlineStr">
+        <is>
           <t>FL-004</t>
         </is>
       </c>
-      <c r="B8" s="57" t="inlineStr">
+      <c r="B12" s="57" t="inlineStr">
         <is>
           <t>هیسترزیس 6/7V</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D8" s="57" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D12" s="57" t="inlineStr">
         <is>
           <t>به‌جای یکی از باتری‌ها منبع آزمایشگاهی گذاشته‌ای؛ دستگاه با برق شهر روشن است</t>
         </is>
       </c>
-      <c r="E8" s="57" t="inlineStr">
+      <c r="E12" s="57" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را حدود ۶٫۵ ولت نگه دار (نه وصلِ سالم، نه قطعِ کامل).
 گام ۲: دو دقیقه نگاه کن؛ خطا نباید پرپر بزند.
 گام ۳: ولتاژ را بالای ۷ ببر (سالم) و بعد زیر ۶ ببر (قطع) و هر بار رفتار را چک کن.</t>
         </is>
       </c>
-      <c r="F8" s="59" t="inlineStr">
+      <c r="F12" s="59" t="inlineStr">
         <is>
           <t>ولتاژ یک نیم باتری: ۶٫۵ بعد بالای ۷ بعد زیر ۶ ولت</t>
         </is>
       </c>
-      <c r="G8" s="59" t="inlineStr">
+      <c r="G12" s="59" t="inlineStr">
         <is>
           <t>سه دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="57" t="inlineStr">
+      <c r="H12" s="57" t="inlineStr">
         <is>
           <t>روی ۶٫۵ نه خطای تازه می‌آید نه پاک و ست می‌شود؛ بالای ۷ سالم است و زیر ۶ خطای ۶ می‌آید</t>
         </is>
       </c>
-      <c r="I8" s="57" t="inlineStr">
+      <c r="I12" s="57" t="inlineStr">
         <is>
           <t>بدون پرپر دور مرز</t>
         </is>
       </c>
-      <c r="J8" s="57" t="inlineStr">
-        <is>
-          <t>رفتار تمیز در هر سه نقطه = قبول؛ پرپر زدن رو ۶٫۵ = رد</t>
-        </is>
-      </c>
-      <c r="K8" s="57" t="inlineStr"/>
-      <c r="L8" s="55" t="inlineStr">
+      <c r="J12" s="57" t="inlineStr">
+        <is>
+          <t>باید ببینید: روی ولتاژ وسط (حدود ۶٫۵ ولت) نه خطای تازه می‌آید نه پرپر می‌زند؛ بالای حد سالم و زیر حد خطا می‌آید. اگر روی وسط پرپر زد، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K12" s="57" t="n"/>
+      <c r="L12" s="55" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="57" t="inlineStr"/>
-      <c r="N8" s="57" t="inlineStr"/>
-      <c r="O8" s="59" t="inlineStr">
+      <c r="M12" s="57" t="n"/>
+      <c r="N12" s="57" t="n"/>
+      <c r="O12" s="59" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="59" t="inlineStr"/>
-      <c r="Q8" s="60" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40.5" customHeight="1">
-      <c r="A9" s="51" t="inlineStr">
-        <is>
-          <t>FL-005</t>
-        </is>
-      </c>
-      <c r="B9" s="52" t="inlineStr">
-        <is>
-          <t>آینه در شارژر</t>
-        </is>
-      </c>
-      <c r="C9" s="53" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D9" s="61" t="inlineStr">
-        <is>
-          <t>خطای ۶ را مثل FL-001 ساخته‌ای و فعال است</t>
-        </is>
-      </c>
-      <c r="E9" s="52" t="inlineStr">
-        <is>
-          <t>گام ۱: یک آمپرمتر دستی سریِ مسیر شارژ بگذار یا جریان شارژ پنل را نگاه کن.
-گام ۲: تا وقتی خطا هست جریان را زیر نظر بگیر.
-گام ۳: باتری را وصل کن و ببین شارژ کی برمی‌گردد.</t>
-        </is>
-      </c>
-      <c r="F9" s="54" t="inlineStr">
-        <is>
-          <t>نگه‌داشتن خطای ۶ و بعد وصل باتری</t>
-        </is>
-      </c>
-      <c r="G9" s="54" t="inlineStr">
-        <is>
-          <t>دو دقیقه</t>
-        </is>
-      </c>
-      <c r="H9" s="52" t="inlineStr">
-        <is>
-          <t>تا وقتی خطای ۶ هست جریان شارژ صفر می‌ماند؛ شارژر بیکار است و فقط با برگشت باتری دوباره راه می‌افتد</t>
-        </is>
-      </c>
-      <c r="I9" s="52" t="inlineStr">
-        <is>
-          <t>توقف کامل تا بازیابی</t>
-        </is>
-      </c>
-      <c r="J9" s="52" t="inlineStr">
-        <is>
-          <t>جریان صفر در تمام مدت خطا = قبول؛ هر جریان شارژی حین خطا = رد</t>
-        </is>
-      </c>
-      <c r="K9" s="52" t="inlineStr"/>
-      <c r="L9" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M9" s="52" t="inlineStr"/>
-      <c r="N9" s="52" t="inlineStr"/>
-      <c r="O9" s="54" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P9" s="54" t="inlineStr"/>
-      <c r="Q9" s="56" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40.5" customHeight="1">
-      <c r="A10" s="51" t="inlineStr">
-        <is>
-          <t>FL-007</t>
-        </is>
-      </c>
-      <c r="B10" s="52" t="inlineStr">
-        <is>
-          <t>فریز در مود دستی</t>
-        </is>
-      </c>
-      <c r="C10" s="53" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D10" s="52" t="inlineStr">
-        <is>
-          <t>دستگاه روشن و از پنل، مود تست دستی شارژر را می‌توانی روشن کنی</t>
-        </is>
-      </c>
-      <c r="E10" s="52" t="inlineStr">
-        <is>
-          <t>گام ۱: از پنل مود تست دستی شارژر را فعال کن.
-گام ۲: در همین مود سیم باتری را بکش و چند ثانیه صبر کن.
-گام ۳: باتری را وصل کن.</t>
-        </is>
-      </c>
-      <c r="F10" s="54" t="inlineStr">
-        <is>
-          <t>قطع و وصل باتری داخل مود دستی</t>
-        </is>
-      </c>
-      <c r="G10" s="54" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H10" s="52" t="inlineStr">
-        <is>
-          <t>در مود دستی خطای ۶ ساخته نمی‌شود و چراغ قرمز قطع باتری نمی‌آید</t>
-        </is>
-      </c>
-      <c r="I10" s="52" t="inlineStr">
-        <is>
-          <t>بدون قفل در مود دستی</t>
-        </is>
-      </c>
-      <c r="J10" s="52" t="inlineStr">
-        <is>
-          <t>نیامدن خطا در مود دستی = قبول؛ آمدن خطای ۶ = رد</t>
-        </is>
-      </c>
-      <c r="K10" s="52" t="inlineStr"/>
-      <c r="L10" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M10" s="52" t="inlineStr"/>
-      <c r="N10" s="52" t="inlineStr"/>
-      <c r="O10" s="54" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P10" s="54" t="inlineStr"/>
-      <c r="Q10" s="56" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="51" t="inlineStr">
-        <is>
-          <t>FL-008</t>
-        </is>
-      </c>
-      <c r="B11" s="57" t="inlineStr">
-        <is>
-          <t>خروج از مود دستی</t>
-        </is>
-      </c>
-      <c r="C11" s="59" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D11" s="62" t="inlineStr">
-        <is>
-          <t>از FL-007 ادامه بده؛ مود دستی فعال است</t>
-        </is>
-      </c>
-      <c r="E11" s="62" t="inlineStr">
-        <is>
-          <t>گام ۱: از پنل از مود تست دستی خارج شو.
-گام ۲: حالا سیم باتری را حین شارژ بکش.
-گام ۳: چراغ‌ها را ببین.</t>
-        </is>
-      </c>
-      <c r="F11" s="59" t="inlineStr">
-        <is>
-          <t>خروج از مود دستی و قطع باتری</t>
-        </is>
-      </c>
-      <c r="G11" s="59" t="inlineStr">
-        <is>
-          <t>یک دقیقه</t>
-        </is>
-      </c>
-      <c r="H11" s="57" t="inlineStr">
-        <is>
-          <t>بعد از خروج از مود دستی، قطع باتری دوباره مثل حالت عادی خطای ۶ می‌سازد</t>
-        </is>
-      </c>
-      <c r="I11" s="57" t="inlineStr">
-        <is>
-          <t>برگشت رفتار عادی</t>
-        </is>
-      </c>
-      <c r="J11" s="62" t="inlineStr">
-        <is>
-          <t>ساخته‌شدن دوبارهٔ خطای ۶ = قبول؛ نساختن = رد</t>
-        </is>
-      </c>
-      <c r="K11" s="57" t="inlineStr"/>
-      <c r="L11" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M11" s="57" t="inlineStr"/>
-      <c r="N11" s="57" t="inlineStr"/>
-      <c r="O11" s="59" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P11" s="59" t="inlineStr"/>
-      <c r="Q11" s="60" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="51" t="inlineStr">
-        <is>
-          <t>FL-010</t>
-        </is>
-      </c>
-      <c r="B12" s="57" t="inlineStr">
-        <is>
-          <t>تله‌متری</t>
-        </is>
-      </c>
-      <c r="C12" s="59" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D12" s="57" t="inlineStr">
-        <is>
-          <t>پنل باز است و تله‌متری زنده را می‌بینی</t>
-        </is>
-      </c>
-      <c r="E12" s="57" t="inlineStr">
-        <is>
-          <t>گام ۱: حین شارژ سیم باتری را بکش تا خطای ۶ بیاید.
-گام ۲: در پنل نگاه کن خطای ۶ و توقف شارژ دیده می‌شود.
-گام ۳: باتری را وصل کن و پاک‌شدن خطا را در پنل ببین.</t>
-        </is>
-      </c>
-      <c r="F12" s="59" t="inlineStr">
-        <is>
-          <t>ساختن و پاک‌کردن خطای ۶ جلوی پنل</t>
-        </is>
-      </c>
-      <c r="G12" s="59" t="inlineStr">
-        <is>
-          <t>دو دقیقه</t>
-        </is>
-      </c>
-      <c r="H12" s="57" t="inlineStr">
-        <is>
-          <t>پنل همان چیزی را نشان می‌دهد که روی دستگاه می‌بینی: خطای ۶ می‌آید و با برگشت باتری پاک می‌شود</t>
-        </is>
-      </c>
-      <c r="I12" s="57" t="inlineStr">
-        <is>
-          <t>هم‌گام با چراغ‌های دستگاه</t>
-        </is>
-      </c>
-      <c r="J12" s="57" t="inlineStr">
-        <is>
-          <t>یکی‌بودن پنل و چراغ‌ها = قبول؛ اختلاف پنل با واقعیت = رد</t>
-        </is>
-      </c>
-      <c r="K12" s="57" t="inlineStr"/>
-      <c r="L12" s="55" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M12" s="57" t="inlineStr"/>
-      <c r="N12" s="57" t="inlineStr"/>
-      <c r="O12" s="59" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P12" s="59" t="inlineStr"/>
-      <c r="Q12" s="60" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="54" customHeight="1">
-      <c r="A13" s="50" t="n"/>
-      <c r="B13" s="50" t="n"/>
-      <c r="C13" s="50" t="n"/>
-      <c r="D13" s="50" t="n"/>
-      <c r="E13" s="50" t="n"/>
-      <c r="F13" s="50" t="n"/>
-      <c r="G13" s="50" t="n"/>
-      <c r="H13" s="50" t="n"/>
-      <c r="I13" s="50" t="n"/>
-      <c r="J13" s="50" t="n"/>
-      <c r="K13" s="50" t="n"/>
-      <c r="L13" s="50" t="n"/>
-      <c r="M13" s="50" t="n"/>
-      <c r="N13" s="50" t="n"/>
-      <c r="O13" s="50" t="n"/>
-      <c r="P13" s="50" t="n"/>
-      <c r="Q13" s="63">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+      <c r="P12" s="59" t="n"/>
+      <c r="Q12" s="60">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="50" t="n"/>
-      <c r="B14" s="50" t="n"/>
-      <c r="C14" s="50" t="n"/>
-      <c r="D14" s="50" t="n"/>
-      <c r="E14" s="50" t="n"/>
-      <c r="F14" s="50" t="n"/>
-      <c r="G14" s="50" t="n"/>
-      <c r="H14" s="50" t="n"/>
-      <c r="I14" s="50" t="n"/>
-      <c r="J14" s="50" t="n"/>
-      <c r="K14" s="50" t="n"/>
-      <c r="L14" s="50" t="n"/>
-      <c r="M14" s="50" t="n"/>
-      <c r="N14" s="50" t="n"/>
-      <c r="O14" s="50" t="n"/>
-      <c r="P14" s="50" t="n"/>
-      <c r="Q14" s="63">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="40.5" customHeight="1">
-      <c r="A15" s="50" t="n"/>
-      <c r="B15" s="50" t="n"/>
-      <c r="C15" s="50" t="n"/>
-      <c r="D15" s="50" t="n"/>
-      <c r="E15" s="50" t="n"/>
-      <c r="F15" s="50" t="n"/>
-      <c r="G15" s="50" t="n"/>
-      <c r="H15" s="50" t="n"/>
-      <c r="I15" s="50" t="n"/>
-      <c r="J15" s="50" t="n"/>
-      <c r="K15" s="50" t="n"/>
-      <c r="L15" s="50" t="n"/>
-      <c r="M15" s="50" t="n"/>
-      <c r="N15" s="50" t="n"/>
-      <c r="O15" s="50" t="n"/>
-      <c r="P15" s="50" t="n"/>
-      <c r="Q15" s="63">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
-        <v/>
-      </c>
+    <row r="13">
+      <c r="A13" s="77" t="n"/>
+      <c r="B13" s="77" t="n"/>
+      <c r="C13" s="77" t="n"/>
+      <c r="D13" s="77" t="n"/>
+      <c r="E13" s="77" t="n"/>
+      <c r="F13" s="77" t="n"/>
+      <c r="G13" s="77" t="n"/>
+      <c r="H13" s="77" t="n"/>
+      <c r="I13" s="77" t="n"/>
+      <c r="J13" s="77" t="n"/>
+      <c r="K13" s="77" t="n"/>
+      <c r="L13" s="77" t="n"/>
+      <c r="M13" s="77" t="n"/>
+      <c r="N13" s="77" t="n"/>
+      <c r="O13" s="77" t="n"/>
+      <c r="P13" s="77" t="n"/>
+      <c r="Q13" s="78" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="77" t="n"/>
+      <c r="B14" s="77" t="n"/>
+      <c r="C14" s="77" t="n"/>
+      <c r="D14" s="77" t="n"/>
+      <c r="E14" s="77" t="n"/>
+      <c r="F14" s="77" t="n"/>
+      <c r="G14" s="77" t="n"/>
+      <c r="H14" s="77" t="n"/>
+      <c r="I14" s="77" t="n"/>
+      <c r="J14" s="77" t="n"/>
+      <c r="K14" s="77" t="n"/>
+      <c r="L14" s="77" t="n"/>
+      <c r="M14" s="77" t="n"/>
+      <c r="N14" s="77" t="n"/>
+      <c r="O14" s="77" t="n"/>
+      <c r="P14" s="77" t="n"/>
+      <c r="Q14" s="78" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="77" t="n"/>
+      <c r="B15" s="77" t="n"/>
+      <c r="C15" s="77" t="n"/>
+      <c r="D15" s="77" t="n"/>
+      <c r="E15" s="77" t="n"/>
+      <c r="F15" s="77" t="n"/>
+      <c r="G15" s="77" t="n"/>
+      <c r="H15" s="77" t="n"/>
+      <c r="I15" s="77" t="n"/>
+      <c r="J15" s="77" t="n"/>
+      <c r="K15" s="77" t="n"/>
+      <c r="L15" s="77" t="n"/>
+      <c r="M15" s="77" t="n"/>
+      <c r="N15" s="77" t="n"/>
+      <c r="O15" s="77" t="n"/>
+      <c r="P15" s="77" t="n"/>
+      <c r="Q15" s="78" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="n"/>
-      <c r="B16" s="50" t="n"/>
-      <c r="C16" s="50" t="n"/>
-      <c r="D16" s="50" t="n"/>
-      <c r="E16" s="50" t="n"/>
-      <c r="F16" s="50" t="n"/>
-      <c r="G16" s="50" t="n"/>
-      <c r="H16" s="50" t="n"/>
-      <c r="I16" s="50" t="n"/>
-      <c r="J16" s="50" t="n"/>
-      <c r="K16" s="50" t="n"/>
-      <c r="L16" s="50" t="n"/>
-      <c r="M16" s="50" t="n"/>
-      <c r="N16" s="50" t="n"/>
-      <c r="O16" s="50" t="n"/>
-      <c r="P16" s="50" t="n"/>
-      <c r="Q16" s="63">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
-        <v/>
-      </c>
+      <c r="A16" s="77" t="n"/>
+      <c r="B16" s="77" t="n"/>
+      <c r="C16" s="77" t="n"/>
+      <c r="D16" s="77" t="n"/>
+      <c r="E16" s="77" t="n"/>
+      <c r="F16" s="77" t="n"/>
+      <c r="G16" s="77" t="n"/>
+      <c r="H16" s="77" t="n"/>
+      <c r="I16" s="77" t="n"/>
+      <c r="J16" s="77" t="n"/>
+      <c r="K16" s="77" t="n"/>
+      <c r="L16" s="77" t="n"/>
+      <c r="M16" s="77" t="n"/>
+      <c r="N16" s="77" t="n"/>
+      <c r="O16" s="77" t="n"/>
+      <c r="P16" s="77" t="n"/>
+      <c r="Q16" s="78" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="n"/>
-      <c r="B17" s="50" t="n"/>
-      <c r="C17" s="50" t="n"/>
-      <c r="D17" s="50" t="n"/>
-      <c r="E17" s="50" t="n"/>
-      <c r="F17" s="50" t="n"/>
-      <c r="G17" s="50" t="n"/>
-      <c r="H17" s="50" t="n"/>
-      <c r="I17" s="50" t="n"/>
-      <c r="J17" s="50" t="n"/>
-      <c r="K17" s="50" t="n"/>
-      <c r="L17" s="50" t="n"/>
-      <c r="M17" s="50" t="n"/>
-      <c r="N17" s="50" t="n"/>
-      <c r="O17" s="50" t="n"/>
-      <c r="P17" s="50" t="n"/>
-      <c r="Q17" s="63">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
-        <v/>
-      </c>
+      <c r="A17" s="77" t="n"/>
+      <c r="B17" s="77" t="n"/>
+      <c r="C17" s="77" t="n"/>
+      <c r="D17" s="77" t="n"/>
+      <c r="E17" s="77" t="n"/>
+      <c r="F17" s="77" t="n"/>
+      <c r="G17" s="77" t="n"/>
+      <c r="H17" s="77" t="n"/>
+      <c r="I17" s="77" t="n"/>
+      <c r="J17" s="77" t="n"/>
+      <c r="K17" s="77" t="n"/>
+      <c r="L17" s="77" t="n"/>
+      <c r="M17" s="77" t="n"/>
+      <c r="N17" s="77" t="n"/>
+      <c r="O17" s="77" t="n"/>
+      <c r="P17" s="77" t="n"/>
+      <c r="Q17" s="78" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="50" t="n"/>
-      <c r="B18" s="50" t="n"/>
-      <c r="C18" s="50" t="n"/>
-      <c r="D18" s="50" t="n"/>
-      <c r="E18" s="50" t="n"/>
-      <c r="F18" s="50" t="n"/>
-      <c r="G18" s="50" t="n"/>
-      <c r="H18" s="50" t="n"/>
-      <c r="I18" s="50" t="n"/>
-      <c r="J18" s="50" t="n"/>
-      <c r="K18" s="50" t="n"/>
-      <c r="L18" s="50" t="n"/>
-      <c r="M18" s="50" t="n"/>
-      <c r="N18" s="50" t="n"/>
-      <c r="O18" s="50" t="n"/>
-      <c r="P18" s="50" t="n"/>
-      <c r="Q18" s="63">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
-        <v/>
-      </c>
+      <c r="A18" s="77" t="n"/>
+      <c r="B18" s="77" t="n"/>
+      <c r="C18" s="77" t="n"/>
+      <c r="D18" s="77" t="n"/>
+      <c r="E18" s="77" t="n"/>
+      <c r="F18" s="77" t="n"/>
+      <c r="G18" s="77" t="n"/>
+      <c r="H18" s="77" t="n"/>
+      <c r="I18" s="77" t="n"/>
+      <c r="J18" s="77" t="n"/>
+      <c r="K18" s="77" t="n"/>
+      <c r="L18" s="77" t="n"/>
+      <c r="M18" s="77" t="n"/>
+      <c r="N18" s="77" t="n"/>
+      <c r="O18" s="77" t="n"/>
+      <c r="P18" s="77" t="n"/>
+      <c r="Q18" s="78" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="50" t="n"/>
-      <c r="B19" s="50" t="n"/>
-      <c r="C19" s="50" t="n"/>
-      <c r="D19" s="50" t="n"/>
-      <c r="E19" s="50" t="n"/>
-      <c r="F19" s="50" t="n"/>
-      <c r="G19" s="50" t="n"/>
-      <c r="H19" s="50" t="n"/>
-      <c r="I19" s="50" t="n"/>
-      <c r="J19" s="50" t="n"/>
-      <c r="K19" s="50" t="n"/>
-      <c r="L19" s="50" t="n"/>
-      <c r="M19" s="50" t="n"/>
-      <c r="N19" s="50" t="n"/>
-      <c r="O19" s="50" t="n"/>
-      <c r="P19" s="50" t="n"/>
-      <c r="Q19" s="63">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
-        <v/>
-      </c>
+      <c r="A19" s="77" t="n"/>
+      <c r="B19" s="77" t="n"/>
+      <c r="C19" s="77" t="n"/>
+      <c r="D19" s="77" t="n"/>
+      <c r="E19" s="77" t="n"/>
+      <c r="F19" s="77" t="n"/>
+      <c r="G19" s="77" t="n"/>
+      <c r="H19" s="77" t="n"/>
+      <c r="I19" s="77" t="n"/>
+      <c r="J19" s="77" t="n"/>
+      <c r="K19" s="77" t="n"/>
+      <c r="L19" s="77" t="n"/>
+      <c r="M19" s="77" t="n"/>
+      <c r="N19" s="77" t="n"/>
+      <c r="O19" s="77" t="n"/>
+      <c r="P19" s="77" t="n"/>
+      <c r="Q19" s="78" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="n"/>
-      <c r="B20" s="50" t="n"/>
-      <c r="C20" s="50" t="n"/>
-      <c r="D20" s="50" t="n"/>
-      <c r="E20" s="50" t="n"/>
-      <c r="F20" s="50" t="n"/>
-      <c r="G20" s="50" t="n"/>
-      <c r="H20" s="50" t="n"/>
-      <c r="I20" s="50" t="n"/>
-      <c r="J20" s="50" t="n"/>
-      <c r="K20" s="50" t="n"/>
-      <c r="L20" s="50" t="n"/>
-      <c r="M20" s="50" t="n"/>
-      <c r="N20" s="50" t="n"/>
-      <c r="O20" s="50" t="n"/>
-      <c r="P20" s="50" t="n"/>
-      <c r="Q20" s="63">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
-        <v/>
-      </c>
+      <c r="A20" s="77" t="n"/>
+      <c r="B20" s="77" t="n"/>
+      <c r="C20" s="77" t="n"/>
+      <c r="D20" s="77" t="n"/>
+      <c r="E20" s="77" t="n"/>
+      <c r="F20" s="77" t="n"/>
+      <c r="G20" s="77" t="n"/>
+      <c r="H20" s="77" t="n"/>
+      <c r="I20" s="77" t="n"/>
+      <c r="J20" s="77" t="n"/>
+      <c r="K20" s="77" t="n"/>
+      <c r="L20" s="77" t="n"/>
+      <c r="M20" s="77" t="n"/>
+      <c r="N20" s="77" t="n"/>
+      <c r="O20" s="77" t="n"/>
+      <c r="P20" s="77" t="n"/>
+      <c r="Q20" s="78" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="n"/>
-      <c r="B21" s="50" t="n"/>
-      <c r="C21" s="50" t="n"/>
-      <c r="D21" s="50" t="n"/>
-      <c r="E21" s="50" t="n"/>
-      <c r="F21" s="50" t="n"/>
-      <c r="G21" s="50" t="n"/>
-      <c r="H21" s="50" t="n"/>
-      <c r="I21" s="50" t="n"/>
-      <c r="J21" s="50" t="n"/>
-      <c r="K21" s="50" t="n"/>
-      <c r="L21" s="50" t="n"/>
-      <c r="M21" s="50" t="n"/>
-      <c r="N21" s="50" t="n"/>
-      <c r="O21" s="50" t="n"/>
-      <c r="P21" s="50" t="n"/>
-      <c r="Q21" s="63">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
-        <v/>
-      </c>
+      <c r="A21" s="77" t="n"/>
+      <c r="B21" s="77" t="n"/>
+      <c r="C21" s="77" t="n"/>
+      <c r="D21" s="77" t="n"/>
+      <c r="E21" s="77" t="n"/>
+      <c r="F21" s="77" t="n"/>
+      <c r="G21" s="77" t="n"/>
+      <c r="H21" s="77" t="n"/>
+      <c r="I21" s="77" t="n"/>
+      <c r="J21" s="77" t="n"/>
+      <c r="K21" s="77" t="n"/>
+      <c r="L21" s="77" t="n"/>
+      <c r="M21" s="77" t="n"/>
+      <c r="N21" s="77" t="n"/>
+      <c r="O21" s="77" t="n"/>
+      <c r="P21" s="77" t="n"/>
+      <c r="Q21" s="78" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="n"/>
-      <c r="B22" s="50" t="n"/>
-      <c r="C22" s="50" t="n"/>
-      <c r="D22" s="50" t="n"/>
-      <c r="E22" s="50" t="n"/>
-      <c r="F22" s="50" t="n"/>
-      <c r="G22" s="50" t="n"/>
-      <c r="H22" s="50" t="n"/>
-      <c r="I22" s="50" t="n"/>
-      <c r="J22" s="50" t="n"/>
-      <c r="K22" s="50" t="n"/>
-      <c r="L22" s="50" t="n"/>
-      <c r="M22" s="50" t="n"/>
-      <c r="N22" s="50" t="n"/>
-      <c r="O22" s="50" t="n"/>
-      <c r="P22" s="50" t="n"/>
-      <c r="Q22" s="63">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
-        <v/>
-      </c>
+      <c r="A22" s="77" t="n"/>
+      <c r="B22" s="77" t="n"/>
+      <c r="C22" s="77" t="n"/>
+      <c r="D22" s="77" t="n"/>
+      <c r="E22" s="77" t="n"/>
+      <c r="F22" s="77" t="n"/>
+      <c r="G22" s="77" t="n"/>
+      <c r="H22" s="77" t="n"/>
+      <c r="I22" s="77" t="n"/>
+      <c r="J22" s="77" t="n"/>
+      <c r="K22" s="77" t="n"/>
+      <c r="L22" s="77" t="n"/>
+      <c r="M22" s="77" t="n"/>
+      <c r="N22" s="77" t="n"/>
+      <c r="O22" s="77" t="n"/>
+      <c r="P22" s="77" t="n"/>
+      <c r="Q22" s="78" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="n"/>
-      <c r="B23" s="50" t="n"/>
-      <c r="C23" s="50" t="n"/>
-      <c r="D23" s="50" t="n"/>
-      <c r="E23" s="50" t="n"/>
-      <c r="F23" s="50" t="n"/>
-      <c r="G23" s="50" t="n"/>
-      <c r="H23" s="50" t="n"/>
-      <c r="I23" s="50" t="n"/>
-      <c r="J23" s="50" t="n"/>
-      <c r="K23" s="50" t="n"/>
-      <c r="L23" s="50" t="n"/>
-      <c r="M23" s="50" t="n"/>
-      <c r="N23" s="50" t="n"/>
-      <c r="O23" s="50" t="n"/>
-      <c r="P23" s="50" t="n"/>
-      <c r="Q23" s="63">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
-        <v/>
-      </c>
+      <c r="A23" s="77" t="n"/>
+      <c r="B23" s="77" t="n"/>
+      <c r="C23" s="77" t="n"/>
+      <c r="D23" s="77" t="n"/>
+      <c r="E23" s="77" t="n"/>
+      <c r="F23" s="77" t="n"/>
+      <c r="G23" s="77" t="n"/>
+      <c r="H23" s="77" t="n"/>
+      <c r="I23" s="77" t="n"/>
+      <c r="J23" s="77" t="n"/>
+      <c r="K23" s="77" t="n"/>
+      <c r="L23" s="77" t="n"/>
+      <c r="M23" s="77" t="n"/>
+      <c r="N23" s="77" t="n"/>
+      <c r="O23" s="77" t="n"/>
+      <c r="P23" s="77" t="n"/>
+      <c r="Q23" s="78" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="50" t="n"/>
-      <c r="B24" s="50" t="n"/>
-      <c r="C24" s="50" t="n"/>
-      <c r="D24" s="50" t="n"/>
-      <c r="E24" s="50" t="n"/>
-      <c r="F24" s="50" t="n"/>
-      <c r="G24" s="50" t="n"/>
-      <c r="H24" s="50" t="n"/>
-      <c r="I24" s="50" t="n"/>
-      <c r="J24" s="50" t="n"/>
-      <c r="K24" s="50" t="n"/>
-      <c r="L24" s="50" t="n"/>
-      <c r="M24" s="50" t="n"/>
-      <c r="N24" s="50" t="n"/>
-      <c r="O24" s="50" t="n"/>
-      <c r="P24" s="50" t="n"/>
-      <c r="Q24" s="63">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
-        <v/>
-      </c>
+      <c r="A24" s="77" t="n"/>
+      <c r="B24" s="77" t="n"/>
+      <c r="C24" s="77" t="n"/>
+      <c r="D24" s="77" t="n"/>
+      <c r="E24" s="77" t="n"/>
+      <c r="F24" s="77" t="n"/>
+      <c r="G24" s="77" t="n"/>
+      <c r="H24" s="77" t="n"/>
+      <c r="I24" s="77" t="n"/>
+      <c r="J24" s="77" t="n"/>
+      <c r="K24" s="77" t="n"/>
+      <c r="L24" s="77" t="n"/>
+      <c r="M24" s="77" t="n"/>
+      <c r="N24" s="77" t="n"/>
+      <c r="O24" s="77" t="n"/>
+      <c r="P24" s="77" t="n"/>
+      <c r="Q24" s="78" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="n"/>
-      <c r="B25" s="50" t="n"/>
-      <c r="C25" s="50" t="n"/>
-      <c r="D25" s="50" t="n"/>
-      <c r="E25" s="50" t="n"/>
-      <c r="F25" s="50" t="n"/>
-      <c r="G25" s="50" t="n"/>
-      <c r="H25" s="50" t="n"/>
-      <c r="I25" s="50" t="n"/>
-      <c r="J25" s="50" t="n"/>
-      <c r="K25" s="50" t="n"/>
-      <c r="L25" s="50" t="n"/>
-      <c r="M25" s="50" t="n"/>
-      <c r="N25" s="50" t="n"/>
-      <c r="O25" s="50" t="n"/>
-      <c r="P25" s="50" t="n"/>
-      <c r="Q25" s="63">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
-        <v/>
-      </c>
+      <c r="A25" s="77" t="n"/>
+      <c r="B25" s="77" t="n"/>
+      <c r="C25" s="77" t="n"/>
+      <c r="D25" s="77" t="n"/>
+      <c r="E25" s="77" t="n"/>
+      <c r="F25" s="77" t="n"/>
+      <c r="G25" s="77" t="n"/>
+      <c r="H25" s="77" t="n"/>
+      <c r="I25" s="77" t="n"/>
+      <c r="J25" s="77" t="n"/>
+      <c r="K25" s="77" t="n"/>
+      <c r="L25" s="77" t="n"/>
+      <c r="M25" s="77" t="n"/>
+      <c r="N25" s="77" t="n"/>
+      <c r="O25" s="77" t="n"/>
+      <c r="P25" s="77" t="n"/>
+      <c r="Q25" s="78" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="50" t="n"/>
-      <c r="B26" s="50" t="n"/>
-      <c r="C26" s="50" t="n"/>
-      <c r="D26" s="50" t="n"/>
-      <c r="E26" s="50" t="n"/>
-      <c r="F26" s="50" t="n"/>
-      <c r="G26" s="50" t="n"/>
-      <c r="H26" s="50" t="n"/>
-      <c r="I26" s="50" t="n"/>
-      <c r="J26" s="50" t="n"/>
-      <c r="K26" s="50" t="n"/>
-      <c r="L26" s="50" t="n"/>
-      <c r="M26" s="50" t="n"/>
-      <c r="N26" s="50" t="n"/>
-      <c r="O26" s="50" t="n"/>
-      <c r="P26" s="50" t="n"/>
-      <c r="Q26" s="63">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
-        <v/>
-      </c>
+      <c r="A26" s="77" t="n"/>
+      <c r="B26" s="77" t="n"/>
+      <c r="C26" s="77" t="n"/>
+      <c r="D26" s="77" t="n"/>
+      <c r="E26" s="77" t="n"/>
+      <c r="F26" s="77" t="n"/>
+      <c r="G26" s="77" t="n"/>
+      <c r="H26" s="77" t="n"/>
+      <c r="I26" s="77" t="n"/>
+      <c r="J26" s="77" t="n"/>
+      <c r="K26" s="77" t="n"/>
+      <c r="L26" s="77" t="n"/>
+      <c r="M26" s="77" t="n"/>
+      <c r="N26" s="77" t="n"/>
+      <c r="O26" s="77" t="n"/>
+      <c r="P26" s="77" t="n"/>
+      <c r="Q26" s="78" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="n"/>
-      <c r="B27" s="50" t="n"/>
-      <c r="C27" s="50" t="n"/>
-      <c r="D27" s="50" t="n"/>
-      <c r="E27" s="50" t="n"/>
-      <c r="F27" s="50" t="n"/>
-      <c r="G27" s="50" t="n"/>
-      <c r="H27" s="50" t="n"/>
-      <c r="I27" s="50" t="n"/>
-      <c r="J27" s="50" t="n"/>
-      <c r="K27" s="50" t="n"/>
-      <c r="L27" s="50" t="n"/>
-      <c r="M27" s="50" t="n"/>
-      <c r="N27" s="50" t="n"/>
-      <c r="O27" s="50" t="n"/>
-      <c r="P27" s="50" t="n"/>
-      <c r="Q27" s="63">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
-        <v/>
-      </c>
+      <c r="A27" s="77" t="n"/>
+      <c r="B27" s="77" t="n"/>
+      <c r="C27" s="77" t="n"/>
+      <c r="D27" s="77" t="n"/>
+      <c r="E27" s="77" t="n"/>
+      <c r="F27" s="77" t="n"/>
+      <c r="G27" s="77" t="n"/>
+      <c r="H27" s="77" t="n"/>
+      <c r="I27" s="77" t="n"/>
+      <c r="J27" s="77" t="n"/>
+      <c r="K27" s="77" t="n"/>
+      <c r="L27" s="77" t="n"/>
+      <c r="M27" s="77" t="n"/>
+      <c r="N27" s="77" t="n"/>
+      <c r="O27" s="77" t="n"/>
+      <c r="P27" s="77" t="n"/>
+      <c r="Q27" s="78" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="50" t="n"/>
-      <c r="B28" s="50" t="n"/>
-      <c r="C28" s="50" t="n"/>
-      <c r="D28" s="50" t="n"/>
-      <c r="E28" s="50" t="n"/>
-      <c r="F28" s="50" t="n"/>
-      <c r="G28" s="50" t="n"/>
-      <c r="H28" s="50" t="n"/>
-      <c r="I28" s="50" t="n"/>
-      <c r="J28" s="50" t="n"/>
-      <c r="K28" s="50" t="n"/>
-      <c r="L28" s="50" t="n"/>
-      <c r="M28" s="50" t="n"/>
-      <c r="N28" s="50" t="n"/>
-      <c r="O28" s="50" t="n"/>
-      <c r="P28" s="50" t="n"/>
-      <c r="Q28" s="63">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
+      <c r="A28" s="77" t="n"/>
+      <c r="B28" s="77" t="n"/>
+      <c r="C28" s="77" t="n"/>
+      <c r="D28" s="77" t="n"/>
+      <c r="E28" s="77" t="n"/>
+      <c r="F28" s="77" t="n"/>
+      <c r="G28" s="77" t="n"/>
+      <c r="H28" s="77" t="n"/>
+      <c r="I28" s="77" t="n"/>
+      <c r="J28" s="77" t="n"/>
+      <c r="K28" s="77" t="n"/>
+      <c r="L28" s="77" t="n"/>
+      <c r="M28" s="77" t="n"/>
+      <c r="N28" s="77" t="n"/>
+      <c r="O28" s="77" t="n"/>
+      <c r="P28" s="77" t="n"/>
+      <c r="Q28" s="78" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="50" t="n"/>
-      <c r="B29" s="50" t="n"/>
-      <c r="C29" s="50" t="n"/>
-      <c r="D29" s="50" t="n"/>
-      <c r="E29" s="50" t="n"/>
-      <c r="F29" s="50" t="n"/>
-      <c r="G29" s="50" t="n"/>
-      <c r="H29" s="50" t="n"/>
-      <c r="I29" s="50" t="n"/>
-      <c r="J29" s="50" t="n"/>
-      <c r="K29" s="50" t="n"/>
-      <c r="L29" s="50" t="n"/>
-      <c r="M29" s="50" t="n"/>
-      <c r="N29" s="50" t="n"/>
-      <c r="O29" s="50" t="n"/>
-      <c r="P29" s="50" t="n"/>
-      <c r="Q29" s="63">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
+      <c r="A29" s="77" t="n"/>
+      <c r="B29" s="77" t="n"/>
+      <c r="C29" s="77" t="n"/>
+      <c r="D29" s="77" t="n"/>
+      <c r="E29" s="77" t="n"/>
+      <c r="F29" s="77" t="n"/>
+      <c r="G29" s="77" t="n"/>
+      <c r="H29" s="77" t="n"/>
+      <c r="I29" s="77" t="n"/>
+      <c r="J29" s="77" t="n"/>
+      <c r="K29" s="77" t="n"/>
+      <c r="L29" s="77" t="n"/>
+      <c r="M29" s="77" t="n"/>
+      <c r="N29" s="77" t="n"/>
+      <c r="O29" s="77" t="n"/>
+      <c r="P29" s="77" t="n"/>
+      <c r="Q29" s="78" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="50" t="n"/>
-      <c r="B30" s="50" t="n"/>
-      <c r="C30" s="50" t="n"/>
-      <c r="D30" s="50" t="n"/>
-      <c r="E30" s="50" t="n"/>
-      <c r="F30" s="50" t="n"/>
-      <c r="G30" s="50" t="n"/>
-      <c r="H30" s="50" t="n"/>
-      <c r="I30" s="50" t="n"/>
-      <c r="J30" s="50" t="n"/>
-      <c r="K30" s="50" t="n"/>
-      <c r="L30" s="50" t="n"/>
-      <c r="M30" s="50" t="n"/>
-      <c r="N30" s="50" t="n"/>
-      <c r="O30" s="50" t="n"/>
-      <c r="P30" s="50" t="n"/>
-      <c r="Q30" s="63">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
-        <v/>
-      </c>
+      <c r="A30" s="77" t="n"/>
+      <c r="B30" s="77" t="n"/>
+      <c r="C30" s="77" t="n"/>
+      <c r="D30" s="77" t="n"/>
+      <c r="E30" s="77" t="n"/>
+      <c r="F30" s="77" t="n"/>
+      <c r="G30" s="77" t="n"/>
+      <c r="H30" s="77" t="n"/>
+      <c r="I30" s="77" t="n"/>
+      <c r="J30" s="77" t="n"/>
+      <c r="K30" s="77" t="n"/>
+      <c r="L30" s="77" t="n"/>
+      <c r="M30" s="77" t="n"/>
+      <c r="N30" s="77" t="n"/>
+      <c r="O30" s="77" t="n"/>
+      <c r="P30" s="77" t="n"/>
+      <c r="Q30" s="78" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="50" t="n"/>
-      <c r="B31" s="50" t="n"/>
-      <c r="C31" s="50" t="n"/>
-      <c r="D31" s="50" t="n"/>
-      <c r="E31" s="50" t="n"/>
-      <c r="F31" s="50" t="n"/>
-      <c r="G31" s="50" t="n"/>
-      <c r="H31" s="50" t="n"/>
-      <c r="I31" s="50" t="n"/>
-      <c r="J31" s="50" t="n"/>
-      <c r="K31" s="50" t="n"/>
-      <c r="L31" s="50" t="n"/>
-      <c r="M31" s="50" t="n"/>
-      <c r="N31" s="50" t="n"/>
-      <c r="O31" s="50" t="n"/>
-      <c r="P31" s="50" t="n"/>
-      <c r="Q31" s="63">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
-        <v/>
-      </c>
+      <c r="A31" s="77" t="n"/>
+      <c r="B31" s="77" t="n"/>
+      <c r="C31" s="77" t="n"/>
+      <c r="D31" s="77" t="n"/>
+      <c r="E31" s="77" t="n"/>
+      <c r="F31" s="77" t="n"/>
+      <c r="G31" s="77" t="n"/>
+      <c r="H31" s="77" t="n"/>
+      <c r="I31" s="77" t="n"/>
+      <c r="J31" s="77" t="n"/>
+      <c r="K31" s="77" t="n"/>
+      <c r="L31" s="77" t="n"/>
+      <c r="M31" s="77" t="n"/>
+      <c r="N31" s="77" t="n"/>
+      <c r="O31" s="77" t="n"/>
+      <c r="P31" s="77" t="n"/>
+      <c r="Q31" s="78" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="50" t="n"/>
-      <c r="B32" s="50" t="n"/>
-      <c r="C32" s="50" t="n"/>
-      <c r="D32" s="50" t="n"/>
-      <c r="E32" s="50" t="n"/>
-      <c r="F32" s="50" t="n"/>
-      <c r="G32" s="50" t="n"/>
-      <c r="H32" s="50" t="n"/>
-      <c r="I32" s="50" t="n"/>
-      <c r="J32" s="50" t="n"/>
-      <c r="K32" s="50" t="n"/>
-      <c r="L32" s="50" t="n"/>
-      <c r="M32" s="50" t="n"/>
-      <c r="N32" s="50" t="n"/>
-      <c r="O32" s="50" t="n"/>
-      <c r="P32" s="50" t="n"/>
-      <c r="Q32" s="63">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
-        <v/>
-      </c>
+      <c r="A32" s="77" t="n"/>
+      <c r="B32" s="77" t="n"/>
+      <c r="C32" s="77" t="n"/>
+      <c r="D32" s="77" t="n"/>
+      <c r="E32" s="77" t="n"/>
+      <c r="F32" s="77" t="n"/>
+      <c r="G32" s="77" t="n"/>
+      <c r="H32" s="77" t="n"/>
+      <c r="I32" s="77" t="n"/>
+      <c r="J32" s="77" t="n"/>
+      <c r="K32" s="77" t="n"/>
+      <c r="L32" s="77" t="n"/>
+      <c r="M32" s="77" t="n"/>
+      <c r="N32" s="77" t="n"/>
+      <c r="O32" s="77" t="n"/>
+      <c r="P32" s="77" t="n"/>
+      <c r="Q32" s="78" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="50" t="n"/>
-      <c r="B33" s="50" t="n"/>
-      <c r="C33" s="50" t="n"/>
-      <c r="D33" s="50" t="n"/>
-      <c r="E33" s="50" t="n"/>
-      <c r="F33" s="50" t="n"/>
-      <c r="G33" s="50" t="n"/>
-      <c r="H33" s="50" t="n"/>
-      <c r="I33" s="50" t="n"/>
-      <c r="J33" s="50" t="n"/>
-      <c r="K33" s="50" t="n"/>
-      <c r="L33" s="50" t="n"/>
-      <c r="M33" s="50" t="n"/>
-      <c r="N33" s="50" t="n"/>
-      <c r="O33" s="50" t="n"/>
-      <c r="P33" s="50" t="n"/>
-      <c r="Q33" s="63">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
-        <v/>
-      </c>
+      <c r="A33" s="77" t="n"/>
+      <c r="B33" s="77" t="n"/>
+      <c r="C33" s="77" t="n"/>
+      <c r="D33" s="77" t="n"/>
+      <c r="E33" s="77" t="n"/>
+      <c r="F33" s="77" t="n"/>
+      <c r="G33" s="77" t="n"/>
+      <c r="H33" s="77" t="n"/>
+      <c r="I33" s="77" t="n"/>
+      <c r="J33" s="77" t="n"/>
+      <c r="K33" s="77" t="n"/>
+      <c r="L33" s="77" t="n"/>
+      <c r="M33" s="77" t="n"/>
+      <c r="N33" s="77" t="n"/>
+      <c r="O33" s="77" t="n"/>
+      <c r="P33" s="77" t="n"/>
+      <c r="Q33" s="78" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="50" t="n"/>
-      <c r="B34" s="50" t="n"/>
-      <c r="C34" s="50" t="n"/>
-      <c r="D34" s="50" t="n"/>
-      <c r="E34" s="50" t="n"/>
-      <c r="F34" s="50" t="n"/>
-      <c r="G34" s="50" t="n"/>
-      <c r="H34" s="50" t="n"/>
-      <c r="I34" s="50" t="n"/>
-      <c r="J34" s="50" t="n"/>
-      <c r="K34" s="50" t="n"/>
-      <c r="L34" s="50" t="n"/>
-      <c r="M34" s="50" t="n"/>
-      <c r="N34" s="50" t="n"/>
-      <c r="O34" s="50" t="n"/>
-      <c r="P34" s="50" t="n"/>
-      <c r="Q34" s="63">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
-        <v/>
-      </c>
+      <c r="A34" s="77" t="n"/>
+      <c r="B34" s="77" t="n"/>
+      <c r="C34" s="77" t="n"/>
+      <c r="D34" s="77" t="n"/>
+      <c r="E34" s="77" t="n"/>
+      <c r="F34" s="77" t="n"/>
+      <c r="G34" s="77" t="n"/>
+      <c r="H34" s="77" t="n"/>
+      <c r="I34" s="77" t="n"/>
+      <c r="J34" s="77" t="n"/>
+      <c r="K34" s="77" t="n"/>
+      <c r="L34" s="77" t="n"/>
+      <c r="M34" s="77" t="n"/>
+      <c r="N34" s="77" t="n"/>
+      <c r="O34" s="77" t="n"/>
+      <c r="P34" s="77" t="n"/>
+      <c r="Q34" s="78" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="50" t="n"/>
-      <c r="B35" s="50" t="n"/>
-      <c r="C35" s="50" t="n"/>
-      <c r="D35" s="50" t="n"/>
-      <c r="E35" s="50" t="n"/>
-      <c r="F35" s="50" t="n"/>
-      <c r="G35" s="50" t="n"/>
-      <c r="H35" s="50" t="n"/>
-      <c r="I35" s="50" t="n"/>
-      <c r="J35" s="50" t="n"/>
-      <c r="K35" s="50" t="n"/>
-      <c r="L35" s="50" t="n"/>
-      <c r="M35" s="50" t="n"/>
-      <c r="N35" s="50" t="n"/>
-      <c r="O35" s="50" t="n"/>
-      <c r="P35" s="50" t="n"/>
-      <c r="Q35" s="63">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
-        <v/>
-      </c>
+      <c r="A35" s="77" t="n"/>
+      <c r="B35" s="77" t="n"/>
+      <c r="C35" s="77" t="n"/>
+      <c r="D35" s="77" t="n"/>
+      <c r="E35" s="77" t="n"/>
+      <c r="F35" s="77" t="n"/>
+      <c r="G35" s="77" t="n"/>
+      <c r="H35" s="77" t="n"/>
+      <c r="I35" s="77" t="n"/>
+      <c r="J35" s="77" t="n"/>
+      <c r="K35" s="77" t="n"/>
+      <c r="L35" s="77" t="n"/>
+      <c r="M35" s="77" t="n"/>
+      <c r="N35" s="77" t="n"/>
+      <c r="O35" s="77" t="n"/>
+      <c r="P35" s="77" t="n"/>
+      <c r="Q35" s="78" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="50" t="n"/>
-      <c r="B36" s="50" t="n"/>
-      <c r="C36" s="50" t="n"/>
-      <c r="D36" s="50" t="n"/>
-      <c r="E36" s="50" t="n"/>
-      <c r="F36" s="50" t="n"/>
-      <c r="G36" s="50" t="n"/>
-      <c r="H36" s="50" t="n"/>
-      <c r="I36" s="50" t="n"/>
-      <c r="J36" s="50" t="n"/>
-      <c r="K36" s="50" t="n"/>
-      <c r="L36" s="50" t="n"/>
-      <c r="M36" s="50" t="n"/>
-      <c r="N36" s="50" t="n"/>
-      <c r="O36" s="50" t="n"/>
-      <c r="P36" s="50" t="n"/>
-      <c r="Q36" s="63">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
-        <v/>
-      </c>
+      <c r="A36" s="77" t="n"/>
+      <c r="B36" s="77" t="n"/>
+      <c r="C36" s="77" t="n"/>
+      <c r="D36" s="77" t="n"/>
+      <c r="E36" s="77" t="n"/>
+      <c r="F36" s="77" t="n"/>
+      <c r="G36" s="77" t="n"/>
+      <c r="H36" s="77" t="n"/>
+      <c r="I36" s="77" t="n"/>
+      <c r="J36" s="77" t="n"/>
+      <c r="K36" s="77" t="n"/>
+      <c r="L36" s="77" t="n"/>
+      <c r="M36" s="77" t="n"/>
+      <c r="N36" s="77" t="n"/>
+      <c r="O36" s="77" t="n"/>
+      <c r="P36" s="77" t="n"/>
+      <c r="Q36" s="78" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="50" t="n"/>
-      <c r="B37" s="50" t="n"/>
-      <c r="C37" s="50" t="n"/>
-      <c r="D37" s="50" t="n"/>
-      <c r="E37" s="50" t="n"/>
-      <c r="F37" s="50" t="n"/>
-      <c r="G37" s="50" t="n"/>
-      <c r="H37" s="50" t="n"/>
-      <c r="I37" s="50" t="n"/>
-      <c r="J37" s="50" t="n"/>
-      <c r="K37" s="50" t="n"/>
-      <c r="L37" s="50" t="n"/>
-      <c r="M37" s="50" t="n"/>
-      <c r="N37" s="50" t="n"/>
-      <c r="O37" s="50" t="n"/>
-      <c r="P37" s="50" t="n"/>
-      <c r="Q37" s="63">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
-        <v/>
-      </c>
+      <c r="A37" s="77" t="n"/>
+      <c r="B37" s="77" t="n"/>
+      <c r="C37" s="77" t="n"/>
+      <c r="D37" s="77" t="n"/>
+      <c r="E37" s="77" t="n"/>
+      <c r="F37" s="77" t="n"/>
+      <c r="G37" s="77" t="n"/>
+      <c r="H37" s="77" t="n"/>
+      <c r="I37" s="77" t="n"/>
+      <c r="J37" s="77" t="n"/>
+      <c r="K37" s="77" t="n"/>
+      <c r="L37" s="77" t="n"/>
+      <c r="M37" s="77" t="n"/>
+      <c r="N37" s="77" t="n"/>
+      <c r="O37" s="77" t="n"/>
+      <c r="P37" s="77" t="n"/>
+      <c r="Q37" s="78" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="50" t="n"/>
-      <c r="B38" s="50" t="n"/>
-      <c r="C38" s="50" t="n"/>
-      <c r="D38" s="50" t="n"/>
-      <c r="E38" s="50" t="n"/>
-      <c r="F38" s="50" t="n"/>
-      <c r="G38" s="50" t="n"/>
-      <c r="H38" s="50" t="n"/>
-      <c r="I38" s="50" t="n"/>
-      <c r="J38" s="50" t="n"/>
-      <c r="K38" s="50" t="n"/>
-      <c r="L38" s="50" t="n"/>
-      <c r="M38" s="50" t="n"/>
-      <c r="N38" s="50" t="n"/>
-      <c r="O38" s="50" t="n"/>
-      <c r="P38" s="50" t="n"/>
-      <c r="Q38" s="63">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
-        <v/>
-      </c>
+      <c r="A38" s="77" t="n"/>
+      <c r="B38" s="77" t="n"/>
+      <c r="C38" s="77" t="n"/>
+      <c r="D38" s="77" t="n"/>
+      <c r="E38" s="77" t="n"/>
+      <c r="F38" s="77" t="n"/>
+      <c r="G38" s="77" t="n"/>
+      <c r="H38" s="77" t="n"/>
+      <c r="I38" s="77" t="n"/>
+      <c r="J38" s="77" t="n"/>
+      <c r="K38" s="77" t="n"/>
+      <c r="L38" s="77" t="n"/>
+      <c r="M38" s="77" t="n"/>
+      <c r="N38" s="77" t="n"/>
+      <c r="O38" s="77" t="n"/>
+      <c r="P38" s="77" t="n"/>
+      <c r="Q38" s="78" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="50" t="n"/>
-      <c r="B39" s="50" t="n"/>
-      <c r="C39" s="50" t="n"/>
-      <c r="D39" s="50" t="n"/>
-      <c r="E39" s="50" t="n"/>
-      <c r="F39" s="50" t="n"/>
-      <c r="G39" s="50" t="n"/>
-      <c r="H39" s="50" t="n"/>
-      <c r="I39" s="50" t="n"/>
-      <c r="J39" s="50" t="n"/>
-      <c r="K39" s="50" t="n"/>
-      <c r="L39" s="50" t="n"/>
-      <c r="M39" s="50" t="n"/>
-      <c r="N39" s="50" t="n"/>
-      <c r="O39" s="50" t="n"/>
-      <c r="P39" s="50" t="n"/>
-      <c r="Q39" s="63">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
-        <v/>
-      </c>
+      <c r="A39" s="77" t="n"/>
+      <c r="B39" s="77" t="n"/>
+      <c r="C39" s="77" t="n"/>
+      <c r="D39" s="77" t="n"/>
+      <c r="E39" s="77" t="n"/>
+      <c r="F39" s="77" t="n"/>
+      <c r="G39" s="77" t="n"/>
+      <c r="H39" s="77" t="n"/>
+      <c r="I39" s="77" t="n"/>
+      <c r="J39" s="77" t="n"/>
+      <c r="K39" s="77" t="n"/>
+      <c r="L39" s="77" t="n"/>
+      <c r="M39" s="77" t="n"/>
+      <c r="N39" s="77" t="n"/>
+      <c r="O39" s="77" t="n"/>
+      <c r="P39" s="77" t="n"/>
+      <c r="Q39" s="78" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="50" t="n"/>
-      <c r="B40" s="50" t="n"/>
-      <c r="C40" s="50" t="n"/>
-      <c r="D40" s="50" t="n"/>
-      <c r="E40" s="50" t="n"/>
-      <c r="F40" s="50" t="n"/>
-      <c r="G40" s="50" t="n"/>
-      <c r="H40" s="50" t="n"/>
-      <c r="I40" s="50" t="n"/>
-      <c r="J40" s="50" t="n"/>
-      <c r="K40" s="50" t="n"/>
-      <c r="L40" s="50" t="n"/>
-      <c r="M40" s="50" t="n"/>
-      <c r="N40" s="50" t="n"/>
-      <c r="O40" s="50" t="n"/>
-      <c r="P40" s="50" t="n"/>
-      <c r="Q40" s="63">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
-        <v/>
-      </c>
+      <c r="A40" s="77" t="n"/>
+      <c r="B40" s="77" t="n"/>
+      <c r="C40" s="77" t="n"/>
+      <c r="D40" s="77" t="n"/>
+      <c r="E40" s="77" t="n"/>
+      <c r="F40" s="77" t="n"/>
+      <c r="G40" s="77" t="n"/>
+      <c r="H40" s="77" t="n"/>
+      <c r="I40" s="77" t="n"/>
+      <c r="J40" s="77" t="n"/>
+      <c r="K40" s="77" t="n"/>
+      <c r="L40" s="77" t="n"/>
+      <c r="M40" s="77" t="n"/>
+      <c r="N40" s="77" t="n"/>
+      <c r="O40" s="77" t="n"/>
+      <c r="P40" s="77" t="n"/>
+      <c r="Q40" s="78" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="50" t="n"/>
-      <c r="B41" s="50" t="n"/>
-      <c r="C41" s="50" t="n"/>
-      <c r="D41" s="50" t="n"/>
-      <c r="E41" s="50" t="n"/>
-      <c r="F41" s="50" t="n"/>
-      <c r="G41" s="50" t="n"/>
-      <c r="H41" s="50" t="n"/>
-      <c r="I41" s="50" t="n"/>
-      <c r="J41" s="50" t="n"/>
-      <c r="K41" s="50" t="n"/>
-      <c r="L41" s="50" t="n"/>
-      <c r="M41" s="50" t="n"/>
-      <c r="N41" s="50" t="n"/>
-      <c r="O41" s="50" t="n"/>
-      <c r="P41" s="50" t="n"/>
-      <c r="Q41" s="63">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
-        <v/>
-      </c>
+      <c r="A41" s="77" t="n"/>
+      <c r="B41" s="77" t="n"/>
+      <c r="C41" s="77" t="n"/>
+      <c r="D41" s="77" t="n"/>
+      <c r="E41" s="77" t="n"/>
+      <c r="F41" s="77" t="n"/>
+      <c r="G41" s="77" t="n"/>
+      <c r="H41" s="77" t="n"/>
+      <c r="I41" s="77" t="n"/>
+      <c r="J41" s="77" t="n"/>
+      <c r="K41" s="77" t="n"/>
+      <c r="L41" s="77" t="n"/>
+      <c r="M41" s="77" t="n"/>
+      <c r="N41" s="77" t="n"/>
+      <c r="O41" s="77" t="n"/>
+      <c r="P41" s="77" t="n"/>
+      <c r="Q41" s="78" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="50" t="n"/>
-      <c r="B42" s="50" t="n"/>
-      <c r="C42" s="50" t="n"/>
-      <c r="D42" s="50" t="n"/>
-      <c r="E42" s="50" t="n"/>
-      <c r="F42" s="50" t="n"/>
-      <c r="G42" s="50" t="n"/>
-      <c r="H42" s="50" t="n"/>
-      <c r="I42" s="50" t="n"/>
-      <c r="J42" s="50" t="n"/>
-      <c r="K42" s="50" t="n"/>
-      <c r="L42" s="50" t="n"/>
-      <c r="M42" s="50" t="n"/>
-      <c r="N42" s="50" t="n"/>
-      <c r="O42" s="50" t="n"/>
-      <c r="P42" s="50" t="n"/>
-      <c r="Q42" s="63">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
+      <c r="A42" s="77" t="n"/>
+      <c r="B42" s="77" t="n"/>
+      <c r="C42" s="77" t="n"/>
+      <c r="D42" s="77" t="n"/>
+      <c r="E42" s="77" t="n"/>
+      <c r="F42" s="77" t="n"/>
+      <c r="G42" s="77" t="n"/>
+      <c r="H42" s="77" t="n"/>
+      <c r="I42" s="77" t="n"/>
+      <c r="J42" s="77" t="n"/>
+      <c r="K42" s="77" t="n"/>
+      <c r="L42" s="77" t="n"/>
+      <c r="M42" s="77" t="n"/>
+      <c r="N42" s="77" t="n"/>
+      <c r="O42" s="77" t="n"/>
+      <c r="P42" s="77" t="n"/>
+      <c r="Q42" s="78" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="50" t="n"/>
-      <c r="B43" s="50" t="n"/>
-      <c r="C43" s="50" t="n"/>
-      <c r="D43" s="50" t="n"/>
-      <c r="E43" s="50" t="n"/>
-      <c r="F43" s="50" t="n"/>
-      <c r="G43" s="50" t="n"/>
-      <c r="H43" s="50" t="n"/>
-      <c r="I43" s="50" t="n"/>
-      <c r="J43" s="50" t="n"/>
-      <c r="K43" s="50" t="n"/>
-      <c r="L43" s="50" t="n"/>
-      <c r="M43" s="50" t="n"/>
-      <c r="N43" s="50" t="n"/>
-      <c r="O43" s="50" t="n"/>
-      <c r="P43" s="50" t="n"/>
-      <c r="Q43" s="63">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
+      <c r="A43" s="77" t="n"/>
+      <c r="B43" s="77" t="n"/>
+      <c r="C43" s="77" t="n"/>
+      <c r="D43" s="77" t="n"/>
+      <c r="E43" s="77" t="n"/>
+      <c r="F43" s="77" t="n"/>
+      <c r="G43" s="77" t="n"/>
+      <c r="H43" s="77" t="n"/>
+      <c r="I43" s="77" t="n"/>
+      <c r="J43" s="77" t="n"/>
+      <c r="K43" s="77" t="n"/>
+      <c r="L43" s="77" t="n"/>
+      <c r="M43" s="77" t="n"/>
+      <c r="N43" s="77" t="n"/>
+      <c r="O43" s="77" t="n"/>
+      <c r="P43" s="77" t="n"/>
+      <c r="Q43" s="78" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="50" t="n"/>
-      <c r="B44" s="50" t="n"/>
-      <c r="C44" s="50" t="n"/>
-      <c r="D44" s="50" t="n"/>
-      <c r="E44" s="50" t="n"/>
-      <c r="F44" s="50" t="n"/>
-      <c r="G44" s="50" t="n"/>
-      <c r="H44" s="50" t="n"/>
-      <c r="I44" s="50" t="n"/>
-      <c r="J44" s="50" t="n"/>
-      <c r="K44" s="50" t="n"/>
-      <c r="L44" s="50" t="n"/>
-      <c r="M44" s="50" t="n"/>
-      <c r="N44" s="50" t="n"/>
-      <c r="O44" s="50" t="n"/>
-      <c r="P44" s="50" t="n"/>
-      <c r="Q44" s="63">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
+      <c r="A44" s="77" t="n"/>
+      <c r="B44" s="77" t="n"/>
+      <c r="C44" s="77" t="n"/>
+      <c r="D44" s="77" t="n"/>
+      <c r="E44" s="77" t="n"/>
+      <c r="F44" s="77" t="n"/>
+      <c r="G44" s="77" t="n"/>
+      <c r="H44" s="77" t="n"/>
+      <c r="I44" s="77" t="n"/>
+      <c r="J44" s="77" t="n"/>
+      <c r="K44" s="77" t="n"/>
+      <c r="L44" s="77" t="n"/>
+      <c r="M44" s="77" t="n"/>
+      <c r="N44" s="77" t="n"/>
+      <c r="O44" s="77" t="n"/>
+      <c r="P44" s="77" t="n"/>
+      <c r="Q44" s="78" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="50" t="n"/>
-      <c r="B45" s="50" t="n"/>
-      <c r="C45" s="50" t="n"/>
-      <c r="D45" s="50" t="n"/>
-      <c r="E45" s="50" t="n"/>
-      <c r="F45" s="50" t="n"/>
-      <c r="G45" s="50" t="n"/>
-      <c r="H45" s="50" t="n"/>
-      <c r="I45" s="50" t="n"/>
-      <c r="J45" s="50" t="n"/>
-      <c r="K45" s="50" t="n"/>
-      <c r="L45" s="50" t="n"/>
-      <c r="M45" s="50" t="n"/>
-      <c r="N45" s="50" t="n"/>
-      <c r="O45" s="50" t="n"/>
-      <c r="P45" s="50" t="n"/>
-      <c r="Q45" s="63">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
+      <c r="A45" s="77" t="n"/>
+      <c r="B45" s="77" t="n"/>
+      <c r="C45" s="77" t="n"/>
+      <c r="D45" s="77" t="n"/>
+      <c r="E45" s="77" t="n"/>
+      <c r="F45" s="77" t="n"/>
+      <c r="G45" s="77" t="n"/>
+      <c r="H45" s="77" t="n"/>
+      <c r="I45" s="77" t="n"/>
+      <c r="J45" s="77" t="n"/>
+      <c r="K45" s="77" t="n"/>
+      <c r="L45" s="77" t="n"/>
+      <c r="M45" s="77" t="n"/>
+      <c r="N45" s="77" t="n"/>
+      <c r="O45" s="77" t="n"/>
+      <c r="P45" s="77" t="n"/>
+      <c r="Q45" s="78" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="50" t="n"/>
-      <c r="B46" s="50" t="n"/>
-      <c r="C46" s="50" t="n"/>
-      <c r="D46" s="50" t="n"/>
-      <c r="E46" s="50" t="n"/>
-      <c r="F46" s="50" t="n"/>
-      <c r="G46" s="50" t="n"/>
-      <c r="H46" s="50" t="n"/>
-      <c r="I46" s="50" t="n"/>
-      <c r="J46" s="50" t="n"/>
-      <c r="K46" s="50" t="n"/>
-      <c r="L46" s="50" t="n"/>
-      <c r="M46" s="50" t="n"/>
-      <c r="N46" s="50" t="n"/>
-      <c r="O46" s="50" t="n"/>
-      <c r="P46" s="50" t="n"/>
-      <c r="Q46" s="63">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
+      <c r="A46" s="77" t="n"/>
+      <c r="B46" s="77" t="n"/>
+      <c r="C46" s="77" t="n"/>
+      <c r="D46" s="77" t="n"/>
+      <c r="E46" s="77" t="n"/>
+      <c r="F46" s="77" t="n"/>
+      <c r="G46" s="77" t="n"/>
+      <c r="H46" s="77" t="n"/>
+      <c r="I46" s="77" t="n"/>
+      <c r="J46" s="77" t="n"/>
+      <c r="K46" s="77" t="n"/>
+      <c r="L46" s="77" t="n"/>
+      <c r="M46" s="77" t="n"/>
+      <c r="N46" s="77" t="n"/>
+      <c r="O46" s="77" t="n"/>
+      <c r="P46" s="77" t="n"/>
+      <c r="Q46" s="78" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="50" t="n"/>
-      <c r="B47" s="50" t="n"/>
-      <c r="C47" s="50" t="n"/>
-      <c r="D47" s="50" t="n"/>
-      <c r="E47" s="50" t="n"/>
-      <c r="F47" s="50" t="n"/>
-      <c r="G47" s="50" t="n"/>
-      <c r="H47" s="50" t="n"/>
-      <c r="I47" s="50" t="n"/>
-      <c r="J47" s="50" t="n"/>
-      <c r="K47" s="50" t="n"/>
-      <c r="L47" s="50" t="n"/>
-      <c r="M47" s="50" t="n"/>
-      <c r="N47" s="50" t="n"/>
-      <c r="O47" s="50" t="n"/>
-      <c r="P47" s="50" t="n"/>
-      <c r="Q47" s="63">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
+      <c r="A47" s="77" t="n"/>
+      <c r="B47" s="77" t="n"/>
+      <c r="C47" s="77" t="n"/>
+      <c r="D47" s="77" t="n"/>
+      <c r="E47" s="77" t="n"/>
+      <c r="F47" s="77" t="n"/>
+      <c r="G47" s="77" t="n"/>
+      <c r="H47" s="77" t="n"/>
+      <c r="I47" s="77" t="n"/>
+      <c r="J47" s="77" t="n"/>
+      <c r="K47" s="77" t="n"/>
+      <c r="L47" s="77" t="n"/>
+      <c r="M47" s="77" t="n"/>
+      <c r="N47" s="77" t="n"/>
+      <c r="O47" s="77" t="n"/>
+      <c r="P47" s="77" t="n"/>
+      <c r="Q47" s="78" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="50" t="n"/>
-      <c r="B48" s="50" t="n"/>
-      <c r="C48" s="50" t="n"/>
-      <c r="D48" s="50" t="n"/>
-      <c r="E48" s="50" t="n"/>
-      <c r="F48" s="50" t="n"/>
-      <c r="G48" s="50" t="n"/>
-      <c r="H48" s="50" t="n"/>
-      <c r="I48" s="50" t="n"/>
-      <c r="J48" s="50" t="n"/>
-      <c r="K48" s="50" t="n"/>
-      <c r="L48" s="50" t="n"/>
-      <c r="M48" s="50" t="n"/>
-      <c r="N48" s="50" t="n"/>
-      <c r="O48" s="50" t="n"/>
-      <c r="P48" s="50" t="n"/>
-      <c r="Q48" s="63">
-        <f>IF(OR(L51="",L51="در انتظار"),"",IF(Q51="",TODAY(),Q51))</f>
-        <v/>
-      </c>
+      <c r="A48" s="77" t="n"/>
+      <c r="B48" s="77" t="n"/>
+      <c r="C48" s="77" t="n"/>
+      <c r="D48" s="77" t="n"/>
+      <c r="E48" s="77" t="n"/>
+      <c r="F48" s="77" t="n"/>
+      <c r="G48" s="77" t="n"/>
+      <c r="H48" s="77" t="n"/>
+      <c r="I48" s="77" t="n"/>
+      <c r="J48" s="77" t="n"/>
+      <c r="K48" s="77" t="n"/>
+      <c r="L48" s="77" t="n"/>
+      <c r="M48" s="77" t="n"/>
+      <c r="N48" s="77" t="n"/>
+      <c r="O48" s="77" t="n"/>
+      <c r="P48" s="77" t="n"/>
+      <c r="Q48" s="78" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="50" t="n"/>
-      <c r="B49" s="50" t="n"/>
-      <c r="C49" s="50" t="n"/>
-      <c r="D49" s="50" t="n"/>
-      <c r="E49" s="50" t="n"/>
-      <c r="F49" s="50" t="n"/>
-      <c r="G49" s="50" t="n"/>
-      <c r="H49" s="50" t="n"/>
-      <c r="I49" s="50" t="n"/>
-      <c r="J49" s="50" t="n"/>
-      <c r="K49" s="50" t="n"/>
-      <c r="L49" s="50" t="n"/>
-      <c r="M49" s="50" t="n"/>
-      <c r="N49" s="50" t="n"/>
-      <c r="O49" s="50" t="n"/>
-      <c r="P49" s="50" t="n"/>
-      <c r="Q49" s="63">
-        <f>IF(OR(L52="",L52="در انتظار"),"",IF(Q52="",TODAY(),Q52))</f>
-        <v/>
-      </c>
+      <c r="A49" s="77" t="n"/>
+      <c r="B49" s="77" t="n"/>
+      <c r="C49" s="77" t="n"/>
+      <c r="D49" s="77" t="n"/>
+      <c r="E49" s="77" t="n"/>
+      <c r="F49" s="77" t="n"/>
+      <c r="G49" s="77" t="n"/>
+      <c r="H49" s="77" t="n"/>
+      <c r="I49" s="77" t="n"/>
+      <c r="J49" s="77" t="n"/>
+      <c r="K49" s="77" t="n"/>
+      <c r="L49" s="77" t="n"/>
+      <c r="M49" s="77" t="n"/>
+      <c r="N49" s="77" t="n"/>
+      <c r="O49" s="77" t="n"/>
+      <c r="P49" s="77" t="n"/>
+      <c r="Q49" s="78" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="50" t="n"/>
-      <c r="B50" s="50" t="n"/>
-      <c r="C50" s="50" t="n"/>
-      <c r="D50" s="50" t="n"/>
-      <c r="E50" s="50" t="n"/>
-      <c r="F50" s="50" t="n"/>
-      <c r="G50" s="50" t="n"/>
-      <c r="H50" s="50" t="n"/>
-      <c r="I50" s="50" t="n"/>
-      <c r="J50" s="50" t="n"/>
-      <c r="K50" s="50" t="n"/>
-      <c r="L50" s="50" t="n"/>
-      <c r="M50" s="50" t="n"/>
-      <c r="N50" s="50" t="n"/>
-      <c r="O50" s="50" t="n"/>
-      <c r="P50" s="50" t="n"/>
-      <c r="Q50" s="63">
-        <f>IF(OR(L53="",L53="در انتظار"),"",IF(Q53="",TODAY(),Q53))</f>
-        <v/>
-      </c>
+      <c r="A50" s="77" t="n"/>
+      <c r="B50" s="77" t="n"/>
+      <c r="C50" s="77" t="n"/>
+      <c r="D50" s="77" t="n"/>
+      <c r="E50" s="77" t="n"/>
+      <c r="F50" s="77" t="n"/>
+      <c r="G50" s="77" t="n"/>
+      <c r="H50" s="77" t="n"/>
+      <c r="I50" s="77" t="n"/>
+      <c r="J50" s="77" t="n"/>
+      <c r="K50" s="77" t="n"/>
+      <c r="L50" s="77" t="n"/>
+      <c r="M50" s="77" t="n"/>
+      <c r="N50" s="77" t="n"/>
+      <c r="O50" s="77" t="n"/>
+      <c r="P50" s="77" t="n"/>
+      <c r="Q50" s="78" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="50" t="n"/>
-      <c r="B51" s="50" t="n"/>
-      <c r="C51" s="50" t="n"/>
-      <c r="D51" s="50" t="n"/>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="50" t="n"/>
-      <c r="G51" s="50" t="n"/>
-      <c r="H51" s="50" t="n"/>
-      <c r="I51" s="50" t="n"/>
-      <c r="J51" s="50" t="n"/>
-      <c r="K51" s="50" t="n"/>
-      <c r="L51" s="50" t="n"/>
-      <c r="M51" s="50" t="n"/>
-      <c r="N51" s="50" t="n"/>
-      <c r="O51" s="50" t="n"/>
-      <c r="P51" s="50" t="n"/>
-      <c r="Q51" s="63">
-        <f>IF(OR(L54="",L54="در انتظار"),"",IF(Q54="",TODAY(),Q54))</f>
-        <v/>
-      </c>
+      <c r="A51" s="77" t="n"/>
+      <c r="B51" s="77" t="n"/>
+      <c r="C51" s="77" t="n"/>
+      <c r="D51" s="77" t="n"/>
+      <c r="E51" s="77" t="n"/>
+      <c r="F51" s="77" t="n"/>
+      <c r="G51" s="77" t="n"/>
+      <c r="H51" s="77" t="n"/>
+      <c r="I51" s="77" t="n"/>
+      <c r="J51" s="77" t="n"/>
+      <c r="K51" s="77" t="n"/>
+      <c r="L51" s="77" t="n"/>
+      <c r="M51" s="77" t="n"/>
+      <c r="N51" s="77" t="n"/>
+      <c r="O51" s="77" t="n"/>
+      <c r="P51" s="77" t="n"/>
+      <c r="Q51" s="78" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="50" t="n"/>
-      <c r="B52" s="50" t="n"/>
-      <c r="C52" s="50" t="n"/>
-      <c r="D52" s="50" t="n"/>
-      <c r="E52" s="50" t="n"/>
-      <c r="F52" s="50" t="n"/>
-      <c r="G52" s="50" t="n"/>
-      <c r="H52" s="50" t="n"/>
-      <c r="I52" s="50" t="n"/>
-      <c r="J52" s="50" t="n"/>
-      <c r="K52" s="50" t="n"/>
-      <c r="L52" s="50" t="n"/>
-      <c r="M52" s="50" t="n"/>
-      <c r="N52" s="50" t="n"/>
-      <c r="O52" s="50" t="n"/>
-      <c r="P52" s="50" t="n"/>
-      <c r="Q52" s="63">
-        <f>IF(OR(L55="",L55="در انتظار"),"",IF(Q55="",TODAY(),Q55))</f>
-        <v/>
-      </c>
+      <c r="A52" s="77" t="n"/>
+      <c r="B52" s="77" t="n"/>
+      <c r="C52" s="77" t="n"/>
+      <c r="D52" s="77" t="n"/>
+      <c r="E52" s="77" t="n"/>
+      <c r="F52" s="77" t="n"/>
+      <c r="G52" s="77" t="n"/>
+      <c r="H52" s="77" t="n"/>
+      <c r="I52" s="77" t="n"/>
+      <c r="J52" s="77" t="n"/>
+      <c r="K52" s="77" t="n"/>
+      <c r="L52" s="77" t="n"/>
+      <c r="M52" s="77" t="n"/>
+      <c r="N52" s="77" t="n"/>
+      <c r="O52" s="77" t="n"/>
+      <c r="P52" s="77" t="n"/>
+      <c r="Q52" s="78" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q54"/>
@@ -2601,17 +2441,17 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L95" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+    <dataValidation sqref="L5:L12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D7" location="'برنامه تست'!A5"/>
-    <hyperlink ref="D9" location="'برنامه تست'!A5"/>
-    <hyperlink ref="D11" location="'برنامه تست'!A10"/>
+    <hyperlink ref="D8" location="'برنامه تست'!A5"/>
+    <hyperlink ref="D10" location="'برنامه تست'!A9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -3398,10 +3238,10 @@
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Fault</t>
         </is>
       </c>
-      <c r="B1" s="67" t="n"/>
-      <c r="C1" s="67" t="n"/>
-      <c r="D1" s="67" t="n"/>
-      <c r="E1" s="68" t="n"/>
+      <c r="B1" s="40" t="n"/>
+      <c r="C1" s="40" t="n"/>
+      <c r="D1" s="40" t="n"/>
+      <c r="E1" s="41" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="50" t="n"/>
@@ -3615,18 +3455,6 @@
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Fault</t>
         </is>
       </c>
-      <c r="B1" s="50" t="n"/>
-      <c r="C1" s="50" t="n"/>
-      <c r="D1" s="50" t="n"/>
-      <c r="E1" s="50" t="n"/>
-      <c r="F1" s="50" t="n"/>
-      <c r="G1" s="50" t="n"/>
-      <c r="H1" s="50" t="n"/>
-      <c r="I1" s="50" t="n"/>
-      <c r="J1" s="50" t="n"/>
-      <c r="K1" s="50" t="n"/>
-      <c r="L1" s="50" t="n"/>
-      <c r="M1" s="50" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="48" t="inlineStr">
@@ -3634,18 +3462,18 @@
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="67" t="n"/>
-      <c r="C2" s="67" t="n"/>
-      <c r="D2" s="67" t="n"/>
-      <c r="E2" s="67" t="n"/>
-      <c r="F2" s="67" t="n"/>
-      <c r="G2" s="67" t="n"/>
-      <c r="H2" s="67" t="n"/>
-      <c r="I2" s="67" t="n"/>
-      <c r="J2" s="67" t="n"/>
-      <c r="K2" s="67" t="n"/>
-      <c r="L2" s="67" t="n"/>
-      <c r="M2" s="68" t="n"/>
+      <c r="B2" s="40" t="n"/>
+      <c r="C2" s="40" t="n"/>
+      <c r="D2" s="40" t="n"/>
+      <c r="E2" s="40" t="n"/>
+      <c r="F2" s="40" t="n"/>
+      <c r="G2" s="40" t="n"/>
+      <c r="H2" s="40" t="n"/>
+      <c r="I2" s="40" t="n"/>
+      <c r="J2" s="40" t="n"/>
+      <c r="K2" s="40" t="n"/>
+      <c r="L2" s="40" t="n"/>
+      <c r="M2" s="41" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="69" t="inlineStr">
@@ -3744,8 +3572,6 @@
           <t>تأیید نهایی اعتبارسنجی — ماژول Fault</t>
         </is>
       </c>
-      <c r="B1" s="50" t="n"/>
-      <c r="C1" s="50" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="47" t="inlineStr">
@@ -3753,8 +3579,6 @@
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
-      <c r="B2" s="50" t="n"/>
-      <c r="C2" s="50" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="47" t="inlineStr">
@@ -3762,8 +3586,6 @@
           <t>مشخصات تست</t>
         </is>
       </c>
-      <c r="B3" s="50" t="n"/>
-      <c r="C3" s="50" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="47" t="inlineStr">
@@ -4148,8 +3970,6 @@
           <t>ماشین حالت ماژول خطا (Fault)</t>
         </is>
       </c>
-      <c r="B1" s="50" t="n"/>
-      <c r="C1" s="50" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="50" t="n"/>
@@ -4256,22 +4076,6 @@
           <t>برنامهٔ تست آزمایشگاهی — ماژول Fault</t>
         </is>
       </c>
-      <c r="B1" s="50" t="n"/>
-      <c r="C1" s="50" t="n"/>
-      <c r="D1" s="50" t="n"/>
-      <c r="E1" s="50" t="n"/>
-      <c r="F1" s="50" t="n"/>
-      <c r="G1" s="50" t="n"/>
-      <c r="H1" s="50" t="n"/>
-      <c r="I1" s="50" t="n"/>
-      <c r="J1" s="50" t="n"/>
-      <c r="K1" s="50" t="n"/>
-      <c r="L1" s="50" t="n"/>
-      <c r="M1" s="50" t="n"/>
-      <c r="N1" s="50" t="n"/>
-      <c r="O1" s="50" t="n"/>
-      <c r="P1" s="50" t="n"/>
-      <c r="Q1" s="50" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="47" t="inlineStr">
@@ -4279,22 +4083,6 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
-      <c r="B2" s="50" t="n"/>
-      <c r="C2" s="50" t="n"/>
-      <c r="D2" s="50" t="n"/>
-      <c r="E2" s="50" t="n"/>
-      <c r="F2" s="50" t="n"/>
-      <c r="G2" s="50" t="n"/>
-      <c r="H2" s="50" t="n"/>
-      <c r="I2" s="50" t="n"/>
-      <c r="J2" s="50" t="n"/>
-      <c r="K2" s="50" t="n"/>
-      <c r="L2" s="50" t="n"/>
-      <c r="M2" s="50" t="n"/>
-      <c r="N2" s="50" t="n"/>
-      <c r="O2" s="50" t="n"/>
-      <c r="P2" s="50" t="n"/>
-      <c r="Q2" s="50" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="47" t="inlineStr">
@@ -4302,22 +4090,6 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
-      <c r="B3" s="50" t="n"/>
-      <c r="C3" s="50" t="n"/>
-      <c r="D3" s="50" t="n"/>
-      <c r="E3" s="50" t="n"/>
-      <c r="F3" s="50" t="n"/>
-      <c r="G3" s="50" t="n"/>
-      <c r="H3" s="50" t="n"/>
-      <c r="I3" s="50" t="n"/>
-      <c r="J3" s="50" t="n"/>
-      <c r="K3" s="50" t="n"/>
-      <c r="L3" s="50" t="n"/>
-      <c r="M3" s="50" t="n"/>
-      <c r="N3" s="50" t="n"/>
-      <c r="O3" s="50" t="n"/>
-      <c r="P3" s="50" t="n"/>
-      <c r="Q3" s="50" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="48" t="inlineStr">

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -936,6 +936,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="76" t="inlineStr">
         <is>
@@ -1254,7 +1255,7 @@
       </c>
       <c r="C7" s="53" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D7" s="61" t="inlineStr">
@@ -1326,7 +1327,7 @@
       </c>
       <c r="C8" s="53" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D8" s="61" t="inlineStr">

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -891,7 +891,8 @@
     <row r="2">
       <c r="A2" s="47" t="inlineStr">
         <is>
-          <t>Fault | مالک تشخیص متمرکز قطع باتری (FAULT_CHARGER_BAT_LOST، بیت ۶) + ماسک خطای قفل‌شده</t>
+          <t>Fault | این ماژول قطع باتری را در یک جا تشخیص می‌دهد: خطای شمارهٔ ۶ (بیت ۶، FAULT_CHARGER_BAT_LOST).
+ماسک خطا اینجا نگه داشته می‌شود و قفل می‌ماند تا پاک شود.</t>
         </is>
       </c>
     </row>
@@ -908,21 +909,25 @@
     <row r="5">
       <c r="A5" s="47" t="inlineStr">
         <is>
-          <t>دو قاعده: پمپ &gt;14.8V حین شارژ فعال (150ms) و غیبت هر نیم &lt;6V با ورودی سالم (1s)؛ بازیابی هر دو نیم ≥7V بدون پمپ (1s).</t>
+          <t>دو قاعده برای تشخیص قطع باتری:
+قاعدهٔ اول: هنگام شارژ فعال، ولتاژ پمپ از 14.8 ولت بالاتر برود و 150 میلی‌ثانیه بماند.
+قاعدهٔ دوم: ولتاژ یکی از نیم‌باتری‌ها زیر 6 ولت باشد، ورودی سالم باشد و این وضع 1 ثانیه بماند.
+بازیابی: هر دو نیم‌باتری دست‌کم 7 ولت باشند، پمپی در کار نباشد و این وضع 1 ثانیه بماند.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="47" t="inlineStr">
         <is>
-          <t>شارژر و UI فقط پرچم را می‌خوانند؛ حین مود تست دستی شارژر، تشخیص کامل فریز است (تمپ‌های دبانس صفر).</t>
+          <t>شارژر و UI فقط این پرچم را می‌خوانند؛ خودشان تشخیص نمی‌دهند.
+در مود تست دستی شارژر، این تشخیص کاملاً متوقف است و شمارنده‌های صبر (دبانس) صفر می‌مانند.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="47" t="inlineStr">
         <is>
-          <t>بدون snapshot معتبر هیچ Set/Clear انجام نمی‌شود.</t>
+          <t>بدون دادهٔ معتبر، هیچ خطایی نه ثبت می‌شود و نه پاک می‌شود.</t>
         </is>
       </c>
     </row>
@@ -932,7 +937,8 @@
     <row r="9">
       <c r="A9" s="47" t="inlineStr">
         <is>
-          <t>هشدار: تست قطع باتری حین شارژ با جریان محدود و زیر نظارت؛ ولتاژ گره پمپ‌شده می‌تواند بالای 15V برود.</t>
+          <t>هشدار: تست قطع باتری هنگام شارژ را با جریان محدود و زیر نظر انجام بده.
+ولتاژ گره پمپ‌شده می‌تواند از 15 ولت بالاتر برود.</t>
         </is>
       </c>
     </row>
@@ -940,8 +946,12 @@
     <row r="11">
       <c r="A11" s="76" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1064,7 @@
       </c>
       <c r="I4" s="48" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="48" t="inlineStr">
@@ -1079,12 +1089,12 @@
       </c>
       <c r="N4" s="48" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="48" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="48" t="inlineStr">
@@ -1121,8 +1131,8 @@
       </c>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>گام ۱: حین شارژ، سیم یکی از باتری‌ها را از ترمینال جدا کن.
-گام ۲: چند ثانیه صبر کن و چراغ‌ها را ببین: قرمز باید تندتند چشمک بزند، سبز ثابت بماند و هر چند ثانیه سه بوق بیاید.
+          <t>گام ۱: هنگام شارژ، سیم یکی از باتری‌ها را از ترمینال جدا کن.
+گام ۲: چند ثانیه صبر کن و چراغ‌ها را ببین. قرمز باید تندتند چشمک بزند و سبز ثابت بماند. هر چند ثانیه سه بوق بیاید.
 گام ۳: در پنل نگاه کن که خطای شمارهٔ ۶ ثبت شده و جریان شارژ صفر شده است.</t>
         </is>
       </c>
@@ -1161,7 +1171,7 @@
       <c r="N5" s="52" t="n"/>
       <c r="O5" s="54" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="54" t="n"/>
@@ -1233,7 +1243,7 @@
       <c r="N6" s="57" t="n"/>
       <c r="O6" s="59" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="59" t="n"/>
@@ -1305,7 +1315,7 @@
       <c r="N7" s="52" t="n"/>
       <c r="O7" s="54" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P7" s="54" t="n"/>
@@ -1377,7 +1387,7 @@
       <c r="N8" s="52" t="n"/>
       <c r="O8" s="54" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P8" s="54" t="n"/>
@@ -1449,7 +1459,7 @@
       <c r="N9" s="52" t="n"/>
       <c r="O9" s="54" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="54" t="n"/>
@@ -1521,7 +1531,7 @@
       <c r="N10" s="57" t="n"/>
       <c r="O10" s="59" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P10" s="59" t="n"/>
@@ -1593,7 +1603,7 @@
       <c r="N11" s="57" t="n"/>
       <c r="O11" s="59" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P11" s="59" t="n"/>
@@ -1665,7 +1675,7 @@
       <c r="N12" s="57" t="n"/>
       <c r="O12" s="59" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P12" s="59" t="n"/>
@@ -2596,7 +2606,7 @@
       </c>
       <c r="I4" s="48" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="48" t="inlineStr">
@@ -2621,12 +2631,12 @@
       </c>
       <c r="N4" s="48" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="48" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="48" t="inlineStr">
@@ -2704,7 +2714,7 @@
       <c r="N5" s="52" t="n"/>
       <c r="O5" s="54" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="54" t="n"/>
@@ -2739,7 +2749,8 @@
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
 گام ۲: آن را 2 ثانیه به Fault_Evaluate بده.
-گام ۳: ماسک خطا را بخوان: هیچ Set یا Clear کاذبی نباید اتفاق افتاده باشد؛ تابع فقط valid را چک می‌کند و بر اساس فیلدهای صفر تصمیم نمی‌گیرد.</t>
+گام ۳: ماسک خطا را بخوان. هیچ ثبت یا پاک‌شدن کاذبی نباید اتفاق افتاده باشد.
+گام ۴: تابع فقط valid را چک می‌کند و بر اساس فیلدهای صفر تصمیم نمی‌گیرد.</t>
         </is>
       </c>
       <c r="F6" s="54" t="inlineStr">
@@ -3524,7 +3535,7 @@
       </c>
       <c r="J3" s="69" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="K3" s="69" t="inlineStr">
@@ -3643,12 +3654,12 @@
     <row r="8">
       <c r="A8" s="47" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="B8" s="47" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="C8" s="50" t="n"/>
@@ -4135,7 +4146,7 @@
       </c>
       <c r="I4" s="48" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="48" t="inlineStr">
@@ -4160,12 +4171,12 @@
       </c>
       <c r="N4" s="48" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="48" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="48" t="inlineStr">
@@ -4242,7 +4253,7 @@
       <c r="N5" s="57" t="n"/>
       <c r="O5" s="59" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="59" t="n"/>

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -14,8 +14,8 @@
     <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$54</definedName>
@@ -191,7 +191,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -231,6 +231,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -319,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -509,6 +519,32 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -882,7 +918,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Fault</t>
         </is>
@@ -897,7 +933,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="48" t="inlineStr">
+      <c r="A3" s="80" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -1001,7 +1037,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Fault</t>
         </is>
@@ -1022,87 +1058,87 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="80" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="80" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="80" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="80" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="E4" s="80" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="48" t="inlineStr">
+      <c r="F4" s="80" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="G4" s="80" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="48" t="inlineStr">
+      <c r="H4" s="80" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="48" t="inlineStr">
+      <c r="I4" s="80" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="48" t="inlineStr">
+      <c r="J4" s="80" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="K4" s="48" t="inlineStr">
+      <c r="K4" s="80" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="48" t="inlineStr">
+      <c r="L4" s="80" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="48" t="inlineStr">
+      <c r="M4" s="80" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="48" t="inlineStr">
+      <c r="N4" s="80" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="48" t="inlineStr">
+      <c r="O4" s="80" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="48" t="inlineStr">
+      <c r="P4" s="80" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="48" t="inlineStr">
+      <c r="Q4" s="80" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -1114,49 +1150,49 @@
           <t>FL-001</t>
         </is>
       </c>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t>قاعدهٔ پمپ</t>
         </is>
       </c>
-      <c r="C5" s="53" t="inlineStr">
+      <c r="C5" s="58" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>دستگاه با برق شهر روشن است و باتری واقعی در حال شارژ است (چراغ زرد چشمک می‌زند)</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="57" t="inlineStr">
         <is>
           <t>گام ۱: هنگام شارژ، سیم یکی از باتری‌ها را از ترمینال جدا کن.
 گام ۲: چند ثانیه صبر کن و چراغ‌ها را ببین. قرمز باید تندتند چشمک بزند و سبز ثابت بماند. هر چند ثانیه سه بوق بیاید.
 گام ۳: در پنل نگاه کن که خطای شمارهٔ ۶ ثبت شده و جریان شارژ صفر شده است.</t>
         </is>
       </c>
-      <c r="F5" s="54" t="inlineStr">
+      <c r="F5" s="59" t="inlineStr">
         <is>
           <t>کشیدن سیم باتری حین شارژ</t>
         </is>
       </c>
-      <c r="G5" s="54" t="inlineStr">
+      <c r="G5" s="59" t="inlineStr">
         <is>
           <t>کمتر از یک دقیقه</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="57" t="inlineStr">
         <is>
           <t>خطای ۶ (قطع باتری) می‌آید: قرمز چشمک‌تند، سبز ثابت، سه بوق دوره‌ای و شارژ کاملاً متوقف</t>
         </is>
       </c>
-      <c r="I5" s="52" t="inlineStr">
+      <c r="I5" s="57" t="inlineStr">
         <is>
           <t>می‌ماند تا باتری برگردد</t>
         </is>
       </c>
-      <c r="J5" s="52" t="inlineStr">
+      <c r="J5" s="57" t="inlineStr">
         <is>
           <t>باید ببینید: ظرف چند ثانیه خطای قطع باتری می‌آید؛ قرمز تند چشمک می‌زند، سبز ثابت است، سه بوق دوره‌ای می‌آید و شارژ کاملاً می‌ایستد. اگر خطا نیامد یا شارژ ادامه داشت، قبول نیست.</t>
         </is>
@@ -1169,13 +1205,13 @@
       </c>
       <c r="M5" s="52" t="n"/>
       <c r="N5" s="52" t="n"/>
-      <c r="O5" s="54" t="inlineStr">
+      <c r="O5" s="59" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="54" t="n"/>
-      <c r="Q5" s="56">
+      <c r="Q5" s="60">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
@@ -1186,49 +1222,49 @@
           <t>FL-002</t>
         </is>
       </c>
-      <c r="B6" s="57" t="inlineStr">
+      <c r="B6" s="81" t="inlineStr">
         <is>
           <t>قاعدهٔ غیبت</t>
         </is>
       </c>
-      <c r="C6" s="58" t="inlineStr">
+      <c r="C6" s="82" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="57" t="inlineStr">
+      <c r="D6" s="81" t="inlineStr">
         <is>
           <t>باتری را اصلاً وصل نکرده‌ای؛ فقط برق شهر آماده است</t>
         </is>
       </c>
-      <c r="E6" s="57" t="inlineStr">
+      <c r="E6" s="81" t="inlineStr">
         <is>
           <t>گام ۱: بدون باتری، برق شهر را به دستگاه وصل کن.
 گام ۲: چند ثانیه صبر کن.
 گام ۳: چراغ‌ها و پنل را چک کن.</t>
         </is>
       </c>
-      <c r="F6" s="59" t="inlineStr">
+      <c r="F6" s="83" t="inlineStr">
         <is>
           <t>روشن‌کردن دستگاه بدون باتری با برق شهر</t>
         </is>
       </c>
-      <c r="G6" s="59" t="inlineStr">
+      <c r="G6" s="83" t="inlineStr">
         <is>
           <t>کمتر از یک دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="57" t="inlineStr">
+      <c r="H6" s="81" t="inlineStr">
         <is>
           <t>خطای ۶ می‌آید (قرمز چشمک‌تند و سه بوق) و شارژ هیچ‌وقت شروع نمی‌شود</t>
         </is>
       </c>
-      <c r="I6" s="57" t="inlineStr">
+      <c r="I6" s="81" t="inlineStr">
         <is>
           <t>می‌ماند تا باتری وصل شود</t>
         </is>
       </c>
-      <c r="J6" s="57" t="inlineStr">
+      <c r="J6" s="81" t="inlineStr">
         <is>
           <t>باید ببینید: بدون باتری خطای قطع باتری می‌آید و شارژ هیچ‌وقت شروع نمی‌شود. اگر شارژ بی‌باتری شروع شد، قبول نیست.</t>
         </is>
@@ -1241,13 +1277,13 @@
       </c>
       <c r="M6" s="57" t="n"/>
       <c r="N6" s="57" t="n"/>
-      <c r="O6" s="59" t="inlineStr">
+      <c r="O6" s="83" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="59" t="n"/>
-      <c r="Q6" s="60">
+      <c r="Q6" s="84">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -1258,49 +1294,49 @@
           <t>FL-003</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
+      <c r="B7" s="57" t="inlineStr">
         <is>
           <t>بازیابی</t>
         </is>
       </c>
-      <c r="C7" s="53" t="inlineStr">
+      <c r="C7" s="58" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D7" s="61" t="inlineStr">
+      <c r="D7" s="62" t="inlineStr">
         <is>
           <t>از FL-001 ادامه بده؛ خطای ۶ فعال است و سیم باتری جداست</t>
         </is>
       </c>
-      <c r="E7" s="52" t="inlineStr">
+      <c r="E7" s="57" t="inlineStr">
         <is>
           <t>گام ۱: سیم باتری را سر جایش وصل کن.
 گام ۲: چند ثانیه صبر کن: چشمک قرمز و بوق باید قطع شود.
 گام ۳: کمی بیشتر صبر کن؛ شارژ باید بعد از یک مکث کوتاه آرام از سر گرفته شود.</t>
         </is>
       </c>
-      <c r="F7" s="54" t="inlineStr">
+      <c r="F7" s="59" t="inlineStr">
         <is>
           <t>وصل دوبارهٔ باتری</t>
         </is>
       </c>
-      <c r="G7" s="54" t="inlineStr">
+      <c r="G7" s="59" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H7" s="52" t="inlineStr">
+      <c r="H7" s="57" t="inlineStr">
         <is>
           <t>خطای ۶ خودش پاک می‌شود و شارژ بدون پرش و ناگهانی برگشتن، عادی شروع می‌شود</t>
         </is>
       </c>
-      <c r="I7" s="52" t="inlineStr">
+      <c r="I7" s="57" t="inlineStr">
         <is>
           <t>پاک‌شدن خودکار با برگشت باتری</t>
         </is>
       </c>
-      <c r="J7" s="52" t="inlineStr">
+      <c r="J7" s="57" t="inlineStr">
         <is>
           <t>باید ببینید: با برگشت باتری خطا خودش پاک می‌شود و شارژ آرام و عادی شروع می‌شود. اگر خطا ماند یا شارژ خشن شروع شد، قبول نیست.</t>
         </is>
@@ -1313,13 +1349,13 @@
       </c>
       <c r="M7" s="52" t="n"/>
       <c r="N7" s="52" t="n"/>
-      <c r="O7" s="54" t="inlineStr">
+      <c r="O7" s="59" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P7" s="54" t="n"/>
-      <c r="Q7" s="56">
+      <c r="Q7" s="60">
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
@@ -1330,49 +1366,49 @@
           <t>FL-005</t>
         </is>
       </c>
-      <c r="B8" s="52" t="inlineStr">
+      <c r="B8" s="81" t="inlineStr">
         <is>
           <t>آینه در شارژر</t>
         </is>
       </c>
-      <c r="C8" s="53" t="inlineStr">
+      <c r="C8" s="82" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="85" t="inlineStr">
         <is>
           <t>خطای ۶ را مثل FL-001 ساخته‌ای و فعال است</t>
         </is>
       </c>
-      <c r="E8" s="52" t="inlineStr">
+      <c r="E8" s="81" t="inlineStr">
         <is>
           <t>گام ۱: یک آمپرمتر دستی سریِ مسیر شارژ بگذار یا جریان شارژ پنل را نگاه کن.
 گام ۲: تا وقتی خطا هست جریان را زیر نظر بگیر.
 گام ۳: باتری را وصل کن و ببین شارژ کی برمی‌گردد.</t>
         </is>
       </c>
-      <c r="F8" s="54" t="inlineStr">
+      <c r="F8" s="83" t="inlineStr">
         <is>
           <t>نگه‌داشتن خطای ۶ و بعد وصل باتری</t>
         </is>
       </c>
-      <c r="G8" s="54" t="inlineStr">
+      <c r="G8" s="83" t="inlineStr">
         <is>
           <t>دو دقیقه</t>
         </is>
       </c>
-      <c r="H8" s="52" t="inlineStr">
+      <c r="H8" s="81" t="inlineStr">
         <is>
           <t>تا وقتی خطای ۶ هست جریان شارژ صفر می‌ماند؛ شارژر بیکار است و فقط با برگشت باتری دوباره راه می‌افتد</t>
         </is>
       </c>
-      <c r="I8" s="52" t="inlineStr">
+      <c r="I8" s="81" t="inlineStr">
         <is>
           <t>توقف کامل تا بازیابی</t>
         </is>
       </c>
-      <c r="J8" s="52" t="inlineStr">
+      <c r="J8" s="81" t="inlineStr">
         <is>
           <t>باید ببینید: تا وقتی خطا هست جریان شارژ در پنل صفر می‌ماند و فقط با برگشت باتری شارژ راه می‌افتد. اگر حین خطا جریان شارژ دیدید، قبول نیست.</t>
         </is>
@@ -1385,13 +1421,13 @@
       </c>
       <c r="M8" s="52" t="n"/>
       <c r="N8" s="52" t="n"/>
-      <c r="O8" s="54" t="inlineStr">
+      <c r="O8" s="83" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P8" s="54" t="n"/>
-      <c r="Q8" s="56">
+      <c r="Q8" s="84">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
@@ -1402,49 +1438,49 @@
           <t>FL-007</t>
         </is>
       </c>
-      <c r="B9" s="52" t="inlineStr">
+      <c r="B9" s="57" t="inlineStr">
         <is>
           <t>فریز در مود دستی</t>
         </is>
       </c>
-      <c r="C9" s="53" t="inlineStr">
+      <c r="C9" s="58" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D9" s="52" t="inlineStr">
+      <c r="D9" s="57" t="inlineStr">
         <is>
           <t>دستگاه روشن و از پنل، مود تست دستی شارژر را می‌توانی روشن کنی</t>
         </is>
       </c>
-      <c r="E9" s="52" t="inlineStr">
+      <c r="E9" s="57" t="inlineStr">
         <is>
           <t>گام ۱: از پنل مود تست دستی شارژر را فعال کن.
 گام ۲: در همین مود سیم باتری را بکش و چند ثانیه صبر کن.
 گام ۳: باتری را وصل کن.</t>
         </is>
       </c>
-      <c r="F9" s="54" t="inlineStr">
+      <c r="F9" s="59" t="inlineStr">
         <is>
           <t>قطع و وصل باتری داخل مود دستی</t>
         </is>
       </c>
-      <c r="G9" s="54" t="inlineStr">
+      <c r="G9" s="59" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H9" s="52" t="inlineStr">
+      <c r="H9" s="57" t="inlineStr">
         <is>
           <t>در مود دستی خطای ۶ ساخته نمی‌شود و چراغ قرمز قطع باتری نمی‌آید</t>
         </is>
       </c>
-      <c r="I9" s="52" t="inlineStr">
+      <c r="I9" s="57" t="inlineStr">
         <is>
           <t>بدون قفل در مود دستی</t>
         </is>
       </c>
-      <c r="J9" s="52" t="inlineStr">
+      <c r="J9" s="57" t="inlineStr">
         <is>
           <t>باید ببینید: در مود دستی خطای قطع باتری ساخته نمی‌شود و چراغ قرمز آن نمی‌آید. اگر خطا آمد، قبول نیست.</t>
         </is>
@@ -1457,13 +1493,13 @@
       </c>
       <c r="M9" s="52" t="n"/>
       <c r="N9" s="52" t="n"/>
-      <c r="O9" s="54" t="inlineStr">
+      <c r="O9" s="59" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P9" s="54" t="n"/>
-      <c r="Q9" s="56">
+      <c r="Q9" s="60">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
@@ -1474,49 +1510,49 @@
           <t>FL-008</t>
         </is>
       </c>
-      <c r="B10" s="57" t="inlineStr">
+      <c r="B10" s="81" t="inlineStr">
         <is>
           <t>خروج از مود دستی</t>
         </is>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="83" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D10" s="62" t="inlineStr">
+      <c r="D10" s="85" t="inlineStr">
         <is>
           <t>از FL-007 ادامه بده؛ مود دستی فعال است</t>
         </is>
       </c>
-      <c r="E10" s="62" t="inlineStr">
+      <c r="E10" s="85" t="inlineStr">
         <is>
           <t>گام ۱: از پنل از مود تست دستی خارج شو.
 گام ۲: حالا سیم باتری را حین شارژ بکش.
 گام ۳: چراغ‌ها را ببین.</t>
         </is>
       </c>
-      <c r="F10" s="59" t="inlineStr">
+      <c r="F10" s="83" t="inlineStr">
         <is>
           <t>خروج از مود دستی و قطع باتری</t>
         </is>
       </c>
-      <c r="G10" s="59" t="inlineStr">
+      <c r="G10" s="83" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H10" s="57" t="inlineStr">
+      <c r="H10" s="81" t="inlineStr">
         <is>
           <t>بعد از خروج از مود دستی، قطع باتری دوباره مثل حالت عادی خطای ۶ می‌سازد</t>
         </is>
       </c>
-      <c r="I10" s="57" t="inlineStr">
+      <c r="I10" s="81" t="inlineStr">
         <is>
           <t>برگشت رفتار عادی</t>
         </is>
       </c>
-      <c r="J10" s="62" t="inlineStr">
+      <c r="J10" s="85" t="inlineStr">
         <is>
           <t>باید ببینید: بعد از خروج از مود دستی، قطع باتری دوباره خطای همیشگی را می‌سازد. اگر نساخت، قبول نیست.</t>
         </is>
@@ -1529,13 +1565,13 @@
       </c>
       <c r="M10" s="57" t="n"/>
       <c r="N10" s="57" t="n"/>
-      <c r="O10" s="59" t="inlineStr">
+      <c r="O10" s="83" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P10" s="59" t="n"/>
-      <c r="Q10" s="60">
+      <c r="Q10" s="84">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
@@ -1618,49 +1654,49 @@
           <t>FL-004</t>
         </is>
       </c>
-      <c r="B12" s="57" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>هیسترزیس 6/7V</t>
         </is>
       </c>
-      <c r="C12" s="59" t="inlineStr">
+      <c r="C12" s="83" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D12" s="57" t="inlineStr">
+      <c r="D12" s="81" t="inlineStr">
         <is>
           <t>به‌جای یکی از باتری‌ها منبع آزمایشگاهی گذاشته‌ای؛ دستگاه با برق شهر روشن است</t>
         </is>
       </c>
-      <c r="E12" s="57" t="inlineStr">
+      <c r="E12" s="81" t="inlineStr">
         <is>
           <t>گام ۱: ولتاژ منبع را حدود ۶٫۵ ولت نگه دار (نه وصلِ سالم، نه قطعِ کامل).
 گام ۲: دو دقیقه نگاه کن؛ خطا نباید پرپر بزند.
 گام ۳: ولتاژ را بالای ۷ ببر (سالم) و بعد زیر ۶ ببر (قطع) و هر بار رفتار را چک کن.</t>
         </is>
       </c>
-      <c r="F12" s="59" t="inlineStr">
+      <c r="F12" s="83" t="inlineStr">
         <is>
           <t>ولتاژ یک نیم باتری: ۶٫۵ بعد بالای ۷ بعد زیر ۶ ولت</t>
         </is>
       </c>
-      <c r="G12" s="59" t="inlineStr">
+      <c r="G12" s="83" t="inlineStr">
         <is>
           <t>سه دقیقه</t>
         </is>
       </c>
-      <c r="H12" s="57" t="inlineStr">
+      <c r="H12" s="81" t="inlineStr">
         <is>
           <t>روی ۶٫۵ نه خطای تازه می‌آید نه پاک و ست می‌شود؛ بالای ۷ سالم است و زیر ۶ خطای ۶ می‌آید</t>
         </is>
       </c>
-      <c r="I12" s="57" t="inlineStr">
+      <c r="I12" s="81" t="inlineStr">
         <is>
           <t>بدون پرپر دور مرز</t>
         </is>
       </c>
-      <c r="J12" s="57" t="inlineStr">
+      <c r="J12" s="81" t="inlineStr">
         <is>
           <t>باید ببینید: روی ولتاژ وسط (حدود ۶٫۵ ولت) نه خطای تازه می‌آید نه پرپر می‌زند؛ بالای حد سالم و زیر حد خطا می‌آید. اگر روی وسط پرپر زد، قبول نیست.</t>
         </is>
@@ -1673,13 +1709,13 @@
       </c>
       <c r="M12" s="57" t="n"/>
       <c r="N12" s="57" t="n"/>
-      <c r="O12" s="59" t="inlineStr">
+      <c r="O12" s="83" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P12" s="59" t="n"/>
-      <c r="Q12" s="60">
+      <c r="Q12" s="84">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
@@ -2472,7 +2508,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2499,7 +2535,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="86" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
@@ -2564,87 +2600,87 @@
       <c r="Q3" s="50" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="80" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="80" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="80" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="80" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="E4" s="80" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="48" t="inlineStr">
+      <c r="F4" s="80" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="G4" s="80" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="48" t="inlineStr">
+      <c r="H4" s="80" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="48" t="inlineStr">
+      <c r="I4" s="80" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="48" t="inlineStr">
+      <c r="J4" s="80" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="48" t="inlineStr">
+      <c r="K4" s="80" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="48" t="inlineStr">
+      <c r="L4" s="80" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="48" t="inlineStr">
+      <c r="M4" s="80" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="48" t="inlineStr">
+      <c r="N4" s="80" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="48" t="inlineStr">
+      <c r="O4" s="80" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="48" t="inlineStr">
+      <c r="P4" s="80" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="48" t="inlineStr">
+      <c r="Q4" s="80" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -2656,22 +2692,22 @@
           <t>FL-009</t>
         </is>
       </c>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t>تزریق دستی</t>
         </is>
       </c>
-      <c r="C5" s="54" t="inlineStr">
+      <c r="C5" s="59" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="57" t="inlineStr">
         <is>
           <t>دیباگر وصل</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="57" t="inlineStr">
         <is>
           <t>گام ۱: دیباگر را وصل کن و مسیر تست func__Fault_Set/Clear را آماده کن.
 گام ۲: چند بیت دلخواه را یک بار Set و یک بار Clear کن.
@@ -2679,27 +2715,27 @@
 گام ۴: ماسک باید دقیقاً همان بیت‌هایی باشد که ست کردی و Any با بودن/نبودن بیت درست جواب دهد.</t>
         </is>
       </c>
-      <c r="F5" s="54" t="inlineStr">
+      <c r="F5" s="59" t="inlineStr">
         <is>
           <t>بیت‌های دلخواه</t>
         </is>
       </c>
-      <c r="G5" s="54" t="inlineStr">
+      <c r="G5" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="52" t="inlineStr">
+      <c r="H5" s="57" t="inlineStr">
         <is>
           <t>ماسک دقیقاً Set/Clear می‌شود</t>
         </is>
       </c>
-      <c r="I5" s="52" t="inlineStr">
+      <c r="I5" s="57" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="52" t="inlineStr">
+      <c r="J5" s="57" t="inlineStr">
         <is>
           <t>Get/Any مطابق</t>
         </is>
@@ -2712,13 +2748,13 @@
       </c>
       <c r="M5" s="52" t="n"/>
       <c r="N5" s="52" t="n"/>
-      <c r="O5" s="54" t="inlineStr">
+      <c r="O5" s="59" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="54" t="n"/>
-      <c r="Q5" s="56" t="inlineStr">
+      <c r="Q5" s="60" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2730,22 +2766,22 @@
           <t>FA-020</t>
         </is>
       </c>
-      <c r="B6" s="52" t="inlineStr">
+      <c r="B6" s="81" t="inlineStr">
         <is>
           <t>snapshot zeroing</t>
         </is>
       </c>
-      <c r="C6" s="53" t="inlineStr">
+      <c r="C6" s="82" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="52" t="inlineStr">
+      <c r="D6" s="81" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="E6" s="52" t="inlineStr">
+      <c r="E6" s="81" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
 گام ۲: آن را 2 ثانیه به Fault_Evaluate بده.
@@ -2753,27 +2789,27 @@
 گام ۴: تابع فقط valid را چک می‌کند و بر اساس فیلدهای صفر تصمیم نمی‌گیرد.</t>
         </is>
       </c>
-      <c r="F6" s="54" t="inlineStr">
+      <c r="F6" s="83" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G6" s="54" t="inlineStr">
+      <c r="G6" s="83" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H6" s="52" t="inlineStr">
+      <c r="H6" s="81" t="inlineStr">
         <is>
           <t>بدون Set/Clear کاذب؛ فقط valid چک شود؛ هر 9 فیلد صفر شده باشد</t>
         </is>
       </c>
-      <c r="I6" s="52" t="inlineStr">
+      <c r="I6" s="81" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="52" t="inlineStr">
+      <c r="J6" s="81" t="inlineStr">
         <is>
           <t>بدون fault کاذب</t>
         </is>
@@ -2786,13 +2822,13 @@
       </c>
       <c r="M6" s="52" t="n"/>
       <c r="N6" s="52" t="n"/>
-      <c r="O6" s="54" t="inlineStr">
+      <c r="O6" s="83" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
       <c r="P6" s="54" t="n"/>
-      <c r="Q6" s="56">
+      <c r="Q6" s="84">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -3245,7 +3281,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="87" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Fault</t>
         </is>
@@ -3462,14 +3498,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Fault</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="48" t="inlineStr">
+      <c r="A2" s="80" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
@@ -3579,7 +3615,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="46" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Fault</t>
         </is>
@@ -3814,7 +3850,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3826,7 +3862,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="74" t="inlineStr">
+      <c r="A1" s="88" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
@@ -3882,7 +3918,7 @@
       <c r="B7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="74" t="inlineStr">
+      <c r="A8" s="88" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
@@ -3918,7 +3954,7 @@
       <c r="B12" s="50" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="74" t="inlineStr">
+      <c r="A13" s="88" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
@@ -3965,98 +4001,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>ماشین حالت ماژول خطا (Fault)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="50" t="n"/>
-      <c r="B2" s="50" t="n"/>
-      <c r="C2" s="50" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>حالت‌ها و گذارهای همین ماژول</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Fault_State_Machine.xlsx</t>
-        </is>
-      </c>
-      <c r="C3" s="50" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>../../../Documentation/System_State_Machine.xlsx</t>
-        </is>
-      </c>
-      <c r="C4" s="50" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>راهنمای رنگ‌ها</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
-        </is>
-      </c>
-      <c r="C5" s="50" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>بازتولید</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>python3 tools/make_module_state_machines.py</t>
-        </is>
-      </c>
-      <c r="C6" s="50" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F4E79"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4083,7 +4028,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>برنامهٔ تست آزمایشگاهی — ماژول Fault</t>
         </is>
@@ -4104,87 +4049,87 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="80" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="80" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="80" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="80" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="E4" s="80" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="48" t="inlineStr">
+      <c r="F4" s="80" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="G4" s="80" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="48" t="inlineStr">
+      <c r="H4" s="80" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="48" t="inlineStr">
+      <c r="I4" s="80" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="48" t="inlineStr">
+      <c r="J4" s="80" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="48" t="inlineStr">
+      <c r="K4" s="80" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="48" t="inlineStr">
+      <c r="L4" s="80" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="48" t="inlineStr">
+      <c r="M4" s="80" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="48" t="inlineStr">
+      <c r="N4" s="80" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="48" t="inlineStr">
+      <c r="O4" s="80" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="48" t="inlineStr">
+      <c r="P4" s="80" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="48" t="inlineStr">
+      <c r="Q4" s="80" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -4281,4 +4226,87 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول خطا (Fault)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Fault_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -190,8 +190,24 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="00808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -241,6 +257,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -329,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -545,6 +566,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -911,7 +953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -978,7 +1020,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="76" t="inlineStr">
         <is>
@@ -988,6 +1029,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="89" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B13" s="90" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1034,12 +1087,20 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="79" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Fault</t>
+        </is>
+      </c>
+      <c r="T1" s="91" t="inlineStr">
+        <is>
+          <t>ورودی‌های پیش‌بینی — خانه‌های زرد را عوض کن و ستون «پیش‌بینی زنده» را ببین</t>
         </is>
       </c>
     </row>
@@ -1049,6 +1110,14 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="T2" s="92" t="inlineStr">
+        <is>
+          <t>ولتاژ نیم بالای باتری (میلی‌ولت)</t>
+        </is>
+      </c>
+      <c r="U2" s="93" t="n">
+        <v>12500</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="47" t="inlineStr">
@@ -1056,6 +1125,14 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="T3" s="92" t="inlineStr">
+        <is>
+          <t>ولتاژ نیم پایین باتری (میلی‌ولت)</t>
+        </is>
+      </c>
+      <c r="U3" s="93" t="n">
+        <v>12500</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="80" t="inlineStr">
@@ -1142,6 +1219,19 @@
         <is>
           <t>تاریخ</t>
         </is>
+      </c>
+      <c r="R4" s="80" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
+        </is>
+      </c>
+      <c r="T4" s="92" t="inlineStr">
+        <is>
+          <t>در حال شارژ؟ (1/0)</t>
+        </is>
+      </c>
+      <c r="U4" s="93" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
@@ -1215,6 +1305,18 @@
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
+      <c r="R5" s="90">
+        <f>IF(AND($U$4=1,$U$6&gt;14800),"بعد از ۱۵۰ میلی‌ثانیه: خطای ۶ (قطع باتری) ثبت می‌شود",IF($U$4=1,"پمپ زیر ۱۴٫۸ ولت است: خطایی نیست","شارژ فعال نیست: قاعدهٔ پمپ کار نمی‌کند"))</f>
+        <v/>
+      </c>
+      <c r="T5" s="92" t="inlineStr">
+        <is>
+          <t>ورودی سالم است؟ (1/0)</t>
+        </is>
+      </c>
+      <c r="U5" s="93" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="51" t="inlineStr">
@@ -1287,6 +1389,18 @@
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
+      <c r="R6" s="90">
+        <f>IF(AND($U$5=1,OR($U$2&lt;6000,$U$3&lt;6000)),"بعد از ۱ ثانیه: خطای ۶ (یک نیم‌باتری نیست)",IF(AND($U$2&gt;=6000,$U$3&gt;=6000),"هر دو نیم حاضرند: خطای غیبت نیست","ورودی سالم نیست: این قاعده قضاوت نمی‌کند"))</f>
+        <v/>
+      </c>
+      <c r="T6" s="92" t="inlineStr">
+        <is>
+          <t>ولتاژ گره پمپ (میلی‌ولت)</t>
+        </is>
+      </c>
+      <c r="U6" s="93" t="n">
+        <v>12000</v>
+      </c>
     </row>
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="51" t="inlineStr">
@@ -1359,6 +1473,18 @@
         <f>IF(OR(L7="",L7="در انتظار"),"",IF(Q7="",TODAY(),Q7))</f>
         <v/>
       </c>
+      <c r="R7" s="90">
+        <f>IF(AND($U$2&gt;=7000,$U$3&gt;=7000,$U$6&lt;14800),"بعد از ۱ ثانیه: خطای ۶ پاک می‌شود و شارژ برمی‌گردد","هنوز شرایط بازیابی کامل نیست (هر دو نیم بالای ۷ ولت و بدون پمپ)")</f>
+        <v/>
+      </c>
+      <c r="T7" s="92" t="inlineStr">
+        <is>
+          <t>مود دستی شارژر؟ (1/0)</t>
+        </is>
+      </c>
+      <c r="U7" s="93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="40.5" customHeight="1">
       <c r="A8" s="51" t="inlineStr">
@@ -1431,6 +1557,15 @@
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
+      <c r="R8" s="90">
+        <f>IF(AND($U$5=1,OR($U$2&lt;6000,$U$3&lt;6000)),"شارژر هم خطای ۶ را می‌بیند و شارژ صفر می‌شود","شارژر عادی کار می‌کند")</f>
+        <v/>
+      </c>
+      <c r="T8" s="94" t="inlineStr">
+        <is>
+          <t>پیش‌بینی برای حالت پایدار است؛ چشمک و زمان‌بندی را با چشم و کرنومتر چک کن و با برد مقایسه کن.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="40.5" customHeight="1">
       <c r="A9" s="51" t="inlineStr">
@@ -1503,6 +1638,10 @@
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
+      <c r="R9" s="90">
+        <f>IF($U$7=1,"مود دستی: تشخیص قطع باتری فریز است و خطای تازه‌ای نمی‌آید","مود عادی: تشخیص فعال است")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="A10" s="51" t="inlineStr">
@@ -1575,6 +1714,10 @@
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
+      <c r="R10" s="90">
+        <f>IF($U$7=1,"هنوز در مود دستی است: تشخیص فریز مانده","از مود دستی خارج شده: تشخیص دوباره فعال است")</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="51" t="inlineStr">
@@ -1647,6 +1790,11 @@
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
+      <c r="R11" s="95" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="54" customHeight="1">
       <c r="A12" s="51" t="inlineStr">
@@ -1717,6 +1865,10 @@
       <c r="P12" s="59" t="n"/>
       <c r="Q12" s="84">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+      <c r="R12" s="90">
+        <f>IF(OR($U$2&lt;6000,$U$3&lt;6000),"زیر ۶ ولت: سمت خطا",IF(AND($U$2&gt;=7000,$U$3&gt;=7000),"بالای ۷ ولت: سمت پاک‌شدن","بین ۶ و ۷ ولت: همان قبلی می‌ماند (هیسترزیس)"))</f>
         <v/>
       </c>
     </row>
@@ -2482,9 +2634,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Q54"/>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="T8:U8"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
@@ -4235,7 +4389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4249,7 +4403,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -4298,7 +4451,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -1067,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2631,6 +2631,65 @@
       <c r="O52" s="77" t="n"/>
       <c r="P52" s="77" t="n"/>
       <c r="Q52" s="78" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FL-011</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>اشمیت مشترک ورودی</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>پنل و تستر هاست Fault در دسترس است</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>گام ۱: q33/q34 را ۲۱۰۰۰/۲۸۰۰۰ و q169/q170 را ۵۰۰/۵۰۰ بگذار.
+گام ۲: host_test_fault.c را اجرا کن.
+گام ۳: روی برد، ورودی را از ۲۱۲۰۰ به ۲۱۵۰۰ و از ۲۷۸۰۰ به ۲۷۵۰۰ ببر و مجوز/شارژ/چراغ را ببین.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>q169/q170 قابل‌تنظیم، گیره 0..3000 و span/4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>دو دقیقه</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>یک مجوز مشترک برای UI، MCU و شارژر؛ بیرون پنجره خام فوراً قطع، برگشت فقط داخل باند داخلی</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ماندگار در NVM</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>PASS: هر سه مصرف‌کننده هم‌زمان عوض می‌شوند. FAIL: هر مصرف‌کننده آستانه جدا دارد.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q54"/>

--- a/Firmware/Modules/Fault/Fault_Validation.xlsx
+++ b/Firmware/Modules/Fault/Fault_Validation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های آزمایشگاهی" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$54</definedName>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B5" s="70" t="inlineStr">
         <is>
-          <t>هر نیم &lt;6V با ورودی سالم، 1s</t>
+          <t>یکی از دو نیم &lt;6V با ورودی سالم، 1s</t>
         </is>
       </c>
       <c r="C5" s="70" t="inlineStr">
